--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -188,8 +188,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ExperimentResultsTable" displayName="ExperimentResultsTable" ref="A1:AE13" headerRowCount="1">
-  <autoFilter ref="A1:AE13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ExperimentResultsTable" displayName="ExperimentResultsTable" ref="A1:AE25" headerRowCount="1">
+  <autoFilter ref="A1:AE25"/>
   <tableColumns count="31">
     <tableColumn id="1" name="Run"/>
     <tableColumn id="2" name="Stage"/>
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>LS-Rep_BCD_RSML_3 — Experiment Metrics (DART-R)</t>
+          <t>LS-Rep_BCD_RSML_3 — Experiment Metrics (DART-R / RDT-CD)</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13 17:38:07 +0800</t>
+          <t>2026-09-15 08:57:47 +0800</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>outputs/DirectionC (Run1 DART-R) + outputs/DART-R-TS (Run2 DART-R-TS); launcher logs excluded</t>
+          <t>outputs/DirectionC (DART-R) + outputs/DART-R-TS + outputs/RDT-CD; launcher logs excluded</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8">
@@ -596,7 +596,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>DART-R=8, DART-R-TS=4</t>
+          <t>DART-R=8, DART-R-TS=4, RDT-CD=12</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Run1 = C0 (gradient routing, failed) vs B0; Run2 = DART-R-TS (C1 task-space) vs B0, B0 only complete. Both 40k, seed 2333 — not a multi-seed paper result.</t>
+          <t>DART-R=C0 gradient routing (failed); DART-R-TS=C1 fixed teacher (failed, B0 only); RDT-CD=D1 dynamic teacher (B0/D1/D2). All 40k, seed 2333 — not a multi-seed paper result.</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE13"/>
+  <dimension ref="A1:AE25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2196,8 +2196,1388 @@
         </is>
       </c>
     </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>RDT-CD</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>B0</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Baseline_A2Net_LWGANet_L0</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>mode=none; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J14" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L14" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O14" s="7" t="n"/>
+      <c r="P14" s="7" t="n"/>
+      <c r="Q14" s="5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R14" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S14" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v>97.6781</v>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v>97.9079</v>
+      </c>
+      <c r="W14" s="8" t="n">
+        <v>99.45580000000001</v>
+      </c>
+      <c r="X14" s="8" t="n">
+        <v>97.7929</v>
+      </c>
+      <c r="Y14" s="8" t="n">
+        <v>95.6811</v>
+      </c>
+      <c r="Z14" s="8" t="n">
+        <v>97.4825</v>
+      </c>
+      <c r="AA14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="5" t="inlineStr">
+        <is>
+          <t>2:20:38.145359</t>
+        </is>
+      </c>
+      <c r="AD14" s="5" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD</t>
+        </is>
+      </c>
+      <c r="AE14" s="6" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/B0/CDD/steps_40000/seed_2333/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>RDT-CD</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>B0</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Baseline_A2Net_LWGANet_L0</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>mode=none; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J15" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O15" s="7" t="n"/>
+      <c r="P15" s="7" t="n"/>
+      <c r="Q15" s="5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R15" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S15" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v>90.49430000000001</v>
+      </c>
+      <c r="V15" s="8" t="n">
+        <v>92.0642</v>
+      </c>
+      <c r="W15" s="8" t="n">
+        <v>99.11839999999999</v>
+      </c>
+      <c r="X15" s="8" t="n">
+        <v>91.27250000000001</v>
+      </c>
+      <c r="Y15" s="8" t="n">
+        <v>83.9461</v>
+      </c>
+      <c r="Z15" s="8" t="n">
+        <v>90.8083</v>
+      </c>
+      <c r="AA15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="5" t="inlineStr">
+        <is>
+          <t>2:16:24.770920</t>
+        </is>
+      </c>
+      <c r="AD15" s="5" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD</t>
+        </is>
+      </c>
+      <c r="AE15" s="6" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/B0/LEVIR/steps_40000/seed_2333/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>RDT-CD</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>B0</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Baseline_A2Net_LWGANet_L0</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>mode=none; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O16" s="7" t="n"/>
+      <c r="P16" s="7" t="n"/>
+      <c r="Q16" s="5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R16" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S16" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v>76.25699999999999</v>
+      </c>
+      <c r="V16" s="8" t="n">
+        <v>85.93730000000001</v>
+      </c>
+      <c r="W16" s="8" t="n">
+        <v>91.45790000000001</v>
+      </c>
+      <c r="X16" s="8" t="n">
+        <v>80.8083</v>
+      </c>
+      <c r="Y16" s="8" t="n">
+        <v>67.79690000000001</v>
+      </c>
+      <c r="Z16" s="8" t="n">
+        <v>75.3399</v>
+      </c>
+      <c r="AA16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="5" t="inlineStr">
+        <is>
+          <t>2:19:29.914205</t>
+        </is>
+      </c>
+      <c r="AD16" s="5" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD</t>
+        </is>
+      </c>
+      <c r="AE16" s="6" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/B0/SYSU/steps_40000/seed_2333/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>RDT-CD</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>B0</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Baseline_A2Net_LWGANet_L0</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>mode=none; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J17" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O17" s="7" t="n"/>
+      <c r="P17" s="7" t="n"/>
+      <c r="Q17" s="5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R17" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S17" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v>92.7128</v>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v>95.3785</v>
+      </c>
+      <c r="W17" s="8" t="n">
+        <v>99.5326</v>
+      </c>
+      <c r="X17" s="8" t="n">
+        <v>94.02669999999999</v>
+      </c>
+      <c r="Y17" s="8" t="n">
+        <v>88.7269</v>
+      </c>
+      <c r="Z17" s="8" t="n">
+        <v>93.78360000000001</v>
+      </c>
+      <c r="AA17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="5" t="inlineStr">
+        <is>
+          <t>2:10:04.530973</t>
+        </is>
+      </c>
+      <c r="AD17" s="5" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD</t>
+        </is>
+      </c>
+      <c r="AE17" s="6" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/B0/WHU/steps_40000/seed_2333/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>RDT-CD</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>D1_RDT_CD_Full</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>mode=direction_c; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J18" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L18" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O18" s="7" t="n"/>
+      <c r="P18" s="7" t="n"/>
+      <c r="Q18" s="5" t="inlineStr">
+        <is>
+          <t>direction_c</t>
+        </is>
+      </c>
+      <c r="R18" s="8" t="n">
+        <v>2.9406</v>
+      </c>
+      <c r="S18" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v>97.69539999999999</v>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v>97.8993</v>
+      </c>
+      <c r="W18" s="8" t="n">
+        <v>99.4568</v>
+      </c>
+      <c r="X18" s="8" t="n">
+        <v>97.79729999999999</v>
+      </c>
+      <c r="Y18" s="8" t="n">
+        <v>95.68950000000001</v>
+      </c>
+      <c r="Z18" s="8" t="n">
+        <v>97.48750000000001</v>
+      </c>
+      <c r="AA18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="5" t="inlineStr">
+        <is>
+          <t>7:18:57.163600</t>
+        </is>
+      </c>
+      <c r="AD18" s="5" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD</t>
+        </is>
+      </c>
+      <c r="AE18" s="6" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/D1/CDD/steps_40000/seed_2333/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>RDT-CD</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>D1_RDT_CD_Full</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>mode=direction_c; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J19" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O19" s="7" t="n"/>
+      <c r="P19" s="7" t="n"/>
+      <c r="Q19" s="5" t="inlineStr">
+        <is>
+          <t>direction_c</t>
+        </is>
+      </c>
+      <c r="R19" s="8" t="n">
+        <v>2.9406</v>
+      </c>
+      <c r="S19" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v>90.00620000000001</v>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v>92.3428</v>
+      </c>
+      <c r="W19" s="8" t="n">
+        <v>99.11069999999999</v>
+      </c>
+      <c r="X19" s="8" t="n">
+        <v>91.15950000000001</v>
+      </c>
+      <c r="Y19" s="8" t="n">
+        <v>83.7552</v>
+      </c>
+      <c r="Z19" s="8" t="n">
+        <v>90.6914</v>
+      </c>
+      <c r="AA19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="5" t="inlineStr">
+        <is>
+          <t>5:24:02.165247</t>
+        </is>
+      </c>
+      <c r="AD19" s="5" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD</t>
+        </is>
+      </c>
+      <c r="AE19" s="6" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/D1/LEVIR/steps_40000/seed_2333/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>RDT-CD</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>D1_RDT_CD_Full</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>mode=direction_c; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J20" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L20" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O20" s="7" t="n"/>
+      <c r="P20" s="7" t="n"/>
+      <c r="Q20" s="5" t="inlineStr">
+        <is>
+          <t>direction_c</t>
+        </is>
+      </c>
+      <c r="R20" s="8" t="n">
+        <v>2.9406</v>
+      </c>
+      <c r="S20" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v>81.0399</v>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v>85.5491</v>
+      </c>
+      <c r="W20" s="8" t="n">
+        <v>92.30040000000001</v>
+      </c>
+      <c r="X20" s="8" t="n">
+        <v>83.2334</v>
+      </c>
+      <c r="Y20" s="8" t="n">
+        <v>71.28189999999999</v>
+      </c>
+      <c r="Z20" s="8" t="n">
+        <v>78.2409</v>
+      </c>
+      <c r="AA20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="5" t="inlineStr">
+        <is>
+          <t>6:55:31.918603</t>
+        </is>
+      </c>
+      <c r="AD20" s="5" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD</t>
+        </is>
+      </c>
+      <c r="AE20" s="6" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/D1/SYSU/steps_40000/seed_2333/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>RDT-CD</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>D1_RDT_CD_Full</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>mode=direction_c; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J21" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O21" s="7" t="n"/>
+      <c r="P21" s="7" t="n"/>
+      <c r="Q21" s="5" t="inlineStr">
+        <is>
+          <t>direction_c</t>
+        </is>
+      </c>
+      <c r="R21" s="8" t="n">
+        <v>2.9406</v>
+      </c>
+      <c r="S21" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v>93.253</v>
+      </c>
+      <c r="V21" s="8" t="n">
+        <v>95.1931</v>
+      </c>
+      <c r="W21" s="8" t="n">
+        <v>99.5455</v>
+      </c>
+      <c r="X21" s="8" t="n">
+        <v>94.21300000000001</v>
+      </c>
+      <c r="Y21" s="8" t="n">
+        <v>89.0592</v>
+      </c>
+      <c r="Z21" s="8" t="n">
+        <v>93.9765</v>
+      </c>
+      <c r="AA21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="5" t="inlineStr">
+        <is>
+          <t>4:12:06.381325</t>
+        </is>
+      </c>
+      <c r="AD21" s="5" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD</t>
+        </is>
+      </c>
+      <c r="AE21" s="6" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/D1/WHU/steps_40000/seed_2333/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>RDT-CD</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>D2_RDT_CD_NoCache</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>mode=direction_c; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J22" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L22" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O22" s="7" t="n"/>
+      <c r="P22" s="7" t="n"/>
+      <c r="Q22" s="5" t="inlineStr">
+        <is>
+          <t>direction_c</t>
+        </is>
+      </c>
+      <c r="R22" s="8" t="n">
+        <v>2.9406</v>
+      </c>
+      <c r="S22" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v>97.6968</v>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v>97.9029</v>
+      </c>
+      <c r="W22" s="8" t="n">
+        <v>99.45739999999999</v>
+      </c>
+      <c r="X22" s="8" t="n">
+        <v>97.7998</v>
+      </c>
+      <c r="Y22" s="8" t="n">
+        <v>95.6943</v>
+      </c>
+      <c r="Z22" s="8" t="n">
+        <v>97.49029999999999</v>
+      </c>
+      <c r="AA22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="5" t="inlineStr">
+        <is>
+          <t>7:17:26.882831</t>
+        </is>
+      </c>
+      <c r="AD22" s="5" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD</t>
+        </is>
+      </c>
+      <c r="AE22" s="6" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/D2/CDD/steps_40000/seed_2333/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>RDT-CD</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>D2_RDT_CD_NoCache</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>mode=direction_c; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J23" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O23" s="7" t="n"/>
+      <c r="P23" s="7" t="n"/>
+      <c r="Q23" s="5" t="inlineStr">
+        <is>
+          <t>direction_c</t>
+        </is>
+      </c>
+      <c r="R23" s="8" t="n">
+        <v>2.9406</v>
+      </c>
+      <c r="S23" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v>90.0788</v>
+      </c>
+      <c r="V23" s="8" t="n">
+        <v>92.26910000000001</v>
+      </c>
+      <c r="W23" s="8" t="n">
+        <v>99.1101</v>
+      </c>
+      <c r="X23" s="8" t="n">
+        <v>91.16079999999999</v>
+      </c>
+      <c r="Y23" s="8" t="n">
+        <v>83.7573</v>
+      </c>
+      <c r="Z23" s="8" t="n">
+        <v>90.6923</v>
+      </c>
+      <c r="AA23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="5" t="inlineStr">
+        <is>
+          <t>5:56:57.031072</t>
+        </is>
+      </c>
+      <c r="AD23" s="5" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD</t>
+        </is>
+      </c>
+      <c r="AE23" s="6" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/D2/LEVIR/steps_40000/seed_2333/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>RDT-CD</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>D2_RDT_CD_NoCache</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>mode=direction_c; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J24" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L24" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O24" s="7" t="n"/>
+      <c r="P24" s="7" t="n"/>
+      <c r="Q24" s="5" t="inlineStr">
+        <is>
+          <t>direction_c</t>
+        </is>
+      </c>
+      <c r="R24" s="8" t="n">
+        <v>2.9406</v>
+      </c>
+      <c r="S24" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v>79.52</v>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v>86.0012</v>
+      </c>
+      <c r="W24" s="8" t="n">
+        <v>92.1177</v>
+      </c>
+      <c r="X24" s="8" t="n">
+        <v>82.6337</v>
+      </c>
+      <c r="Y24" s="8" t="n">
+        <v>70.4067</v>
+      </c>
+      <c r="Z24" s="8" t="n">
+        <v>77.5457</v>
+      </c>
+      <c r="AA24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="5" t="inlineStr">
+        <is>
+          <t>6:39:38.461859</t>
+        </is>
+      </c>
+      <c r="AD24" s="5" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD</t>
+        </is>
+      </c>
+      <c r="AE24" s="6" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/D2/SYSU/steps_40000/seed_2333/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>RDT-CD</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>D2_RDT_CD_NoCache</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>mode=direction_c; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J25" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L25" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O25" s="7" t="n"/>
+      <c r="P25" s="7" t="n"/>
+      <c r="Q25" s="5" t="inlineStr">
+        <is>
+          <t>direction_c</t>
+        </is>
+      </c>
+      <c r="R25" s="8" t="n">
+        <v>2.9406</v>
+      </c>
+      <c r="S25" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v>92.12780000000001</v>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v>95.0633</v>
+      </c>
+      <c r="W25" s="8" t="n">
+        <v>99.4979</v>
+      </c>
+      <c r="X25" s="8" t="n">
+        <v>93.57259999999999</v>
+      </c>
+      <c r="Y25" s="8" t="n">
+        <v>87.92149999999999</v>
+      </c>
+      <c r="Z25" s="8" t="n">
+        <v>93.3113</v>
+      </c>
+      <c r="AA25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="5" t="inlineStr">
+        <is>
+          <t>4:54:24.014019</t>
+        </is>
+      </c>
+      <c r="AD25" s="5" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD</t>
+        </is>
+      </c>
+      <c r="AE25" s="6" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/D2/WHU/steps_40000/seed_2333/train_log.txt</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="X2:X13">
+  <conditionalFormatting sqref="X2:X25">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -2222,7 +3602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2451,6 +3831,210 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/B0/CDD/steps_40000/seed_2333/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/B0/LEVIR/steps_40000/seed_2333/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/B0/SYSU/steps_40000/seed_2333/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/B0/WHU/steps_40000/seed_2333/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/D1/CDD/steps_40000/seed_2333/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/D1/LEVIR/steps_40000/seed_2333/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/D1/SYSU/steps_40000/seed_2333/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/D1/WHU/steps_40000/seed_2333/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/D2/CDD/steps_40000/seed_2333/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/D2/LEVIR/steps_40000/seed_2333/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/D2/SYSU/steps_40000/seed_2333/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/D2/WHU/steps_40000/seed_2333/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -188,8 +188,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ExperimentResultsTable" displayName="ExperimentResultsTable" ref="A1:AE25" headerRowCount="1">
-  <autoFilter ref="A1:AE25"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ExperimentResultsTable" displayName="ExperimentResultsTable" ref="A1:AE36" headerRowCount="1">
+  <autoFilter ref="A1:AE36"/>
   <tableColumns count="31">
     <tableColumn id="1" name="Run"/>
     <tableColumn id="2" name="Stage"/>
@@ -538,7 +538,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15 08:57:47 +0800</t>
+          <t>2026-09-17 11:35:05 +0800</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8">
@@ -596,7 +596,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>DART-R=8, DART-R-TS=4, RDT-CD=12</t>
+          <t>DART-R=8, DART-R-TS=4, RDT-CD-Run1=12, RDT-CD-Run2=11</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>DART-R=C0 gradient routing (failed); DART-R-TS=C1 fixed teacher (failed, B0 only); RDT-CD=D1 dynamic teacher (B0/D1/D2). All 40k, seed 2333 — not a multi-seed paper result.</t>
+          <t>DART-R=C0 gradient routing (failed); DART-R-TS=C1 fixed teacher (failed, B0 only); RDT-CD-Run1=D1 dynamic teacher (B0/D1/D2); RDT-CD-Run2=SCGR (B0/D1NG/D1/D2, ineffective). All 40k, seed 2333 — not a multi-seed paper result.</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE25"/>
+  <dimension ref="A1:AE36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2199,7 +2199,7 @@
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>RDT-CD</t>
+          <t>RDT-CD-Run1</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -2302,19 +2302,19 @@
       </c>
       <c r="AD14" s="5" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD</t>
+          <t>outputs/RDT-CD/Run1</t>
         </is>
       </c>
       <c r="AE14" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/B0/CDD/steps_40000/seed_2333/train_log.txt</t>
+          <t>outputs/RDT-CD/Run1/B0/CDD/steps_40000/seed_2333/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>RDT-CD</t>
+          <t>RDT-CD-Run1</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -2417,19 +2417,19 @@
       </c>
       <c r="AD15" s="5" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD</t>
+          <t>outputs/RDT-CD/Run1</t>
         </is>
       </c>
       <c r="AE15" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/B0/LEVIR/steps_40000/seed_2333/train_log.txt</t>
+          <t>outputs/RDT-CD/Run1/B0/LEVIR/steps_40000/seed_2333/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>RDT-CD</t>
+          <t>RDT-CD-Run1</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -2532,19 +2532,19 @@
       </c>
       <c r="AD16" s="5" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD</t>
+          <t>outputs/RDT-CD/Run1</t>
         </is>
       </c>
       <c r="AE16" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/B0/SYSU/steps_40000/seed_2333/train_log.txt</t>
+          <t>outputs/RDT-CD/Run1/B0/SYSU/steps_40000/seed_2333/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>RDT-CD</t>
+          <t>RDT-CD-Run1</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -2647,19 +2647,19 @@
       </c>
       <c r="AD17" s="5" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD</t>
+          <t>outputs/RDT-CD/Run1</t>
         </is>
       </c>
       <c r="AE17" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/B0/WHU/steps_40000/seed_2333/train_log.txt</t>
+          <t>outputs/RDT-CD/Run1/B0/WHU/steps_40000/seed_2333/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>RDT-CD</t>
+          <t>RDT-CD-Run1</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -2762,19 +2762,19 @@
       </c>
       <c r="AD18" s="5" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD</t>
+          <t>outputs/RDT-CD/Run1</t>
         </is>
       </c>
       <c r="AE18" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/D1/CDD/steps_40000/seed_2333/train_log.txt</t>
+          <t>outputs/RDT-CD/Run1/D1/CDD/steps_40000/seed_2333/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>RDT-CD</t>
+          <t>RDT-CD-Run1</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -2877,19 +2877,19 @@
       </c>
       <c r="AD19" s="5" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD</t>
+          <t>outputs/RDT-CD/Run1</t>
         </is>
       </c>
       <c r="AE19" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/D1/LEVIR/steps_40000/seed_2333/train_log.txt</t>
+          <t>outputs/RDT-CD/Run1/D1/LEVIR/steps_40000/seed_2333/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>RDT-CD</t>
+          <t>RDT-CD-Run1</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -2992,19 +2992,19 @@
       </c>
       <c r="AD20" s="5" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD</t>
+          <t>outputs/RDT-CD/Run1</t>
         </is>
       </c>
       <c r="AE20" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/D1/SYSU/steps_40000/seed_2333/train_log.txt</t>
+          <t>outputs/RDT-CD/Run1/D1/SYSU/steps_40000/seed_2333/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>RDT-CD</t>
+          <t>RDT-CD-Run1</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -3107,19 +3107,19 @@
       </c>
       <c r="AD21" s="5" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD</t>
+          <t>outputs/RDT-CD/Run1</t>
         </is>
       </c>
       <c r="AE21" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/D1/WHU/steps_40000/seed_2333/train_log.txt</t>
+          <t>outputs/RDT-CD/Run1/D1/WHU/steps_40000/seed_2333/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>RDT-CD</t>
+          <t>RDT-CD-Run1</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -3222,19 +3222,19 @@
       </c>
       <c r="AD22" s="5" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD</t>
+          <t>outputs/RDT-CD/Run1</t>
         </is>
       </c>
       <c r="AE22" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/D2/CDD/steps_40000/seed_2333/train_log.txt</t>
+          <t>outputs/RDT-CD/Run1/D2/CDD/steps_40000/seed_2333/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>RDT-CD</t>
+          <t>RDT-CD-Run1</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -3337,19 +3337,19 @@
       </c>
       <c r="AD23" s="5" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD</t>
+          <t>outputs/RDT-CD/Run1</t>
         </is>
       </c>
       <c r="AE23" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/D2/LEVIR/steps_40000/seed_2333/train_log.txt</t>
+          <t>outputs/RDT-CD/Run1/D2/LEVIR/steps_40000/seed_2333/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>RDT-CD</t>
+          <t>RDT-CD-Run1</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -3452,19 +3452,19 @@
       </c>
       <c r="AD24" s="5" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD</t>
+          <t>outputs/RDT-CD/Run1</t>
         </is>
       </c>
       <c r="AE24" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/D2/SYSU/steps_40000/seed_2333/train_log.txt</t>
+          <t>outputs/RDT-CD/Run1/D2/SYSU/steps_40000/seed_2333/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>RDT-CD</t>
+          <t>RDT-CD-Run1</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -3567,17 +3567,1282 @@
       </c>
       <c r="AD25" s="5" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD</t>
+          <t>outputs/RDT-CD/Run1</t>
         </is>
       </c>
       <c r="AE25" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/D2/WHU/steps_40000/seed_2333/train_log.txt</t>
+          <t>outputs/RDT-CD/Run1/D2/WHU/steps_40000/seed_2333/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>RDT-CD-Run2</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>B0</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Baseline_A2Net_LWGANet_L0</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>mode=none; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J26" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L26" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O26" s="7" t="n"/>
+      <c r="P26" s="7" t="n"/>
+      <c r="Q26" s="5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R26" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S26" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v>97.70060000000001</v>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v>97.89489999999999</v>
+      </c>
+      <c r="W26" s="8" t="n">
+        <v>99.4568</v>
+      </c>
+      <c r="X26" s="8" t="n">
+        <v>97.79759999999999</v>
+      </c>
+      <c r="Y26" s="8" t="n">
+        <v>95.6902</v>
+      </c>
+      <c r="Z26" s="8" t="n">
+        <v>97.48790000000001</v>
+      </c>
+      <c r="AA26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="5" t="inlineStr">
+        <is>
+          <t>5:49:25.812505</t>
+        </is>
+      </c>
+      <c r="AD26" s="5" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2</t>
+        </is>
+      </c>
+      <c r="AE26" s="6" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2/B0/CDD/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>RDT-CD-Run2</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>B0</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Baseline_A2Net_LWGANet_L0</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>mode=none; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J27" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L27" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O27" s="7" t="n"/>
+      <c r="P27" s="7" t="n"/>
+      <c r="Q27" s="5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R27" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S27" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v>89.9204</v>
+      </c>
+      <c r="V27" s="8" t="n">
+        <v>92.0727</v>
+      </c>
+      <c r="W27" s="8" t="n">
+        <v>99.0921</v>
+      </c>
+      <c r="X27" s="8" t="n">
+        <v>90.9838</v>
+      </c>
+      <c r="Y27" s="8" t="n">
+        <v>83.459</v>
+      </c>
+      <c r="Z27" s="8" t="n">
+        <v>90.5059</v>
+      </c>
+      <c r="AA27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="5" t="inlineStr">
+        <is>
+          <t>7:30:54.783011</t>
+        </is>
+      </c>
+      <c r="AD27" s="5" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2</t>
+        </is>
+      </c>
+      <c r="AE27" s="6" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2/B0/LEVIR/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>RDT-CD-Run2</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>B0</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Baseline_A2Net_LWGANet_L0</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>mode=none; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J28" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L28" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O28" s="7" t="n"/>
+      <c r="P28" s="7" t="n"/>
+      <c r="Q28" s="5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R28" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S28" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v>80.76689999999999</v>
+      </c>
+      <c r="V28" s="8" t="n">
+        <v>85.8715</v>
+      </c>
+      <c r="W28" s="8" t="n">
+        <v>92.3305</v>
+      </c>
+      <c r="X28" s="8" t="n">
+        <v>83.241</v>
+      </c>
+      <c r="Y28" s="8" t="n">
+        <v>71.2931</v>
+      </c>
+      <c r="Z28" s="8" t="n">
+        <v>78.2745</v>
+      </c>
+      <c r="AA28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="5" t="inlineStr">
+        <is>
+          <t>3:44:43.745533</t>
+        </is>
+      </c>
+      <c r="AD28" s="5" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2</t>
+        </is>
+      </c>
+      <c r="AE28" s="6" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2/B0/SYSU/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>RDT-CD-Run2</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>B0</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Baseline_A2Net_LWGANet_L0</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>mode=none; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J29" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L29" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O29" s="7" t="n"/>
+      <c r="P29" s="7" t="n"/>
+      <c r="Q29" s="5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R29" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S29" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v>92.73</v>
+      </c>
+      <c r="V29" s="8" t="n">
+        <v>94.67</v>
+      </c>
+      <c r="W29" s="8" t="n">
+        <v>99.5044</v>
+      </c>
+      <c r="X29" s="8" t="n">
+        <v>93.69</v>
+      </c>
+      <c r="Y29" s="8" t="n">
+        <v>88.129</v>
+      </c>
+      <c r="Z29" s="8" t="n">
+        <v>93.43209999999999</v>
+      </c>
+      <c r="AA29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="5" t="inlineStr">
+        <is>
+          <t>5:47:21.732638</t>
+        </is>
+      </c>
+      <c r="AD29" s="5" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2</t>
+        </is>
+      </c>
+      <c r="AE29" s="6" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2/B0/WHU/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>RDT-CD-Run2</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>D1_RDT_SCGR_Full</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>mode=direction_c; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J30" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L30" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O30" s="7" t="n"/>
+      <c r="P30" s="7" t="n"/>
+      <c r="Q30" s="5" t="inlineStr">
+        <is>
+          <t>direction_c</t>
+        </is>
+      </c>
+      <c r="R30" s="8" t="n">
+        <v>2.9406</v>
+      </c>
+      <c r="S30" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v>97.78149999999999</v>
+      </c>
+      <c r="V30" s="8" t="n">
+        <v>97.7444</v>
+      </c>
+      <c r="W30" s="8" t="n">
+        <v>99.44760000000001</v>
+      </c>
+      <c r="X30" s="8" t="n">
+        <v>97.7629</v>
+      </c>
+      <c r="Y30" s="8" t="n">
+        <v>95.6238</v>
+      </c>
+      <c r="Z30" s="8" t="n">
+        <v>97.4479</v>
+      </c>
+      <c r="AA30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="5" t="inlineStr">
+        <is>
+          <t>8:16:12.117763</t>
+        </is>
+      </c>
+      <c r="AD30" s="5" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2</t>
+        </is>
+      </c>
+      <c r="AE30" s="6" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2/D1/CDD/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>RDT-CD-Run2</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>D1_RDT_SCGR_Full</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>mode=direction_c; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J31" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L31" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O31" s="7" t="n"/>
+      <c r="P31" s="7" t="n"/>
+      <c r="Q31" s="5" t="inlineStr">
+        <is>
+          <t>direction_c</t>
+        </is>
+      </c>
+      <c r="R31" s="8" t="n">
+        <v>2.9406</v>
+      </c>
+      <c r="S31" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v>89.17870000000001</v>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v>93.1447</v>
+      </c>
+      <c r="W31" s="8" t="n">
+        <v>99.1144</v>
+      </c>
+      <c r="X31" s="8" t="n">
+        <v>91.1186</v>
+      </c>
+      <c r="Y31" s="8" t="n">
+        <v>83.6861</v>
+      </c>
+      <c r="Z31" s="8" t="n">
+        <v>90.6528</v>
+      </c>
+      <c r="AA31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="5" t="inlineStr">
+        <is>
+          <t>5:12:10.074311</t>
+        </is>
+      </c>
+      <c r="AD31" s="5" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2</t>
+        </is>
+      </c>
+      <c r="AE31" s="6" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2/D1/LEVIR/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>RDT-CD-Run2</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>D1_RDT_SCGR_Full</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>mode=direction_c; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J32" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L32" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N32" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O32" s="7" t="n"/>
+      <c r="P32" s="7" t="n"/>
+      <c r="Q32" s="5" t="inlineStr">
+        <is>
+          <t>direction_c</t>
+        </is>
+      </c>
+      <c r="R32" s="8" t="n">
+        <v>2.9406</v>
+      </c>
+      <c r="S32" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v>78.9362</v>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v>86.7041</v>
+      </c>
+      <c r="W32" s="8" t="n">
+        <v>92.17790000000001</v>
+      </c>
+      <c r="X32" s="8" t="n">
+        <v>82.63800000000001</v>
+      </c>
+      <c r="Y32" s="8" t="n">
+        <v>70.413</v>
+      </c>
+      <c r="Z32" s="8" t="n">
+        <v>77.60420000000001</v>
+      </c>
+      <c r="AA32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="5" t="inlineStr">
+        <is>
+          <t>16:43:30.502484</t>
+        </is>
+      </c>
+      <c r="AD32" s="5" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2</t>
+        </is>
+      </c>
+      <c r="AE32" s="6" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2/D1/SYSU/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>RDT-CD-Run2</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>D1NG</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>D1NG_RDT_SCGR_NoGradGate</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>mode=direction_c; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J33" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L33" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O33" s="7" t="n"/>
+      <c r="P33" s="7" t="n"/>
+      <c r="Q33" s="5" t="inlineStr">
+        <is>
+          <t>direction_c</t>
+        </is>
+      </c>
+      <c r="R33" s="8" t="n">
+        <v>2.9406</v>
+      </c>
+      <c r="S33" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v>97.87439999999999</v>
+      </c>
+      <c r="V33" s="8" t="n">
+        <v>97.63030000000001</v>
+      </c>
+      <c r="W33" s="8" t="n">
+        <v>99.4444</v>
+      </c>
+      <c r="X33" s="8" t="n">
+        <v>97.7522</v>
+      </c>
+      <c r="Y33" s="8" t="n">
+        <v>95.6033</v>
+      </c>
+      <c r="Z33" s="8" t="n">
+        <v>97.4353</v>
+      </c>
+      <c r="AA33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="5" t="inlineStr">
+        <is>
+          <t>8:55:09.050631</t>
+        </is>
+      </c>
+      <c r="AD33" s="5" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2</t>
+        </is>
+      </c>
+      <c r="AE33" s="6" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2/D1NG/CDD/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>RDT-CD-Run2</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>D1NG</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>D1NG_RDT_SCGR_NoGradGate</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>mode=direction_c; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J34" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L34" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O34" s="7" t="n"/>
+      <c r="P34" s="7" t="n"/>
+      <c r="Q34" s="5" t="inlineStr">
+        <is>
+          <t>direction_c</t>
+        </is>
+      </c>
+      <c r="R34" s="8" t="n">
+        <v>2.9406</v>
+      </c>
+      <c r="S34" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v>90.3505</v>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="W34" s="8" t="n">
+        <v>99.0946</v>
+      </c>
+      <c r="X34" s="8" t="n">
+        <v>91.0449</v>
+      </c>
+      <c r="Y34" s="8" t="n">
+        <v>83.56179999999999</v>
+      </c>
+      <c r="Z34" s="8" t="n">
+        <v>90.5681</v>
+      </c>
+      <c r="AA34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="5" t="inlineStr">
+        <is>
+          <t>6:23:29.883230</t>
+        </is>
+      </c>
+      <c r="AD34" s="5" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2</t>
+        </is>
+      </c>
+      <c r="AE34" s="6" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2/D1NG/LEVIR/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>RDT-CD-Run2</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>D1NG</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>D1NG_RDT_SCGR_NoGradGate</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>mode=direction_c; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J35" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L35" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N35" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O35" s="7" t="n"/>
+      <c r="P35" s="7" t="n"/>
+      <c r="Q35" s="5" t="inlineStr">
+        <is>
+          <t>direction_c</t>
+        </is>
+      </c>
+      <c r="R35" s="8" t="n">
+        <v>2.9406</v>
+      </c>
+      <c r="S35" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v>80.45659999999999</v>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="W35" s="8" t="n">
+        <v>92.0454</v>
+      </c>
+      <c r="X35" s="8" t="n">
+        <v>82.6707</v>
+      </c>
+      <c r="Y35" s="8" t="n">
+        <v>70.46040000000001</v>
+      </c>
+      <c r="Z35" s="8" t="n">
+        <v>77.5137</v>
+      </c>
+      <c r="AA35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="5" t="inlineStr">
+        <is>
+          <t>8:17:02.482089</t>
+        </is>
+      </c>
+      <c r="AD35" s="5" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2</t>
+        </is>
+      </c>
+      <c r="AE35" s="6" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2/D1NG/SYSU/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>RDT-CD-Run2</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>D1NG</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>D1NG_RDT_SCGR_NoGradGate</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>mode=direction_c; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J36" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L36" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O36" s="7" t="n"/>
+      <c r="P36" s="7" t="n"/>
+      <c r="Q36" s="5" t="inlineStr">
+        <is>
+          <t>direction_c</t>
+        </is>
+      </c>
+      <c r="R36" s="8" t="n">
+        <v>2.9406</v>
+      </c>
+      <c r="S36" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v>91.36609999999999</v>
+      </c>
+      <c r="V36" s="8" t="n">
+        <v>94.0733</v>
+      </c>
+      <c r="W36" s="8" t="n">
+        <v>99.42910000000001</v>
+      </c>
+      <c r="X36" s="8" t="n">
+        <v>92.6999</v>
+      </c>
+      <c r="Y36" s="8" t="n">
+        <v>86.39320000000001</v>
+      </c>
+      <c r="Z36" s="8" t="n">
+        <v>92.4029</v>
+      </c>
+      <c r="AA36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="5" t="inlineStr">
+        <is>
+          <t>4:17:06.922035</t>
+        </is>
+      </c>
+      <c r="AD36" s="5" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2</t>
+        </is>
+      </c>
+      <c r="AE36" s="6" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2/D1NG/WHU/train_log.txt</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="X2:X25">
+  <conditionalFormatting sqref="X2:X36">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -3602,7 +4867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3834,12 +5099,12 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD</t>
+          <t>outputs/RDT-CD/Run1</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/B0/CDD/steps_40000/seed_2333/train_log.txt</t>
+          <t>outputs/RDT-CD/Run1/B0/CDD/steps_40000/seed_2333/train_log.txt</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
@@ -3851,12 +5116,12 @@
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD</t>
+          <t>outputs/RDT-CD/Run1</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/B0/LEVIR/steps_40000/seed_2333/train_log.txt</t>
+          <t>outputs/RDT-CD/Run1/B0/LEVIR/steps_40000/seed_2333/train_log.txt</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
@@ -3868,12 +5133,12 @@
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD</t>
+          <t>outputs/RDT-CD/Run1</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/B0/SYSU/steps_40000/seed_2333/train_log.txt</t>
+          <t>outputs/RDT-CD/Run1/B0/SYSU/steps_40000/seed_2333/train_log.txt</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
@@ -3885,12 +5150,12 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD</t>
+          <t>outputs/RDT-CD/Run1</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/B0/WHU/steps_40000/seed_2333/train_log.txt</t>
+          <t>outputs/RDT-CD/Run1/B0/WHU/steps_40000/seed_2333/train_log.txt</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
@@ -3902,12 +5167,12 @@
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD</t>
+          <t>outputs/RDT-CD/Run1</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/D1/CDD/steps_40000/seed_2333/train_log.txt</t>
+          <t>outputs/RDT-CD/Run1/D1/CDD/steps_40000/seed_2333/train_log.txt</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
@@ -3919,12 +5184,12 @@
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD</t>
+          <t>outputs/RDT-CD/Run1</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/D1/LEVIR/steps_40000/seed_2333/train_log.txt</t>
+          <t>outputs/RDT-CD/Run1/D1/LEVIR/steps_40000/seed_2333/train_log.txt</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
@@ -3936,12 +5201,12 @@
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD</t>
+          <t>outputs/RDT-CD/Run1</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/D1/SYSU/steps_40000/seed_2333/train_log.txt</t>
+          <t>outputs/RDT-CD/Run1/D1/SYSU/steps_40000/seed_2333/train_log.txt</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
@@ -3953,12 +5218,12 @@
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD</t>
+          <t>outputs/RDT-CD/Run1</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/D1/WHU/steps_40000/seed_2333/train_log.txt</t>
+          <t>outputs/RDT-CD/Run1/D1/WHU/steps_40000/seed_2333/train_log.txt</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
@@ -3970,12 +5235,12 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD</t>
+          <t>outputs/RDT-CD/Run1</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/D2/CDD/steps_40000/seed_2333/train_log.txt</t>
+          <t>outputs/RDT-CD/Run1/D2/CDD/steps_40000/seed_2333/train_log.txt</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
@@ -3987,12 +5252,12 @@
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD</t>
+          <t>outputs/RDT-CD/Run1</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/D2/LEVIR/steps_40000/seed_2333/train_log.txt</t>
+          <t>outputs/RDT-CD/Run1/D2/LEVIR/steps_40000/seed_2333/train_log.txt</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
@@ -4004,12 +5269,12 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD</t>
+          <t>outputs/RDT-CD/Run1</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/D2/SYSU/steps_40000/seed_2333/train_log.txt</t>
+          <t>outputs/RDT-CD/Run1/D2/SYSU/steps_40000/seed_2333/train_log.txt</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
@@ -4021,15 +5286,202 @@
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD</t>
+          <t>outputs/RDT-CD/Run1</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/D2/WHU/steps_40000/seed_2333/train_log.txt</t>
+          <t>outputs/RDT-CD/Run1/D2/WHU/steps_40000/seed_2333/train_log.txt</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2/B0/CDD/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2/B0/LEVIR/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2/B0/SYSU/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2/B0/WHU/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2/D1/CDD/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2/D1/LEVIR/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2/D1/SYSU/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2/D1NG/CDD/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2/D1NG/LEVIR/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2/D1NG/SYSU/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run2/D1NG/WHU/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
         <is>
           <t>complete</t>
         </is>

--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -188,8 +188,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ExperimentResultsTable" displayName="ExperimentResultsTable" ref="A1:AE36" headerRowCount="1">
-  <autoFilter ref="A1:AE36"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ExperimentResultsTable" displayName="ExperimentResultsTable" ref="A1:AE48" headerRowCount="1">
+  <autoFilter ref="A1:AE48"/>
   <tableColumns count="31">
     <tableColumn id="1" name="Run"/>
     <tableColumn id="2" name="Stage"/>
@@ -538,7 +538,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17 11:35:05 +0800</t>
+          <t>2026-09-19 12:29:07 +0800</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8">
@@ -596,7 +596,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>DART-R=8, DART-R-TS=4, RDT-CD-Run1=12, RDT-CD-Run2=11</t>
+          <t>DART-R=8, DART-R-TS=4, RDT-CD-Run1=12, RDT-CD-Run2=11, RDT-CD-Run3=12</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE36"/>
+  <dimension ref="A1:AE48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4841,8 +4841,1388 @@
         </is>
       </c>
     </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>RDT-CD-Run3</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>B0</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>B0_Clean_A2Net_LWGANet_L0</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>mode=none; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J37" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L37" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O37" s="7" t="n"/>
+      <c r="P37" s="7" t="n"/>
+      <c r="Q37" s="5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R37" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S37" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v>97.67400000000001</v>
+      </c>
+      <c r="V37" s="8" t="n">
+        <v>97.90870000000001</v>
+      </c>
+      <c r="W37" s="8" t="n">
+        <v>99.45540000000001</v>
+      </c>
+      <c r="X37" s="8" t="n">
+        <v>97.7912</v>
+      </c>
+      <c r="Y37" s="8" t="n">
+        <v>95.67790000000001</v>
+      </c>
+      <c r="Z37" s="8" t="n">
+        <v>97.4806</v>
+      </c>
+      <c r="AA37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="5" t="inlineStr">
+        <is>
+          <t>3:48:35.477713</t>
+        </is>
+      </c>
+      <c r="AD37" s="5" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3</t>
+        </is>
+      </c>
+      <c r="AE37" s="6" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3/B0/CDD/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>RDT-CD-Run3</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>B0</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>B0_Clean_A2Net_LWGANet_L0</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>mode=none; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J38" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L38" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M38" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N38" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O38" s="7" t="n"/>
+      <c r="P38" s="7" t="n"/>
+      <c r="Q38" s="5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R38" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S38" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v>89.3151</v>
+      </c>
+      <c r="V38" s="8" t="n">
+        <v>93.02679999999999</v>
+      </c>
+      <c r="W38" s="8" t="n">
+        <v>99.1146</v>
+      </c>
+      <c r="X38" s="8" t="n">
+        <v>91.1332</v>
+      </c>
+      <c r="Y38" s="8" t="n">
+        <v>83.7107</v>
+      </c>
+      <c r="Z38" s="8" t="n">
+        <v>90.6674</v>
+      </c>
+      <c r="AA38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="5" t="inlineStr">
+        <is>
+          <t>3:13:21.820469</t>
+        </is>
+      </c>
+      <c r="AD38" s="5" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3</t>
+        </is>
+      </c>
+      <c r="AE38" s="6" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3/B0/LEVIR/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>RDT-CD-Run3</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>B0</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>B0_Clean_A2Net_LWGANet_L0</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>mode=none; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J39" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L39" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N39" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O39" s="7" t="n"/>
+      <c r="P39" s="7" t="n"/>
+      <c r="Q39" s="5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R39" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S39" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v>77.89570000000001</v>
+      </c>
+      <c r="V39" s="8" t="n">
+        <v>85.99719999999999</v>
+      </c>
+      <c r="W39" s="8" t="n">
+        <v>91.79600000000001</v>
+      </c>
+      <c r="X39" s="8" t="n">
+        <v>81.7462</v>
+      </c>
+      <c r="Y39" s="8" t="n">
+        <v>69.12779999999999</v>
+      </c>
+      <c r="Z39" s="8" t="n">
+        <v>76.47190000000001</v>
+      </c>
+      <c r="AA39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="5" t="inlineStr">
+        <is>
+          <t>4:06:14.223274</t>
+        </is>
+      </c>
+      <c r="AD39" s="5" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3</t>
+        </is>
+      </c>
+      <c r="AE39" s="6" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3/B0/SYSU/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>RDT-CD-Run3</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>B0</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>B0_Clean_A2Net_LWGANet_L0</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>mode=none; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J40" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L40" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M40" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N40" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O40" s="7" t="n"/>
+      <c r="P40" s="7" t="n"/>
+      <c r="Q40" s="5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R40" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S40" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v>92.7808</v>
+      </c>
+      <c r="V40" s="8" t="n">
+        <v>95.3728</v>
+      </c>
+      <c r="W40" s="8" t="n">
+        <v>99.535</v>
+      </c>
+      <c r="X40" s="8" t="n">
+        <v>94.059</v>
+      </c>
+      <c r="Y40" s="8" t="n">
+        <v>88.7842</v>
+      </c>
+      <c r="Z40" s="8" t="n">
+        <v>93.81699999999999</v>
+      </c>
+      <c r="AA40" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" s="5" t="inlineStr">
+        <is>
+          <t>3:15:04.521316</t>
+        </is>
+      </c>
+      <c r="AD40" s="5" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3</t>
+        </is>
+      </c>
+      <c r="AE40" s="6" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3/B0/WHU/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>RDT-CD-Run3</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>R3_BT_SAM_RDT_Full</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>mode=bt_sam_rdt; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J41" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L41" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N41" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O41" s="7" t="n"/>
+      <c r="P41" s="7" t="n"/>
+      <c r="Q41" s="5" t="inlineStr">
+        <is>
+          <t>bt_sam_rdt</t>
+        </is>
+      </c>
+      <c r="R41" s="8" t="n">
+        <v>2.9269</v>
+      </c>
+      <c r="S41" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v>97.6738</v>
+      </c>
+      <c r="V41" s="8" t="n">
+        <v>97.91459999999999</v>
+      </c>
+      <c r="W41" s="8" t="n">
+        <v>99.45610000000001</v>
+      </c>
+      <c r="X41" s="8" t="n">
+        <v>97.794</v>
+      </c>
+      <c r="Y41" s="8" t="n">
+        <v>95.6833</v>
+      </c>
+      <c r="Z41" s="8" t="n">
+        <v>97.4838</v>
+      </c>
+      <c r="AA41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="5" t="inlineStr">
+        <is>
+          <t>11:08:17.035446</t>
+        </is>
+      </c>
+      <c r="AD41" s="5" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3</t>
+        </is>
+      </c>
+      <c r="AE41" s="6" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3/R3/CDD/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>RDT-CD-Run3</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>R3_BT_SAM_RDT_Full</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>mode=bt_sam_rdt; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J42" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L42" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M42" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N42" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O42" s="7" t="n"/>
+      <c r="P42" s="7" t="n"/>
+      <c r="Q42" s="5" t="inlineStr">
+        <is>
+          <t>bt_sam_rdt</t>
+        </is>
+      </c>
+      <c r="R42" s="8" t="n">
+        <v>2.9269</v>
+      </c>
+      <c r="S42" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v>89.21550000000001</v>
+      </c>
+      <c r="V42" s="8" t="n">
+        <v>92.8203</v>
+      </c>
+      <c r="W42" s="8" t="n">
+        <v>99.09909999999999</v>
+      </c>
+      <c r="X42" s="8" t="n">
+        <v>90.98220000000001</v>
+      </c>
+      <c r="Y42" s="8" t="n">
+        <v>83.4564</v>
+      </c>
+      <c r="Z42" s="8" t="n">
+        <v>90.50829999999999</v>
+      </c>
+      <c r="AA42" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="5" t="inlineStr">
+        <is>
+          <t>5:19:09.846917</t>
+        </is>
+      </c>
+      <c r="AD42" s="5" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3</t>
+        </is>
+      </c>
+      <c r="AE42" s="6" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3/R3/LEVIR/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>RDT-CD-Run3</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>R3_BT_SAM_RDT_Full</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>mode=bt_sam_rdt; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J43" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L43" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M43" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N43" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O43" s="7" t="n"/>
+      <c r="P43" s="7" t="n"/>
+      <c r="Q43" s="5" t="inlineStr">
+        <is>
+          <t>bt_sam_rdt</t>
+        </is>
+      </c>
+      <c r="R43" s="8" t="n">
+        <v>2.9269</v>
+      </c>
+      <c r="S43" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v>81.1455</v>
+      </c>
+      <c r="V43" s="8" t="n">
+        <v>85.2085</v>
+      </c>
+      <c r="W43" s="8" t="n">
+        <v>92.2317</v>
+      </c>
+      <c r="X43" s="8" t="n">
+        <v>83.12739999999999</v>
+      </c>
+      <c r="Y43" s="8" t="n">
+        <v>71.12650000000001</v>
+      </c>
+      <c r="Z43" s="8" t="n">
+        <v>78.0856</v>
+      </c>
+      <c r="AA43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="5" t="inlineStr">
+        <is>
+          <t>10:47:31.810425</t>
+        </is>
+      </c>
+      <c r="AD43" s="5" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3</t>
+        </is>
+      </c>
+      <c r="AE43" s="6" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3/R3/SYSU/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>RDT-CD-Run3</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>R3_BT_SAM_RDT_Full</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>mode=bt_sam_rdt; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J44" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L44" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M44" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N44" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O44" s="7" t="n"/>
+      <c r="P44" s="7" t="n"/>
+      <c r="Q44" s="5" t="inlineStr">
+        <is>
+          <t>bt_sam_rdt</t>
+        </is>
+      </c>
+      <c r="R44" s="8" t="n">
+        <v>2.9269</v>
+      </c>
+      <c r="S44" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v>93.0294</v>
+      </c>
+      <c r="V44" s="8" t="n">
+        <v>94.3871</v>
+      </c>
+      <c r="W44" s="8" t="n">
+        <v>99.5039</v>
+      </c>
+      <c r="X44" s="8" t="n">
+        <v>93.7033</v>
+      </c>
+      <c r="Y44" s="8" t="n">
+        <v>88.1527</v>
+      </c>
+      <c r="Z44" s="8" t="n">
+        <v>93.4452</v>
+      </c>
+      <c r="AA44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="5" t="inlineStr">
+        <is>
+          <t>4:27:10.216507</t>
+        </is>
+      </c>
+      <c r="AD44" s="5" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3</t>
+        </is>
+      </c>
+      <c r="AE44" s="6" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3/R3/WHU/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>RDT-CD-Run3</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>R3A</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>R3A_BT_SAM_RDT_SAM_Only</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>mode=bt_sam_rdt; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J45" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L45" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M45" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N45" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O45" s="7" t="n"/>
+      <c r="P45" s="7" t="n"/>
+      <c r="Q45" s="5" t="inlineStr">
+        <is>
+          <t>bt_sam_rdt</t>
+        </is>
+      </c>
+      <c r="R45" s="8" t="n">
+        <v>2.9269</v>
+      </c>
+      <c r="S45" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v>97.7008</v>
+      </c>
+      <c r="V45" s="8" t="n">
+        <v>97.858</v>
+      </c>
+      <c r="W45" s="8" t="n">
+        <v>99.4522</v>
+      </c>
+      <c r="X45" s="8" t="n">
+        <v>97.77930000000001</v>
+      </c>
+      <c r="Y45" s="8" t="n">
+        <v>95.65519999999999</v>
+      </c>
+      <c r="Z45" s="8" t="n">
+        <v>97.4669</v>
+      </c>
+      <c r="AA45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="5" t="inlineStr">
+        <is>
+          <t>11:25:23.866980</t>
+        </is>
+      </c>
+      <c r="AD45" s="5" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3</t>
+        </is>
+      </c>
+      <c r="AE45" s="6" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3/R3A/CDD/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>RDT-CD-Run3</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>R3A</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>R3A_BT_SAM_RDT_SAM_Only</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>mode=bt_sam_rdt; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J46" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L46" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M46" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N46" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O46" s="7" t="n"/>
+      <c r="P46" s="7" t="n"/>
+      <c r="Q46" s="5" t="inlineStr">
+        <is>
+          <t>bt_sam_rdt</t>
+        </is>
+      </c>
+      <c r="R46" s="8" t="n">
+        <v>2.9269</v>
+      </c>
+      <c r="S46" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v>90.7855</v>
+      </c>
+      <c r="V46" s="8" t="n">
+        <v>91.2675</v>
+      </c>
+      <c r="W46" s="8" t="n">
+        <v>99.0881</v>
+      </c>
+      <c r="X46" s="8" t="n">
+        <v>91.0258</v>
+      </c>
+      <c r="Y46" s="8" t="n">
+        <v>83.52979999999999</v>
+      </c>
+      <c r="Z46" s="8" t="n">
+        <v>90.5455</v>
+      </c>
+      <c r="AA46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC46" s="5" t="inlineStr">
+        <is>
+          <t>5:37:16.217701</t>
+        </is>
+      </c>
+      <c r="AD46" s="5" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3</t>
+        </is>
+      </c>
+      <c r="AE46" s="6" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3/R3A/LEVIR/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>RDT-CD-Run3</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>R3A</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>R3A_BT_SAM_RDT_SAM_Only</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>mode=bt_sam_rdt; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J47" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L47" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M47" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N47" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O47" s="7" t="n"/>
+      <c r="P47" s="7" t="n"/>
+      <c r="Q47" s="5" t="inlineStr">
+        <is>
+          <t>bt_sam_rdt</t>
+        </is>
+      </c>
+      <c r="R47" s="8" t="n">
+        <v>2.9269</v>
+      </c>
+      <c r="S47" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v>77.91940000000001</v>
+      </c>
+      <c r="V47" s="8" t="n">
+        <v>87.1811</v>
+      </c>
+      <c r="W47" s="8" t="n">
+        <v>92.0909</v>
+      </c>
+      <c r="X47" s="8" t="n">
+        <v>82.29049999999999</v>
+      </c>
+      <c r="Y47" s="8" t="n">
+        <v>69.9098</v>
+      </c>
+      <c r="Z47" s="8" t="n">
+        <v>77.2196</v>
+      </c>
+      <c r="AA47" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="5" t="inlineStr">
+        <is>
+          <t>10:51:06.656145</t>
+        </is>
+      </c>
+      <c r="AD47" s="5" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3</t>
+        </is>
+      </c>
+      <c r="AE47" s="6" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3/R3A/SYSU/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>RDT-CD-Run3</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>R3A</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>R3A_BT_SAM_RDT_SAM_Only</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>mode=bt_sam_rdt; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J48" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L48" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M48" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N48" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O48" s="7" t="n"/>
+      <c r="P48" s="7" t="n"/>
+      <c r="Q48" s="5" t="inlineStr">
+        <is>
+          <t>bt_sam_rdt</t>
+        </is>
+      </c>
+      <c r="R48" s="8" t="n">
+        <v>2.9269</v>
+      </c>
+      <c r="S48" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v>93.08840000000001</v>
+      </c>
+      <c r="V48" s="8" t="n">
+        <v>94.8141</v>
+      </c>
+      <c r="W48" s="8" t="n">
+        <v>99.52379999999999</v>
+      </c>
+      <c r="X48" s="8" t="n">
+        <v>93.94329999999999</v>
+      </c>
+      <c r="Y48" s="8" t="n">
+        <v>88.5784</v>
+      </c>
+      <c r="Z48" s="8" t="n">
+        <v>93.6955</v>
+      </c>
+      <c r="AA48" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" s="5" t="inlineStr">
+        <is>
+          <t>4:29:12.633871</t>
+        </is>
+      </c>
+      <c r="AD48" s="5" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3</t>
+        </is>
+      </c>
+      <c r="AE48" s="6" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3/R3A/WHU/train_log.txt</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="X2:X36">
+  <conditionalFormatting sqref="X2:X48">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -4867,7 +6247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -5487,6 +6867,210 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3/B0/CDD/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3/B0/LEVIR/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3/B0/SYSU/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3/B0/WHU/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3/R3/CDD/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3/R3/LEVIR/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3/R3/SYSU/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3/R3/WHU/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3/R3A/CDD/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3/R3A/LEVIR/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3/R3A/SYSU/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3/R3A/WHU/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -188,8 +188,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ExperimentResultsTable" displayName="ExperimentResultsTable" ref="A1:AE48" headerRowCount="1">
-  <autoFilter ref="A1:AE48"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ExperimentResultsTable" displayName="ExperimentResultsTable" ref="A1:AE50" headerRowCount="1">
+  <autoFilter ref="A1:AE50"/>
   <tableColumns count="31">
     <tableColumn id="1" name="Run"/>
     <tableColumn id="2" name="Stage"/>
@@ -538,7 +538,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 12:29:07 +0800</t>
+          <t>2026-09-20 07:54:56 +0800</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8">
@@ -596,7 +596,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>DART-R=8, DART-R-TS=4, RDT-CD-Run1=12, RDT-CD-Run2=11, RDT-CD-Run3=12</t>
+          <t>DART-R=8, DART-R-TS=4, RDT-CD-Run1=12, RDT-CD-Run2=11, RDT-CD-Run3=14</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE48"/>
+  <dimension ref="A1:AE50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6221,8 +6221,238 @@
         </is>
       </c>
     </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>RDT-CD-Run3</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>R3O</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>R3O_BT_SAM_RDT_OV_Only</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>mode=bt_sam_rdt; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J49" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L49" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M49" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N49" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O49" s="7" t="n"/>
+      <c r="P49" s="7" t="n"/>
+      <c r="Q49" s="5" t="inlineStr">
+        <is>
+          <t>bt_sam_rdt</t>
+        </is>
+      </c>
+      <c r="R49" s="8" t="n">
+        <v>2.9269</v>
+      </c>
+      <c r="S49" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v>79.3635</v>
+      </c>
+      <c r="V49" s="8" t="n">
+        <v>86.4628</v>
+      </c>
+      <c r="W49" s="8" t="n">
+        <v>92.203</v>
+      </c>
+      <c r="X49" s="8" t="n">
+        <v>82.7612</v>
+      </c>
+      <c r="Y49" s="8" t="n">
+        <v>70.592</v>
+      </c>
+      <c r="Z49" s="8" t="n">
+        <v>77.7353</v>
+      </c>
+      <c r="AA49" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB49" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="5" t="inlineStr">
+        <is>
+          <t>7:05:18.102962</t>
+        </is>
+      </c>
+      <c r="AD49" s="5" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3</t>
+        </is>
+      </c>
+      <c r="AE49" s="6" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3/R3O/SYSU/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>RDT-CD-Run3</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>R3O</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>R3O_BT_SAM_RDT_OV_Only</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>mode=bt_sam_rdt; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J50" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L50" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M50" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N50" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O50" s="7" t="n"/>
+      <c r="P50" s="7" t="n"/>
+      <c r="Q50" s="5" t="inlineStr">
+        <is>
+          <t>bt_sam_rdt</t>
+        </is>
+      </c>
+      <c r="R50" s="8" t="n">
+        <v>2.9269</v>
+      </c>
+      <c r="S50" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v>91.0621</v>
+      </c>
+      <c r="V50" s="8" t="n">
+        <v>95.70359999999999</v>
+      </c>
+      <c r="W50" s="8" t="n">
+        <v>99.48320000000001</v>
+      </c>
+      <c r="X50" s="8" t="n">
+        <v>93.3252</v>
+      </c>
+      <c r="Y50" s="8" t="n">
+        <v>87.48559999999999</v>
+      </c>
+      <c r="Z50" s="8" t="n">
+        <v>93.0565</v>
+      </c>
+      <c r="AA50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="5" t="inlineStr">
+        <is>
+          <t>3:37:24.949796</t>
+        </is>
+      </c>
+      <c r="AD50" s="5" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3</t>
+        </is>
+      </c>
+      <c r="AE50" s="6" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3/R3O/WHU/train_log.txt</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="X2:X48">
+  <conditionalFormatting sqref="X2:X50">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -6247,7 +6477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -7071,6 +7301,40 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3/R3O/SYSU/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C49" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t>outputs/RDT-CD/Run3/R3O/WHU/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -188,8 +188,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ExperimentResultsTable" displayName="ExperimentResultsTable" ref="A1:AE50" headerRowCount="1">
-  <autoFilter ref="A1:AE50"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ExperimentResultsTable" displayName="ExperimentResultsTable" ref="A1:AE62" headerRowCount="1">
+  <autoFilter ref="A1:AE62"/>
   <tableColumns count="31">
     <tableColumn id="1" name="Run"/>
     <tableColumn id="2" name="Stage"/>
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>LS-Rep_BCD_RSML_3 — Experiment Metrics (DART-R / RDT-CD)</t>
+          <t>LS-Rep_BCD_RSML_3 — Experiment Metrics (DART-R / RDT-CD / SCTC)</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20 07:54:56 +0800</t>
+          <t>2026-09-21 10:26:53 +0800</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>outputs/DirectionC (DART-R) + outputs/DART-R-TS + outputs/RDT-CD; launcher logs excluded</t>
+          <t>outputs/DirectionC (DART-R) + outputs/DART-R-TS + outputs/RDT-CD + outputs/SCTC; launcher logs excluded</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8">
@@ -596,7 +596,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>DART-R=8, DART-R-TS=4, RDT-CD-Run1=12, RDT-CD-Run2=11, RDT-CD-Run3=14</t>
+          <t>DART-R=8, DART-R-TS=4, RDT-CD-Run1=12, RDT-CD-Run2=11, RDT-CD-Run3=14, SCTC-Run1=12</t>
         </is>
       </c>
     </row>
@@ -609,6 +609,18 @@
       <c r="B9" s="3" t="inlineStr">
         <is>
           <t>DART-R=C0 gradient routing (failed); DART-R-TS=C1 fixed teacher (failed, B0 only); RDT-CD-Run1=D1 dynamic teacher (B0/D1/D2); RDT-CD-Run2=SCGR (B0/D1NG/D1/D2, ineffective). All 40k, seed 2333 — not a multi-seed paper result.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>SCTC scope</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>SCTC-Run1: S0=clean A2Net, S1=full-pixel symmetric calibration, S2=unchanged-aware SCTC. S2-S0 = WHU +0.43 / SYSU -0.25 / CDD -0.20 / LEVIR -0.10 → WHU-only single-dataset trick, H4 failed. 40k, seed 2333 only.</t>
         </is>
       </c>
     </row>
@@ -623,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE50"/>
+  <dimension ref="A1:AE62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6451,8 +6463,1316 @@
         </is>
       </c>
     </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>SCTC-Run1</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>S0</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>S0_Clean_A2Net_LWGANet_L0</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=none</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J51" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L51" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M51" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N51" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O51" s="7" t="n"/>
+      <c r="P51" s="7" t="n"/>
+      <c r="Q51" s="5" t="n"/>
+      <c r="R51" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S51" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v>97.68770000000001</v>
+      </c>
+      <c r="V51" s="8" t="n">
+        <v>97.8814</v>
+      </c>
+      <c r="W51" s="8" t="n">
+        <v>99.45359999999999</v>
+      </c>
+      <c r="X51" s="8" t="n">
+        <v>97.78449999999999</v>
+      </c>
+      <c r="Y51" s="8" t="n">
+        <v>95.66500000000001</v>
+      </c>
+      <c r="Z51" s="8" t="n">
+        <v>97.47280000000001</v>
+      </c>
+      <c r="AA51" s="9" t="n"/>
+      <c r="AB51" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="5" t="inlineStr">
+        <is>
+          <t>3:42:46.634404</t>
+        </is>
+      </c>
+      <c r="AD51" s="5" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="AE51" s="6" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S0/CDD/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>SCTC-Run1</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>S0</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>S0_Clean_A2Net_LWGANet_L0</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=none</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J52" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L52" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M52" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N52" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O52" s="7" t="n"/>
+      <c r="P52" s="7" t="n"/>
+      <c r="Q52" s="5" t="n"/>
+      <c r="R52" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S52" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v>89.4019</v>
+      </c>
+      <c r="V52" s="8" t="n">
+        <v>92.447</v>
+      </c>
+      <c r="W52" s="8" t="n">
+        <v>99.08799999999999</v>
+      </c>
+      <c r="X52" s="8" t="n">
+        <v>90.8989</v>
+      </c>
+      <c r="Y52" s="8" t="n">
+        <v>83.3163</v>
+      </c>
+      <c r="Z52" s="8" t="n">
+        <v>90.41900000000001</v>
+      </c>
+      <c r="AA52" s="9" t="n"/>
+      <c r="AB52" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="5" t="inlineStr">
+        <is>
+          <t>2:47:14.389924</t>
+        </is>
+      </c>
+      <c r="AD52" s="5" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="AE52" s="6" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S0/LEVIR/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>SCTC-Run1</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>S0</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>S0_Clean_A2Net_LWGANet_L0</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=none</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J53" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L53" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M53" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N53" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O53" s="7" t="n"/>
+      <c r="P53" s="7" t="n"/>
+      <c r="Q53" s="5" t="n"/>
+      <c r="R53" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S53" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v>81.14139999999999</v>
+      </c>
+      <c r="V53" s="8" t="n">
+        <v>84.9704</v>
+      </c>
+      <c r="W53" s="8" t="n">
+        <v>92.1679</v>
+      </c>
+      <c r="X53" s="8" t="n">
+        <v>83.01180000000001</v>
+      </c>
+      <c r="Y53" s="8" t="n">
+        <v>70.9573</v>
+      </c>
+      <c r="Z53" s="8" t="n">
+        <v>77.92609999999999</v>
+      </c>
+      <c r="AA53" s="9" t="n"/>
+      <c r="AB53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="5" t="inlineStr">
+        <is>
+          <t>2:20:47.929272</t>
+        </is>
+      </c>
+      <c r="AD53" s="5" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="AE53" s="6" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S0/SYSU/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>SCTC-Run1</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>S0</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>S0_Clean_A2Net_LWGANet_L0</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=none</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J54" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K54" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L54" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M54" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N54" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O54" s="7" t="n"/>
+      <c r="P54" s="7" t="n"/>
+      <c r="Q54" s="5" t="n"/>
+      <c r="R54" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S54" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U54" s="8" t="n">
+        <v>91.9434</v>
+      </c>
+      <c r="V54" s="8" t="n">
+        <v>95.20650000000001</v>
+      </c>
+      <c r="W54" s="8" t="n">
+        <v>99.4967</v>
+      </c>
+      <c r="X54" s="8" t="n">
+        <v>93.54649999999999</v>
+      </c>
+      <c r="Y54" s="8" t="n">
+        <v>87.87549999999999</v>
+      </c>
+      <c r="Z54" s="8" t="n">
+        <v>93.2847</v>
+      </c>
+      <c r="AA54" s="9" t="n"/>
+      <c r="AB54" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" s="5" t="inlineStr">
+        <is>
+          <t>2:43:01.630317</t>
+        </is>
+      </c>
+      <c r="AD54" s="5" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="AE54" s="6" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S0/WHU/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>SCTC-Run1</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>S1_FullPixel_Symmetric_Calibration</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=symmetric</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J55" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L55" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M55" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N55" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O55" s="7" t="n"/>
+      <c r="P55" s="7" t="n"/>
+      <c r="Q55" s="5" t="n"/>
+      <c r="R55" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S55" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v>97.39619999999999</v>
+      </c>
+      <c r="V55" s="8" t="n">
+        <v>97.7011</v>
+      </c>
+      <c r="W55" s="8" t="n">
+        <v>99.39570000000001</v>
+      </c>
+      <c r="X55" s="8" t="n">
+        <v>97.5484</v>
+      </c>
+      <c r="Y55" s="8" t="n">
+        <v>95.21420000000001</v>
+      </c>
+      <c r="Z55" s="8" t="n">
+        <v>97.2038</v>
+      </c>
+      <c r="AA55" s="9" t="n"/>
+      <c r="AB55" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC55" s="5" t="inlineStr">
+        <is>
+          <t>3:19:01.505607</t>
+        </is>
+      </c>
+      <c r="AD55" s="5" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="AE55" s="6" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S1/CDD/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="30" customHeight="1">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>SCTC-Run1</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>S1_FullPixel_Symmetric_Calibration</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=symmetric</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J56" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K56" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L56" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M56" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N56" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O56" s="7" t="n"/>
+      <c r="P56" s="7" t="n"/>
+      <c r="Q56" s="5" t="n"/>
+      <c r="R56" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S56" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U56" s="8" t="n">
+        <v>89.7944</v>
+      </c>
+      <c r="V56" s="8" t="n">
+        <v>92.1617</v>
+      </c>
+      <c r="W56" s="8" t="n">
+        <v>99.0911</v>
+      </c>
+      <c r="X56" s="8" t="n">
+        <v>90.96260000000001</v>
+      </c>
+      <c r="Y56" s="8" t="n">
+        <v>83.4233</v>
+      </c>
+      <c r="Z56" s="8" t="n">
+        <v>90.4842</v>
+      </c>
+      <c r="AA56" s="9" t="n"/>
+      <c r="AB56" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC56" s="5" t="inlineStr">
+        <is>
+          <t>0:33:15.349976</t>
+        </is>
+      </c>
+      <c r="AD56" s="5" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="AE56" s="6" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S1/LEVIR/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>SCTC-Run1</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>S1_FullPixel_Symmetric_Calibration</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=symmetric</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J57" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L57" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M57" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N57" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O57" s="7" t="n"/>
+      <c r="P57" s="7" t="n"/>
+      <c r="Q57" s="5" t="n"/>
+      <c r="R57" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S57" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v>80.42610000000001</v>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v>85.6097</v>
+      </c>
+      <c r="W57" s="8" t="n">
+        <v>92.19580000000001</v>
+      </c>
+      <c r="X57" s="8" t="n">
+        <v>82.93700000000001</v>
+      </c>
+      <c r="Y57" s="8" t="n">
+        <v>70.8481</v>
+      </c>
+      <c r="Z57" s="8" t="n">
+        <v>77.8843</v>
+      </c>
+      <c r="AA57" s="9" t="n"/>
+      <c r="AB57" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC57" s="5" t="inlineStr">
+        <is>
+          <t>3:32:56.072083</t>
+        </is>
+      </c>
+      <c r="AD57" s="5" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="AE57" s="6" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S1/SYSU/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>SCTC-Run1</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>S1_FullPixel_Symmetric_Calibration</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=symmetric</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J58" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K58" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L58" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M58" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N58" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O58" s="7" t="n"/>
+      <c r="P58" s="7" t="n"/>
+      <c r="Q58" s="5" t="n"/>
+      <c r="R58" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S58" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v>92.1589</v>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v>95.1091</v>
+      </c>
+      <c r="W58" s="8" t="n">
+        <v>99.5009</v>
+      </c>
+      <c r="X58" s="8" t="n">
+        <v>93.61070000000001</v>
+      </c>
+      <c r="Y58" s="8" t="n">
+        <v>87.9889</v>
+      </c>
+      <c r="Z58" s="8" t="n">
+        <v>93.3511</v>
+      </c>
+      <c r="AA58" s="9" t="n"/>
+      <c r="AB58" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="5" t="inlineStr">
+        <is>
+          <t>2:40:44.864364</t>
+        </is>
+      </c>
+      <c r="AD58" s="5" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="AE58" s="6" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S1/WHU/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>SCTC-Run1</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>S2_SCTC_UnchangedAware_Symmetric_CrossTemporal_Calibration</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=sctc</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I59" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J59" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L59" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M59" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N59" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O59" s="7" t="n"/>
+      <c r="P59" s="7" t="n"/>
+      <c r="Q59" s="5" t="n"/>
+      <c r="R59" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S59" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U59" s="8" t="n">
+        <v>97.4438</v>
+      </c>
+      <c r="V59" s="8" t="n">
+        <v>97.71940000000001</v>
+      </c>
+      <c r="W59" s="8" t="n">
+        <v>99.4038</v>
+      </c>
+      <c r="X59" s="8" t="n">
+        <v>97.5814</v>
+      </c>
+      <c r="Y59" s="8" t="n">
+        <v>95.277</v>
+      </c>
+      <c r="Z59" s="8" t="n">
+        <v>97.2414</v>
+      </c>
+      <c r="AA59" s="9" t="n"/>
+      <c r="AB59" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC59" s="5" t="inlineStr">
+        <is>
+          <t>2:52:30.285254</t>
+        </is>
+      </c>
+      <c r="AD59" s="5" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="AE59" s="6" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S2/CDD/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>SCTC-Run1</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>S2_SCTC_UnchangedAware_Symmetric_CrossTemporal_Calibration</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=sctc</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H60" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J60" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K60" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L60" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M60" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N60" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O60" s="7" t="n"/>
+      <c r="P60" s="7" t="n"/>
+      <c r="Q60" s="5" t="n"/>
+      <c r="R60" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S60" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U60" s="8" t="n">
+        <v>90.1421</v>
+      </c>
+      <c r="V60" s="8" t="n">
+        <v>91.4601</v>
+      </c>
+      <c r="W60" s="8" t="n">
+        <v>99.069</v>
+      </c>
+      <c r="X60" s="8" t="n">
+        <v>90.7963</v>
+      </c>
+      <c r="Y60" s="8" t="n">
+        <v>83.14399999999999</v>
+      </c>
+      <c r="Z60" s="8" t="n">
+        <v>90.3061</v>
+      </c>
+      <c r="AA60" s="9" t="n"/>
+      <c r="AB60" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC60" s="5" t="inlineStr">
+        <is>
+          <t>3:18:11.767618</t>
+        </is>
+      </c>
+      <c r="AD60" s="5" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="AE60" s="6" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S2/LEVIR/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>SCTC-Run1</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>S2_SCTC_UnchangedAware_Symmetric_CrossTemporal_Calibration</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=sctc</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H61" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I61" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J61" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L61" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M61" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N61" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O61" s="7" t="n"/>
+      <c r="P61" s="7" t="n"/>
+      <c r="Q61" s="5" t="n"/>
+      <c r="R61" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S61" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U61" s="8" t="n">
+        <v>81.00070000000001</v>
+      </c>
+      <c r="V61" s="8" t="n">
+        <v>84.595</v>
+      </c>
+      <c r="W61" s="8" t="n">
+        <v>92.04090000000001</v>
+      </c>
+      <c r="X61" s="8" t="n">
+        <v>82.75879999999999</v>
+      </c>
+      <c r="Y61" s="8" t="n">
+        <v>70.5885</v>
+      </c>
+      <c r="Z61" s="8" t="n">
+        <v>77.5882</v>
+      </c>
+      <c r="AA61" s="9" t="n"/>
+      <c r="AB61" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="5" t="inlineStr">
+        <is>
+          <t>4:06:34.060509</t>
+        </is>
+      </c>
+      <c r="AD61" s="5" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="AE61" s="6" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S2/SYSU/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>SCTC-Run1</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>S2_SCTC_UnchangedAware_Symmetric_CrossTemporal_Calibration</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=sctc</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I62" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J62" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K62" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L62" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M62" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N62" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O62" s="7" t="n"/>
+      <c r="P62" s="7" t="n"/>
+      <c r="Q62" s="5" t="n"/>
+      <c r="R62" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S62" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U62" s="8" t="n">
+        <v>92.7942</v>
+      </c>
+      <c r="V62" s="8" t="n">
+        <v>95.1825</v>
+      </c>
+      <c r="W62" s="8" t="n">
+        <v>99.5278</v>
+      </c>
+      <c r="X62" s="8" t="n">
+        <v>93.9731</v>
+      </c>
+      <c r="Y62" s="8" t="n">
+        <v>88.6315</v>
+      </c>
+      <c r="Z62" s="8" t="n">
+        <v>93.7274</v>
+      </c>
+      <c r="AA62" s="9" t="n"/>
+      <c r="AB62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC62" s="5" t="inlineStr">
+        <is>
+          <t>2:08:54.218613</t>
+        </is>
+      </c>
+      <c r="AD62" s="5" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="AE62" s="6" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S2/WHU/train_log.txt</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="X2:X50">
+  <conditionalFormatting sqref="X2:X62">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -6477,7 +7797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -7335,6 +8655,210 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S0/CDD/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C51" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S0/LEVIR/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C52" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S0/SYSU/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C53" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S0/WHU/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C54" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S1/CDD/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C55" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S1/LEVIR/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C56" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S1/SYSU/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C57" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S1/WHU/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C58" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="B59" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S2/CDD/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C59" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S2/LEVIR/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C60" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S2/SYSU/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C61" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S2/WHU/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C62" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -188,8 +188,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ExperimentResultsTable" displayName="ExperimentResultsTable" ref="A1:AE62" headerRowCount="1">
-  <autoFilter ref="A1:AE62"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ExperimentResultsTable" displayName="ExperimentResultsTable" ref="A1:AE70" headerRowCount="1">
+  <autoFilter ref="A1:AE70"/>
   <tableColumns count="31">
     <tableColumn id="1" name="Run"/>
     <tableColumn id="2" name="Stage"/>
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>LS-Rep_BCD_RSML_3 — Experiment Metrics (DART-R / RDT-CD / SCTC)</t>
+          <t>LS-Rep_BCD_RSML_3 — Experiment Metrics (DART-R / RDT-CD / SCTC / FA-SCRD)</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21 10:26:53 +0800</t>
+          <t>2026-09-22 10:05:46 +0800</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8">
@@ -596,7 +596,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>DART-R=8, DART-R-TS=4, RDT-CD-Run1=12, RDT-CD-Run2=11, RDT-CD-Run3=14, SCTC-Run1=12</t>
+          <t>DART-R=8, DART-R-TS=4, FA-SCRD-Run1=8, RDT-CD-Run1=12, RDT-CD-Run2=11, RDT-CD-Run3=14, SCTC-Run1=12</t>
         </is>
       </c>
     </row>
@@ -621,6 +621,18 @@
       <c r="B10" s="3" t="inlineStr">
         <is>
           <t>SCTC-Run1: S0=clean A2Net, S1=full-pixel symmetric calibration, S2=unchanged-aware SCTC. S2-S0 = WHU +0.43 / SYSU -0.25 / CDD -0.20 / LEVIR -0.10 → WHU-only single-dataset trick, H4 failed. 40k, seed 2333 only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>FA-SCRD scope</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>FA-SCRD-Run1: C0=clean, C1=joint temporal BN, A1=fixed DINOv3 teacher relation KD, M1=+failure-aware weighting. A1-C1 = SYSU -0.33 / CDD -0.33 → teacher transfer negative (not a trick, a straight loss). WHU/LEVIR stopped early (C0 only). 40k, seed 2333 only.</t>
         </is>
       </c>
     </row>
@@ -635,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE62"/>
+  <dimension ref="A1:AE70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2211,7 +2223,7 @@
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>RDT-CD-Run1</t>
+          <t>FA-SCRD-Run1</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -2221,12 +2233,12 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>B0</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Baseline_A2Net_LWGANet_L0</t>
+          <t>A1_FixedTeacherRelationKD</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -2236,7 +2248,7 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>mode=none; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G14" s="5" t="n">
@@ -2269,11 +2281,7 @@
       </c>
       <c r="O14" s="7" t="n"/>
       <c r="P14" s="7" t="n"/>
-      <c r="Q14" s="5" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="Q14" s="5" t="n"/>
       <c r="R14" s="8" t="n">
         <v>2.9131</v>
       </c>
@@ -2284,49 +2292,47 @@
         <v>2.7676</v>
       </c>
       <c r="U14" s="8" t="n">
+        <v>97.2534</v>
+      </c>
+      <c r="V14" s="8" t="n">
         <v>97.6781</v>
       </c>
-      <c r="V14" s="8" t="n">
-        <v>97.9079</v>
-      </c>
       <c r="W14" s="8" t="n">
-        <v>99.45580000000001</v>
+        <v>99.37559999999999</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>97.7929</v>
+        <v>97.4653</v>
       </c>
       <c r="Y14" s="8" t="n">
-        <v>95.6811</v>
+        <v>95.05590000000001</v>
       </c>
       <c r="Z14" s="8" t="n">
-        <v>97.4825</v>
-      </c>
-      <c r="AA14" s="9" t="n">
-        <v>0</v>
-      </c>
+        <v>97.1093</v>
+      </c>
+      <c r="AA14" s="9" t="n"/>
       <c r="AB14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AC14" s="5" t="inlineStr">
         <is>
-          <t>2:20:38.145359</t>
+          <t>3:59:53.374851</t>
         </is>
       </c>
       <c r="AD14" s="5" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run1</t>
+          <t>outputs/FA-SCRD/Run1</t>
         </is>
       </c>
       <c r="AE14" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run1/B0/CDD/steps_40000/seed_2333/train_log.txt</t>
+          <t>outputs/FA-SCRD/Run1/A1/CDD/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>RDT-CD-Run1</t>
+          <t>FA-SCRD-Run1</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -2336,22 +2342,22 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>B0</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Baseline_A2Net_LWGANet_L0</t>
+          <t>A1_FixedTeacherRelationKD</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>mode=none; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G15" s="5" t="n">
@@ -2384,11 +2390,7 @@
       </c>
       <c r="O15" s="7" t="n"/>
       <c r="P15" s="7" t="n"/>
-      <c r="Q15" s="5" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="Q15" s="5" t="n"/>
       <c r="R15" s="8" t="n">
         <v>2.9131</v>
       </c>
@@ -2399,49 +2401,47 @@
         <v>2.7676</v>
       </c>
       <c r="U15" s="8" t="n">
-        <v>90.49430000000001</v>
+        <v>80.2927</v>
       </c>
       <c r="V15" s="8" t="n">
-        <v>92.0642</v>
+        <v>83.8117</v>
       </c>
       <c r="W15" s="8" t="n">
-        <v>99.11839999999999</v>
+        <v>91.6951</v>
       </c>
       <c r="X15" s="8" t="n">
-        <v>91.27250000000001</v>
+        <v>82.01439999999999</v>
       </c>
       <c r="Y15" s="8" t="n">
-        <v>83.9461</v>
+        <v>69.51230000000001</v>
       </c>
       <c r="Z15" s="8" t="n">
-        <v>90.8083</v>
-      </c>
-      <c r="AA15" s="9" t="n">
-        <v>0</v>
-      </c>
+        <v>76.61869999999999</v>
+      </c>
+      <c r="AA15" s="9" t="n"/>
       <c r="AB15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AC15" s="5" t="inlineStr">
         <is>
-          <t>2:16:24.770920</t>
+          <t>4:15:52.937349</t>
         </is>
       </c>
       <c r="AD15" s="5" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run1</t>
+          <t>outputs/FA-SCRD/Run1</t>
         </is>
       </c>
       <c r="AE15" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run1/B0/LEVIR/steps_40000/seed_2333/train_log.txt</t>
+          <t>outputs/FA-SCRD/Run1/A1/SYSU/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>RDT-CD-Run1</t>
+          <t>FA-SCRD-Run1</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -2451,22 +2451,22 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>B0</t>
+          <t>C0</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Baseline_A2Net_LWGANet_L0</t>
+          <t>C0_Clean_A2Net</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>mode=none; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G16" s="5" t="n">
@@ -2499,11 +2499,7 @@
       </c>
       <c r="O16" s="7" t="n"/>
       <c r="P16" s="7" t="n"/>
-      <c r="Q16" s="5" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="Q16" s="5" t="n"/>
       <c r="R16" s="8" t="n">
         <v>2.9131</v>
       </c>
@@ -2514,49 +2510,47 @@
         <v>2.7676</v>
       </c>
       <c r="U16" s="8" t="n">
-        <v>76.25699999999999</v>
+        <v>97.6695</v>
       </c>
       <c r="V16" s="8" t="n">
-        <v>85.93730000000001</v>
+        <v>97.90600000000001</v>
       </c>
       <c r="W16" s="8" t="n">
-        <v>91.45790000000001</v>
+        <v>99.4545</v>
       </c>
       <c r="X16" s="8" t="n">
-        <v>80.8083</v>
+        <v>97.7876</v>
       </c>
       <c r="Y16" s="8" t="n">
-        <v>67.79690000000001</v>
+        <v>95.67099999999999</v>
       </c>
       <c r="Z16" s="8" t="n">
-        <v>75.3399</v>
-      </c>
-      <c r="AA16" s="9" t="n">
-        <v>0</v>
-      </c>
+        <v>97.4765</v>
+      </c>
+      <c r="AA16" s="9" t="n"/>
       <c r="AB16" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AC16" s="5" t="inlineStr">
         <is>
-          <t>2:19:29.914205</t>
+          <t>3:29:12.561341</t>
         </is>
       </c>
       <c r="AD16" s="5" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run1</t>
+          <t>outputs/FA-SCRD/Run1</t>
         </is>
       </c>
       <c r="AE16" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run1/B0/SYSU/steps_40000/seed_2333/train_log.txt</t>
+          <t>outputs/FA-SCRD/Run1/C0/CDD/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>RDT-CD-Run1</t>
+          <t>FA-SCRD-Run1</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -2566,22 +2560,22 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>B0</t>
+          <t>C0</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Baseline_A2Net_LWGANet_L0</t>
+          <t>C0_Clean_A2Net</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>mode=none; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G17" s="5" t="n">
@@ -2614,11 +2608,7 @@
       </c>
       <c r="O17" s="7" t="n"/>
       <c r="P17" s="7" t="n"/>
-      <c r="Q17" s="5" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
+      <c r="Q17" s="5" t="n"/>
       <c r="R17" s="8" t="n">
         <v>2.9131</v>
       </c>
@@ -2629,49 +2619,47 @@
         <v>2.7676</v>
       </c>
       <c r="U17" s="8" t="n">
-        <v>92.7128</v>
+        <v>80.6332</v>
       </c>
       <c r="V17" s="8" t="n">
-        <v>95.3785</v>
+        <v>83.9975</v>
       </c>
       <c r="W17" s="8" t="n">
-        <v>99.5326</v>
+        <v>91.81009999999999</v>
       </c>
       <c r="X17" s="8" t="n">
-        <v>94.02669999999999</v>
+        <v>82.28100000000001</v>
       </c>
       <c r="Y17" s="8" t="n">
-        <v>88.7269</v>
+        <v>69.8961</v>
       </c>
       <c r="Z17" s="8" t="n">
-        <v>93.78360000000001</v>
-      </c>
-      <c r="AA17" s="9" t="n">
-        <v>0</v>
-      </c>
+        <v>76.9581</v>
+      </c>
+      <c r="AA17" s="9" t="n"/>
       <c r="AB17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AC17" s="5" t="inlineStr">
         <is>
-          <t>2:10:04.530973</t>
+          <t>3:31:35.044716</t>
         </is>
       </c>
       <c r="AD17" s="5" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run1</t>
+          <t>outputs/FA-SCRD/Run1</t>
         </is>
       </c>
       <c r="AE17" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run1/B0/WHU/steps_40000/seed_2333/train_log.txt</t>
+          <t>outputs/FA-SCRD/Run1/C0/SYSU/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>RDT-CD-Run1</t>
+          <t>FA-SCRD-Run1</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -2681,12 +2669,12 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>D1_RDT_CD_Full</t>
+          <t>C1_JointTemporalBN</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -2696,7 +2684,7 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>mode=direction_c; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G18" s="5" t="n">
@@ -2729,13 +2717,9 @@
       </c>
       <c r="O18" s="7" t="n"/>
       <c r="P18" s="7" t="n"/>
-      <c r="Q18" s="5" t="inlineStr">
-        <is>
-          <t>direction_c</t>
-        </is>
-      </c>
+      <c r="Q18" s="5" t="n"/>
       <c r="R18" s="8" t="n">
-        <v>2.9406</v>
+        <v>2.9131</v>
       </c>
       <c r="S18" s="8" t="n">
         <v>2.9131</v>
@@ -2744,49 +2728,47 @@
         <v>2.7676</v>
       </c>
       <c r="U18" s="8" t="n">
-        <v>97.69539999999999</v>
+        <v>97.69839999999999</v>
       </c>
       <c r="V18" s="8" t="n">
-        <v>97.8993</v>
+        <v>97.8925</v>
       </c>
       <c r="W18" s="8" t="n">
-        <v>99.4568</v>
+        <v>99.4563</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>97.79729999999999</v>
+        <v>97.7953</v>
       </c>
       <c r="Y18" s="8" t="n">
-        <v>95.68950000000001</v>
+        <v>95.6858</v>
       </c>
       <c r="Z18" s="8" t="n">
-        <v>97.48750000000001</v>
-      </c>
-      <c r="AA18" s="9" t="n">
-        <v>0</v>
-      </c>
+        <v>97.4853</v>
+      </c>
+      <c r="AA18" s="9" t="n"/>
       <c r="AB18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AC18" s="5" t="inlineStr">
         <is>
-          <t>7:18:57.163600</t>
+          <t>3:14:10.393120</t>
         </is>
       </c>
       <c r="AD18" s="5" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run1</t>
+          <t>outputs/FA-SCRD/Run1</t>
         </is>
       </c>
       <c r="AE18" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run1/D1/CDD/steps_40000/seed_2333/train_log.txt</t>
+          <t>outputs/FA-SCRD/Run1/C1/CDD/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>RDT-CD-Run1</t>
+          <t>FA-SCRD-Run1</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -2796,22 +2778,22 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>D1_RDT_CD_Full</t>
+          <t>C1_JointTemporalBN</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>mode=direction_c; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G19" s="5" t="n">
@@ -2844,13 +2826,9 @@
       </c>
       <c r="O19" s="7" t="n"/>
       <c r="P19" s="7" t="n"/>
-      <c r="Q19" s="5" t="inlineStr">
-        <is>
-          <t>direction_c</t>
-        </is>
-      </c>
+      <c r="Q19" s="5" t="n"/>
       <c r="R19" s="8" t="n">
-        <v>2.9406</v>
+        <v>2.9131</v>
       </c>
       <c r="S19" s="8" t="n">
         <v>2.9131</v>
@@ -2859,49 +2837,47 @@
         <v>2.7676</v>
       </c>
       <c r="U19" s="8" t="n">
-        <v>90.00620000000001</v>
+        <v>78.55839999999999</v>
       </c>
       <c r="V19" s="8" t="n">
-        <v>92.3428</v>
+        <v>86.51649999999999</v>
       </c>
       <c r="W19" s="8" t="n">
-        <v>99.11069999999999</v>
+        <v>92.0562</v>
       </c>
       <c r="X19" s="8" t="n">
-        <v>91.15950000000001</v>
+        <v>82.34559999999999</v>
       </c>
       <c r="Y19" s="8" t="n">
-        <v>83.7552</v>
+        <v>69.9894</v>
       </c>
       <c r="Z19" s="8" t="n">
-        <v>90.6914</v>
-      </c>
-      <c r="AA19" s="9" t="n">
-        <v>0</v>
-      </c>
+        <v>77.236</v>
+      </c>
+      <c r="AA19" s="9" t="n"/>
       <c r="AB19" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AC19" s="5" t="inlineStr">
         <is>
-          <t>5:24:02.165247</t>
+          <t>3:28:18.240041</t>
         </is>
       </c>
       <c r="AD19" s="5" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run1</t>
+          <t>outputs/FA-SCRD/Run1</t>
         </is>
       </c>
       <c r="AE19" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run1/D1/LEVIR/steps_40000/seed_2333/train_log.txt</t>
+          <t>outputs/FA-SCRD/Run1/C1/SYSU/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>RDT-CD-Run1</t>
+          <t>FA-SCRD-Run1</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -2911,22 +2887,22 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>D1_RDT_CD_Full</t>
+          <t>M1_FASCRD</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>mode=direction_c; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G20" s="5" t="n">
@@ -2959,13 +2935,9 @@
       </c>
       <c r="O20" s="7" t="n"/>
       <c r="P20" s="7" t="n"/>
-      <c r="Q20" s="5" t="inlineStr">
-        <is>
-          <t>direction_c</t>
-        </is>
-      </c>
+      <c r="Q20" s="5" t="n"/>
       <c r="R20" s="8" t="n">
-        <v>2.9406</v>
+        <v>2.9131</v>
       </c>
       <c r="S20" s="8" t="n">
         <v>2.9131</v>
@@ -2974,49 +2946,47 @@
         <v>2.7676</v>
       </c>
       <c r="U20" s="8" t="n">
-        <v>81.0399</v>
+        <v>97.66930000000001</v>
       </c>
       <c r="V20" s="8" t="n">
-        <v>85.5491</v>
+        <v>97.9135</v>
       </c>
       <c r="W20" s="8" t="n">
-        <v>92.30040000000001</v>
+        <v>99.45540000000001</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>83.2334</v>
+        <v>97.79130000000001</v>
       </c>
       <c r="Y20" s="8" t="n">
-        <v>71.28189999999999</v>
+        <v>95.678</v>
       </c>
       <c r="Z20" s="8" t="n">
-        <v>78.2409</v>
-      </c>
-      <c r="AA20" s="9" t="n">
-        <v>0</v>
-      </c>
+        <v>97.4807</v>
+      </c>
+      <c r="AA20" s="9" t="n"/>
       <c r="AB20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AC20" s="5" t="inlineStr">
         <is>
-          <t>6:55:31.918603</t>
+          <t>3:48:30.111460</t>
         </is>
       </c>
       <c r="AD20" s="5" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run1</t>
+          <t>outputs/FA-SCRD/Run1</t>
         </is>
       </c>
       <c r="AE20" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run1/D1/SYSU/steps_40000/seed_2333/train_log.txt</t>
+          <t>outputs/FA-SCRD/Run1/M1/CDD/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>RDT-CD-Run1</t>
+          <t>FA-SCRD-Run1</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -3026,22 +2996,22 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>D1_RDT_CD_Full</t>
+          <t>M1_FASCRD</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>mode=direction_c; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G21" s="5" t="n">
@@ -3074,13 +3044,9 @@
       </c>
       <c r="O21" s="7" t="n"/>
       <c r="P21" s="7" t="n"/>
-      <c r="Q21" s="5" t="inlineStr">
-        <is>
-          <t>direction_c</t>
-        </is>
-      </c>
+      <c r="Q21" s="5" t="n"/>
       <c r="R21" s="8" t="n">
-        <v>2.9406</v>
+        <v>2.9131</v>
       </c>
       <c r="S21" s="8" t="n">
         <v>2.9131</v>
@@ -3089,42 +3055,40 @@
         <v>2.7676</v>
       </c>
       <c r="U21" s="8" t="n">
-        <v>93.253</v>
+        <v>79.8026</v>
       </c>
       <c r="V21" s="8" t="n">
-        <v>95.1931</v>
+        <v>83.8237</v>
       </c>
       <c r="W21" s="8" t="n">
-        <v>99.5455</v>
+        <v>91.60509999999999</v>
       </c>
       <c r="X21" s="8" t="n">
-        <v>94.21300000000001</v>
+        <v>81.7637</v>
       </c>
       <c r="Y21" s="8" t="n">
-        <v>89.0592</v>
+        <v>69.15289999999999</v>
       </c>
       <c r="Z21" s="8" t="n">
-        <v>93.9765</v>
-      </c>
-      <c r="AA21" s="9" t="n">
-        <v>0</v>
-      </c>
+        <v>76.3155</v>
+      </c>
+      <c r="AA21" s="9" t="n"/>
       <c r="AB21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AC21" s="5" t="inlineStr">
         <is>
-          <t>4:12:06.381325</t>
+          <t>3:36:38.540552</t>
         </is>
       </c>
       <c r="AD21" s="5" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run1</t>
+          <t>outputs/FA-SCRD/Run1</t>
         </is>
       </c>
       <c r="AE21" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run1/D1/WHU/steps_40000/seed_2333/train_log.txt</t>
+          <t>outputs/FA-SCRD/Run1/M1/SYSU/train_log.txt</t>
         </is>
       </c>
     </row>
@@ -3141,12 +3105,12 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>B0</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>D2_RDT_CD_NoCache</t>
+          <t>Baseline_A2Net_LWGANet_L0</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -3156,7 +3120,7 @@
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>mode=direction_c; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>mode=none; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G22" s="5" t="n">
@@ -3191,11 +3155,11 @@
       <c r="P22" s="7" t="n"/>
       <c r="Q22" s="5" t="inlineStr">
         <is>
-          <t>direction_c</t>
+          <t>none</t>
         </is>
       </c>
       <c r="R22" s="8" t="n">
-        <v>2.9406</v>
+        <v>2.9131</v>
       </c>
       <c r="S22" s="8" t="n">
         <v>2.9131</v>
@@ -3204,22 +3168,22 @@
         <v>2.7676</v>
       </c>
       <c r="U22" s="8" t="n">
-        <v>97.6968</v>
+        <v>97.6781</v>
       </c>
       <c r="V22" s="8" t="n">
-        <v>97.9029</v>
+        <v>97.9079</v>
       </c>
       <c r="W22" s="8" t="n">
-        <v>99.45739999999999</v>
+        <v>99.45580000000001</v>
       </c>
       <c r="X22" s="8" t="n">
-        <v>97.7998</v>
+        <v>97.7929</v>
       </c>
       <c r="Y22" s="8" t="n">
-        <v>95.6943</v>
+        <v>95.6811</v>
       </c>
       <c r="Z22" s="8" t="n">
-        <v>97.49029999999999</v>
+        <v>97.4825</v>
       </c>
       <c r="AA22" s="9" t="n">
         <v>0</v>
@@ -3229,7 +3193,7 @@
       </c>
       <c r="AC22" s="5" t="inlineStr">
         <is>
-          <t>7:17:26.882831</t>
+          <t>2:20:38.145359</t>
         </is>
       </c>
       <c r="AD22" s="5" t="inlineStr">
@@ -3239,7 +3203,7 @@
       </c>
       <c r="AE22" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run1/D2/CDD/steps_40000/seed_2333/train_log.txt</t>
+          <t>outputs/RDT-CD/Run1/B0/CDD/steps_40000/seed_2333/train_log.txt</t>
         </is>
       </c>
     </row>
@@ -3256,12 +3220,12 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>B0</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>D2_RDT_CD_NoCache</t>
+          <t>Baseline_A2Net_LWGANet_L0</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -3271,7 +3235,7 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>mode=direction_c; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>mode=none; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G23" s="5" t="n">
@@ -3306,11 +3270,11 @@
       <c r="P23" s="7" t="n"/>
       <c r="Q23" s="5" t="inlineStr">
         <is>
-          <t>direction_c</t>
+          <t>none</t>
         </is>
       </c>
       <c r="R23" s="8" t="n">
-        <v>2.9406</v>
+        <v>2.9131</v>
       </c>
       <c r="S23" s="8" t="n">
         <v>2.9131</v>
@@ -3319,22 +3283,22 @@
         <v>2.7676</v>
       </c>
       <c r="U23" s="8" t="n">
-        <v>90.0788</v>
+        <v>90.49430000000001</v>
       </c>
       <c r="V23" s="8" t="n">
-        <v>92.26910000000001</v>
+        <v>92.0642</v>
       </c>
       <c r="W23" s="8" t="n">
-        <v>99.1101</v>
+        <v>99.11839999999999</v>
       </c>
       <c r="X23" s="8" t="n">
-        <v>91.16079999999999</v>
+        <v>91.27250000000001</v>
       </c>
       <c r="Y23" s="8" t="n">
-        <v>83.7573</v>
+        <v>83.9461</v>
       </c>
       <c r="Z23" s="8" t="n">
-        <v>90.6923</v>
+        <v>90.8083</v>
       </c>
       <c r="AA23" s="9" t="n">
         <v>0</v>
@@ -3344,7 +3308,7 @@
       </c>
       <c r="AC23" s="5" t="inlineStr">
         <is>
-          <t>5:56:57.031072</t>
+          <t>2:16:24.770920</t>
         </is>
       </c>
       <c r="AD23" s="5" t="inlineStr">
@@ -3354,7 +3318,7 @@
       </c>
       <c r="AE23" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run1/D2/LEVIR/steps_40000/seed_2333/train_log.txt</t>
+          <t>outputs/RDT-CD/Run1/B0/LEVIR/steps_40000/seed_2333/train_log.txt</t>
         </is>
       </c>
     </row>
@@ -3371,12 +3335,12 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>B0</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>D2_RDT_CD_NoCache</t>
+          <t>Baseline_A2Net_LWGANet_L0</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -3386,7 +3350,7 @@
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>mode=direction_c; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>mode=none; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G24" s="5" t="n">
@@ -3421,11 +3385,11 @@
       <c r="P24" s="7" t="n"/>
       <c r="Q24" s="5" t="inlineStr">
         <is>
-          <t>direction_c</t>
+          <t>none</t>
         </is>
       </c>
       <c r="R24" s="8" t="n">
-        <v>2.9406</v>
+        <v>2.9131</v>
       </c>
       <c r="S24" s="8" t="n">
         <v>2.9131</v>
@@ -3434,22 +3398,22 @@
         <v>2.7676</v>
       </c>
       <c r="U24" s="8" t="n">
-        <v>79.52</v>
+        <v>76.25699999999999</v>
       </c>
       <c r="V24" s="8" t="n">
-        <v>86.0012</v>
+        <v>85.93730000000001</v>
       </c>
       <c r="W24" s="8" t="n">
-        <v>92.1177</v>
+        <v>91.45790000000001</v>
       </c>
       <c r="X24" s="8" t="n">
-        <v>82.6337</v>
+        <v>80.8083</v>
       </c>
       <c r="Y24" s="8" t="n">
-        <v>70.4067</v>
+        <v>67.79690000000001</v>
       </c>
       <c r="Z24" s="8" t="n">
-        <v>77.5457</v>
+        <v>75.3399</v>
       </c>
       <c r="AA24" s="9" t="n">
         <v>0</v>
@@ -3459,7 +3423,7 @@
       </c>
       <c r="AC24" s="5" t="inlineStr">
         <is>
-          <t>6:39:38.461859</t>
+          <t>2:19:29.914205</t>
         </is>
       </c>
       <c r="AD24" s="5" t="inlineStr">
@@ -3469,7 +3433,7 @@
       </c>
       <c r="AE24" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run1/D2/SYSU/steps_40000/seed_2333/train_log.txt</t>
+          <t>outputs/RDT-CD/Run1/B0/SYSU/steps_40000/seed_2333/train_log.txt</t>
         </is>
       </c>
     </row>
@@ -3486,12 +3450,12 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>B0</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>D2_RDT_CD_NoCache</t>
+          <t>Baseline_A2Net_LWGANet_L0</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -3501,7 +3465,7 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>mode=direction_c; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>mode=none; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G25" s="5" t="n">
@@ -3536,11 +3500,11 @@
       <c r="P25" s="7" t="n"/>
       <c r="Q25" s="5" t="inlineStr">
         <is>
-          <t>direction_c</t>
+          <t>none</t>
         </is>
       </c>
       <c r="R25" s="8" t="n">
-        <v>2.9406</v>
+        <v>2.9131</v>
       </c>
       <c r="S25" s="8" t="n">
         <v>2.9131</v>
@@ -3549,22 +3513,22 @@
         <v>2.7676</v>
       </c>
       <c r="U25" s="8" t="n">
-        <v>92.12780000000001</v>
+        <v>92.7128</v>
       </c>
       <c r="V25" s="8" t="n">
-        <v>95.0633</v>
+        <v>95.3785</v>
       </c>
       <c r="W25" s="8" t="n">
-        <v>99.4979</v>
+        <v>99.5326</v>
       </c>
       <c r="X25" s="8" t="n">
-        <v>93.57259999999999</v>
+        <v>94.02669999999999</v>
       </c>
       <c r="Y25" s="8" t="n">
-        <v>87.92149999999999</v>
+        <v>88.7269</v>
       </c>
       <c r="Z25" s="8" t="n">
-        <v>93.3113</v>
+        <v>93.78360000000001</v>
       </c>
       <c r="AA25" s="9" t="n">
         <v>0</v>
@@ -3574,7 +3538,7 @@
       </c>
       <c r="AC25" s="5" t="inlineStr">
         <is>
-          <t>4:54:24.014019</t>
+          <t>2:10:04.530973</t>
         </is>
       </c>
       <c r="AD25" s="5" t="inlineStr">
@@ -3584,14 +3548,14 @@
       </c>
       <c r="AE25" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run1/D2/WHU/steps_40000/seed_2333/train_log.txt</t>
+          <t>outputs/RDT-CD/Run1/B0/WHU/steps_40000/seed_2333/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>RDT-CD-Run2</t>
+          <t>RDT-CD-Run1</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -3601,12 +3565,12 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>B0</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Baseline_A2Net_LWGANet_L0</t>
+          <t>D1_RDT_CD_Full</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -3616,7 +3580,7 @@
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>mode=none; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>mode=direction_c; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G26" s="5" t="n">
@@ -3651,11 +3615,11 @@
       <c r="P26" s="7" t="n"/>
       <c r="Q26" s="5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direction_c</t>
         </is>
       </c>
       <c r="R26" s="8" t="n">
-        <v>2.9131</v>
+        <v>2.9406</v>
       </c>
       <c r="S26" s="8" t="n">
         <v>2.9131</v>
@@ -3664,22 +3628,22 @@
         <v>2.7676</v>
       </c>
       <c r="U26" s="8" t="n">
-        <v>97.70060000000001</v>
+        <v>97.69539999999999</v>
       </c>
       <c r="V26" s="8" t="n">
-        <v>97.89489999999999</v>
+        <v>97.8993</v>
       </c>
       <c r="W26" s="8" t="n">
         <v>99.4568</v>
       </c>
       <c r="X26" s="8" t="n">
-        <v>97.79759999999999</v>
+        <v>97.79729999999999</v>
       </c>
       <c r="Y26" s="8" t="n">
-        <v>95.6902</v>
+        <v>95.68950000000001</v>
       </c>
       <c r="Z26" s="8" t="n">
-        <v>97.48790000000001</v>
+        <v>97.48750000000001</v>
       </c>
       <c r="AA26" s="9" t="n">
         <v>0</v>
@@ -3689,24 +3653,24 @@
       </c>
       <c r="AC26" s="5" t="inlineStr">
         <is>
-          <t>5:49:25.812505</t>
+          <t>7:18:57.163600</t>
         </is>
       </c>
       <c r="AD26" s="5" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run2</t>
+          <t>outputs/RDT-CD/Run1</t>
         </is>
       </c>
       <c r="AE26" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run2/B0/CDD/train_log.txt</t>
+          <t>outputs/RDT-CD/Run1/D1/CDD/steps_40000/seed_2333/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>RDT-CD-Run2</t>
+          <t>RDT-CD-Run1</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -3716,12 +3680,12 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>B0</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Baseline_A2Net_LWGANet_L0</t>
+          <t>D1_RDT_CD_Full</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -3731,7 +3695,7 @@
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>mode=none; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>mode=direction_c; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G27" s="5" t="n">
@@ -3766,11 +3730,11 @@
       <c r="P27" s="7" t="n"/>
       <c r="Q27" s="5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direction_c</t>
         </is>
       </c>
       <c r="R27" s="8" t="n">
-        <v>2.9131</v>
+        <v>2.9406</v>
       </c>
       <c r="S27" s="8" t="n">
         <v>2.9131</v>
@@ -3779,22 +3743,22 @@
         <v>2.7676</v>
       </c>
       <c r="U27" s="8" t="n">
-        <v>89.9204</v>
+        <v>90.00620000000001</v>
       </c>
       <c r="V27" s="8" t="n">
-        <v>92.0727</v>
+        <v>92.3428</v>
       </c>
       <c r="W27" s="8" t="n">
-        <v>99.0921</v>
+        <v>99.11069999999999</v>
       </c>
       <c r="X27" s="8" t="n">
-        <v>90.9838</v>
+        <v>91.15950000000001</v>
       </c>
       <c r="Y27" s="8" t="n">
-        <v>83.459</v>
+        <v>83.7552</v>
       </c>
       <c r="Z27" s="8" t="n">
-        <v>90.5059</v>
+        <v>90.6914</v>
       </c>
       <c r="AA27" s="9" t="n">
         <v>0</v>
@@ -3804,24 +3768,24 @@
       </c>
       <c r="AC27" s="5" t="inlineStr">
         <is>
-          <t>7:30:54.783011</t>
+          <t>5:24:02.165247</t>
         </is>
       </c>
       <c r="AD27" s="5" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run2</t>
+          <t>outputs/RDT-CD/Run1</t>
         </is>
       </c>
       <c r="AE27" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run2/B0/LEVIR/train_log.txt</t>
+          <t>outputs/RDT-CD/Run1/D1/LEVIR/steps_40000/seed_2333/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>RDT-CD-Run2</t>
+          <t>RDT-CD-Run1</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -3831,12 +3795,12 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>B0</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Baseline_A2Net_LWGANet_L0</t>
+          <t>D1_RDT_CD_Full</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -3846,7 +3810,7 @@
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>mode=none; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>mode=direction_c; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G28" s="5" t="n">
@@ -3881,11 +3845,11 @@
       <c r="P28" s="7" t="n"/>
       <c r="Q28" s="5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direction_c</t>
         </is>
       </c>
       <c r="R28" s="8" t="n">
-        <v>2.9131</v>
+        <v>2.9406</v>
       </c>
       <c r="S28" s="8" t="n">
         <v>2.9131</v>
@@ -3894,22 +3858,22 @@
         <v>2.7676</v>
       </c>
       <c r="U28" s="8" t="n">
-        <v>80.76689999999999</v>
+        <v>81.0399</v>
       </c>
       <c r="V28" s="8" t="n">
-        <v>85.8715</v>
+        <v>85.5491</v>
       </c>
       <c r="W28" s="8" t="n">
-        <v>92.3305</v>
+        <v>92.30040000000001</v>
       </c>
       <c r="X28" s="8" t="n">
-        <v>83.241</v>
+        <v>83.2334</v>
       </c>
       <c r="Y28" s="8" t="n">
-        <v>71.2931</v>
+        <v>71.28189999999999</v>
       </c>
       <c r="Z28" s="8" t="n">
-        <v>78.2745</v>
+        <v>78.2409</v>
       </c>
       <c r="AA28" s="9" t="n">
         <v>0</v>
@@ -3919,24 +3883,24 @@
       </c>
       <c r="AC28" s="5" t="inlineStr">
         <is>
-          <t>3:44:43.745533</t>
+          <t>6:55:31.918603</t>
         </is>
       </c>
       <c r="AD28" s="5" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run2</t>
+          <t>outputs/RDT-CD/Run1</t>
         </is>
       </c>
       <c r="AE28" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run2/B0/SYSU/train_log.txt</t>
+          <t>outputs/RDT-CD/Run1/D1/SYSU/steps_40000/seed_2333/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>RDT-CD-Run2</t>
+          <t>RDT-CD-Run1</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -3946,12 +3910,12 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>B0</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Baseline_A2Net_LWGANet_L0</t>
+          <t>D1_RDT_CD_Full</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -3961,7 +3925,7 @@
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>mode=none; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>mode=direction_c; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G29" s="5" t="n">
@@ -3996,11 +3960,11 @@
       <c r="P29" s="7" t="n"/>
       <c r="Q29" s="5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direction_c</t>
         </is>
       </c>
       <c r="R29" s="8" t="n">
-        <v>2.9131</v>
+        <v>2.9406</v>
       </c>
       <c r="S29" s="8" t="n">
         <v>2.9131</v>
@@ -4009,22 +3973,22 @@
         <v>2.7676</v>
       </c>
       <c r="U29" s="8" t="n">
-        <v>92.73</v>
+        <v>93.253</v>
       </c>
       <c r="V29" s="8" t="n">
-        <v>94.67</v>
+        <v>95.1931</v>
       </c>
       <c r="W29" s="8" t="n">
-        <v>99.5044</v>
+        <v>99.5455</v>
       </c>
       <c r="X29" s="8" t="n">
-        <v>93.69</v>
+        <v>94.21300000000001</v>
       </c>
       <c r="Y29" s="8" t="n">
-        <v>88.129</v>
+        <v>89.0592</v>
       </c>
       <c r="Z29" s="8" t="n">
-        <v>93.43209999999999</v>
+        <v>93.9765</v>
       </c>
       <c r="AA29" s="9" t="n">
         <v>0</v>
@@ -4034,24 +3998,24 @@
       </c>
       <c r="AC29" s="5" t="inlineStr">
         <is>
-          <t>5:47:21.732638</t>
+          <t>4:12:06.381325</t>
         </is>
       </c>
       <c r="AD29" s="5" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run2</t>
+          <t>outputs/RDT-CD/Run1</t>
         </is>
       </c>
       <c r="AE29" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run2/B0/WHU/train_log.txt</t>
+          <t>outputs/RDT-CD/Run1/D1/WHU/steps_40000/seed_2333/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>RDT-CD-Run2</t>
+          <t>RDT-CD-Run1</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -4061,12 +4025,12 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>D1_RDT_SCGR_Full</t>
+          <t>D2_RDT_CD_NoCache</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -4124,22 +4088,22 @@
         <v>2.7676</v>
       </c>
       <c r="U30" s="8" t="n">
-        <v>97.78149999999999</v>
+        <v>97.6968</v>
       </c>
       <c r="V30" s="8" t="n">
-        <v>97.7444</v>
+        <v>97.9029</v>
       </c>
       <c r="W30" s="8" t="n">
-        <v>99.44760000000001</v>
+        <v>99.45739999999999</v>
       </c>
       <c r="X30" s="8" t="n">
-        <v>97.7629</v>
+        <v>97.7998</v>
       </c>
       <c r="Y30" s="8" t="n">
-        <v>95.6238</v>
+        <v>95.6943</v>
       </c>
       <c r="Z30" s="8" t="n">
-        <v>97.4479</v>
+        <v>97.49029999999999</v>
       </c>
       <c r="AA30" s="9" t="n">
         <v>0</v>
@@ -4149,24 +4113,24 @@
       </c>
       <c r="AC30" s="5" t="inlineStr">
         <is>
-          <t>8:16:12.117763</t>
+          <t>7:17:26.882831</t>
         </is>
       </c>
       <c r="AD30" s="5" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run2</t>
+          <t>outputs/RDT-CD/Run1</t>
         </is>
       </c>
       <c r="AE30" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run2/D1/CDD/train_log.txt</t>
+          <t>outputs/RDT-CD/Run1/D2/CDD/steps_40000/seed_2333/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>RDT-CD-Run2</t>
+          <t>RDT-CD-Run1</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -4176,12 +4140,12 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>D1_RDT_SCGR_Full</t>
+          <t>D2_RDT_CD_NoCache</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -4239,22 +4203,22 @@
         <v>2.7676</v>
       </c>
       <c r="U31" s="8" t="n">
-        <v>89.17870000000001</v>
+        <v>90.0788</v>
       </c>
       <c r="V31" s="8" t="n">
-        <v>93.1447</v>
+        <v>92.26910000000001</v>
       </c>
       <c r="W31" s="8" t="n">
-        <v>99.1144</v>
+        <v>99.1101</v>
       </c>
       <c r="X31" s="8" t="n">
-        <v>91.1186</v>
+        <v>91.16079999999999</v>
       </c>
       <c r="Y31" s="8" t="n">
-        <v>83.6861</v>
+        <v>83.7573</v>
       </c>
       <c r="Z31" s="8" t="n">
-        <v>90.6528</v>
+        <v>90.6923</v>
       </c>
       <c r="AA31" s="9" t="n">
         <v>0</v>
@@ -4264,24 +4228,24 @@
       </c>
       <c r="AC31" s="5" t="inlineStr">
         <is>
-          <t>5:12:10.074311</t>
+          <t>5:56:57.031072</t>
         </is>
       </c>
       <c r="AD31" s="5" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run2</t>
+          <t>outputs/RDT-CD/Run1</t>
         </is>
       </c>
       <c r="AE31" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run2/D1/LEVIR/train_log.txt</t>
+          <t>outputs/RDT-CD/Run1/D2/LEVIR/steps_40000/seed_2333/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>RDT-CD-Run2</t>
+          <t>RDT-CD-Run1</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -4291,12 +4255,12 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>D1_RDT_SCGR_Full</t>
+          <t>D2_RDT_CD_NoCache</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -4354,22 +4318,22 @@
         <v>2.7676</v>
       </c>
       <c r="U32" s="8" t="n">
-        <v>78.9362</v>
+        <v>79.52</v>
       </c>
       <c r="V32" s="8" t="n">
-        <v>86.7041</v>
+        <v>86.0012</v>
       </c>
       <c r="W32" s="8" t="n">
-        <v>92.17790000000001</v>
+        <v>92.1177</v>
       </c>
       <c r="X32" s="8" t="n">
-        <v>82.63800000000001</v>
+        <v>82.6337</v>
       </c>
       <c r="Y32" s="8" t="n">
-        <v>70.413</v>
+        <v>70.4067</v>
       </c>
       <c r="Z32" s="8" t="n">
-        <v>77.60420000000001</v>
+        <v>77.5457</v>
       </c>
       <c r="AA32" s="9" t="n">
         <v>0</v>
@@ -4379,24 +4343,24 @@
       </c>
       <c r="AC32" s="5" t="inlineStr">
         <is>
-          <t>16:43:30.502484</t>
+          <t>6:39:38.461859</t>
         </is>
       </c>
       <c r="AD32" s="5" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run2</t>
+          <t>outputs/RDT-CD/Run1</t>
         </is>
       </c>
       <c r="AE32" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run2/D1/SYSU/train_log.txt</t>
+          <t>outputs/RDT-CD/Run1/D2/SYSU/steps_40000/seed_2333/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>RDT-CD-Run2</t>
+          <t>RDT-CD-Run1</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -4406,17 +4370,17 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>D1NG</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>D1NG_RDT_SCGR_NoGradGate</t>
+          <t>D2_RDT_CD_NoCache</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
@@ -4469,22 +4433,22 @@
         <v>2.7676</v>
       </c>
       <c r="U33" s="8" t="n">
-        <v>97.87439999999999</v>
+        <v>92.12780000000001</v>
       </c>
       <c r="V33" s="8" t="n">
-        <v>97.63030000000001</v>
+        <v>95.0633</v>
       </c>
       <c r="W33" s="8" t="n">
-        <v>99.4444</v>
+        <v>99.4979</v>
       </c>
       <c r="X33" s="8" t="n">
-        <v>97.7522</v>
+        <v>93.57259999999999</v>
       </c>
       <c r="Y33" s="8" t="n">
-        <v>95.6033</v>
+        <v>87.92149999999999</v>
       </c>
       <c r="Z33" s="8" t="n">
-        <v>97.4353</v>
+        <v>93.3113</v>
       </c>
       <c r="AA33" s="9" t="n">
         <v>0</v>
@@ -4494,17 +4458,17 @@
       </c>
       <c r="AC33" s="5" t="inlineStr">
         <is>
-          <t>8:55:09.050631</t>
+          <t>4:54:24.014019</t>
         </is>
       </c>
       <c r="AD33" s="5" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run2</t>
+          <t>outputs/RDT-CD/Run1</t>
         </is>
       </c>
       <c r="AE33" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run2/D1NG/CDD/train_log.txt</t>
+          <t>outputs/RDT-CD/Run1/D2/WHU/steps_40000/seed_2333/train_log.txt</t>
         </is>
       </c>
     </row>
@@ -4521,22 +4485,22 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>D1NG</t>
+          <t>B0</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>D1NG_RDT_SCGR_NoGradGate</t>
+          <t>Baseline_A2Net_LWGANet_L0</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>mode=direction_c; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>mode=none; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G34" s="5" t="n">
@@ -4571,11 +4535,11 @@
       <c r="P34" s="7" t="n"/>
       <c r="Q34" s="5" t="inlineStr">
         <is>
-          <t>direction_c</t>
+          <t>none</t>
         </is>
       </c>
       <c r="R34" s="8" t="n">
-        <v>2.9406</v>
+        <v>2.9131</v>
       </c>
       <c r="S34" s="8" t="n">
         <v>2.9131</v>
@@ -4584,22 +4548,22 @@
         <v>2.7676</v>
       </c>
       <c r="U34" s="8" t="n">
-        <v>90.3505</v>
+        <v>97.70060000000001</v>
       </c>
       <c r="V34" s="8" t="n">
-        <v>91.75</v>
+        <v>97.89489999999999</v>
       </c>
       <c r="W34" s="8" t="n">
-        <v>99.0946</v>
+        <v>99.4568</v>
       </c>
       <c r="X34" s="8" t="n">
-        <v>91.0449</v>
+        <v>97.79759999999999</v>
       </c>
       <c r="Y34" s="8" t="n">
-        <v>83.56179999999999</v>
+        <v>95.6902</v>
       </c>
       <c r="Z34" s="8" t="n">
-        <v>90.5681</v>
+        <v>97.48790000000001</v>
       </c>
       <c r="AA34" s="9" t="n">
         <v>0</v>
@@ -4609,7 +4573,7 @@
       </c>
       <c r="AC34" s="5" t="inlineStr">
         <is>
-          <t>6:23:29.883230</t>
+          <t>5:49:25.812505</t>
         </is>
       </c>
       <c r="AD34" s="5" t="inlineStr">
@@ -4619,7 +4583,7 @@
       </c>
       <c r="AE34" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run2/D1NG/LEVIR/train_log.txt</t>
+          <t>outputs/RDT-CD/Run2/B0/CDD/train_log.txt</t>
         </is>
       </c>
     </row>
@@ -4636,22 +4600,22 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>D1NG</t>
+          <t>B0</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>D1NG_RDT_SCGR_NoGradGate</t>
+          <t>Baseline_A2Net_LWGANet_L0</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>mode=direction_c; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>mode=none; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G35" s="5" t="n">
@@ -4686,11 +4650,11 @@
       <c r="P35" s="7" t="n"/>
       <c r="Q35" s="5" t="inlineStr">
         <is>
-          <t>direction_c</t>
+          <t>none</t>
         </is>
       </c>
       <c r="R35" s="8" t="n">
-        <v>2.9406</v>
+        <v>2.9131</v>
       </c>
       <c r="S35" s="8" t="n">
         <v>2.9131</v>
@@ -4699,22 +4663,22 @@
         <v>2.7676</v>
       </c>
       <c r="U35" s="8" t="n">
-        <v>80.45659999999999</v>
+        <v>89.9204</v>
       </c>
       <c r="V35" s="8" t="n">
-        <v>85.00999999999999</v>
+        <v>92.0727</v>
       </c>
       <c r="W35" s="8" t="n">
-        <v>92.0454</v>
+        <v>99.0921</v>
       </c>
       <c r="X35" s="8" t="n">
-        <v>82.6707</v>
+        <v>90.9838</v>
       </c>
       <c r="Y35" s="8" t="n">
-        <v>70.46040000000001</v>
+        <v>83.459</v>
       </c>
       <c r="Z35" s="8" t="n">
-        <v>77.5137</v>
+        <v>90.5059</v>
       </c>
       <c r="AA35" s="9" t="n">
         <v>0</v>
@@ -4724,7 +4688,7 @@
       </c>
       <c r="AC35" s="5" t="inlineStr">
         <is>
-          <t>8:17:02.482089</t>
+          <t>7:30:54.783011</t>
         </is>
       </c>
       <c r="AD35" s="5" t="inlineStr">
@@ -4734,7 +4698,7 @@
       </c>
       <c r="AE35" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run2/D1NG/SYSU/train_log.txt</t>
+          <t>outputs/RDT-CD/Run2/B0/LEVIR/train_log.txt</t>
         </is>
       </c>
     </row>
@@ -4751,22 +4715,22 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>D1NG</t>
+          <t>B0</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>D1NG_RDT_SCGR_NoGradGate</t>
+          <t>Baseline_A2Net_LWGANet_L0</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>mode=direction_c; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>mode=none; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G36" s="5" t="n">
@@ -4801,11 +4765,11 @@
       <c r="P36" s="7" t="n"/>
       <c r="Q36" s="5" t="inlineStr">
         <is>
-          <t>direction_c</t>
+          <t>none</t>
         </is>
       </c>
       <c r="R36" s="8" t="n">
-        <v>2.9406</v>
+        <v>2.9131</v>
       </c>
       <c r="S36" s="8" t="n">
         <v>2.9131</v>
@@ -4814,22 +4778,22 @@
         <v>2.7676</v>
       </c>
       <c r="U36" s="8" t="n">
-        <v>91.36609999999999</v>
+        <v>80.76689999999999</v>
       </c>
       <c r="V36" s="8" t="n">
-        <v>94.0733</v>
+        <v>85.8715</v>
       </c>
       <c r="W36" s="8" t="n">
-        <v>99.42910000000001</v>
+        <v>92.3305</v>
       </c>
       <c r="X36" s="8" t="n">
-        <v>92.6999</v>
+        <v>83.241</v>
       </c>
       <c r="Y36" s="8" t="n">
-        <v>86.39320000000001</v>
+        <v>71.2931</v>
       </c>
       <c r="Z36" s="8" t="n">
-        <v>92.4029</v>
+        <v>78.2745</v>
       </c>
       <c r="AA36" s="9" t="n">
         <v>0</v>
@@ -4839,7 +4803,7 @@
       </c>
       <c r="AC36" s="5" t="inlineStr">
         <is>
-          <t>4:17:06.922035</t>
+          <t>3:44:43.745533</t>
         </is>
       </c>
       <c r="AD36" s="5" t="inlineStr">
@@ -4849,14 +4813,14 @@
       </c>
       <c r="AE36" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run2/D1NG/WHU/train_log.txt</t>
+          <t>outputs/RDT-CD/Run2/B0/SYSU/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>RDT-CD-Run3</t>
+          <t>RDT-CD-Run2</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -4871,12 +4835,12 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>B0_Clean_A2Net_LWGANet_L0</t>
+          <t>Baseline_A2Net_LWGANet_L0</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
@@ -4929,22 +4893,22 @@
         <v>2.7676</v>
       </c>
       <c r="U37" s="8" t="n">
-        <v>97.67400000000001</v>
+        <v>92.73</v>
       </c>
       <c r="V37" s="8" t="n">
-        <v>97.90870000000001</v>
+        <v>94.67</v>
       </c>
       <c r="W37" s="8" t="n">
-        <v>99.45540000000001</v>
+        <v>99.5044</v>
       </c>
       <c r="X37" s="8" t="n">
-        <v>97.7912</v>
+        <v>93.69</v>
       </c>
       <c r="Y37" s="8" t="n">
-        <v>95.67790000000001</v>
+        <v>88.129</v>
       </c>
       <c r="Z37" s="8" t="n">
-        <v>97.4806</v>
+        <v>93.43209999999999</v>
       </c>
       <c r="AA37" s="9" t="n">
         <v>0</v>
@@ -4954,24 +4918,24 @@
       </c>
       <c r="AC37" s="5" t="inlineStr">
         <is>
-          <t>3:48:35.477713</t>
+          <t>5:47:21.732638</t>
         </is>
       </c>
       <c r="AD37" s="5" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run3</t>
+          <t>outputs/RDT-CD/Run2</t>
         </is>
       </c>
       <c r="AE37" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run3/B0/CDD/train_log.txt</t>
+          <t>outputs/RDT-CD/Run2/B0/WHU/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>RDT-CD-Run3</t>
+          <t>RDT-CD-Run2</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -4981,22 +4945,22 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>B0</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>B0_Clean_A2Net_LWGANet_L0</t>
+          <t>D1_RDT_SCGR_Full</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>mode=none; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>mode=direction_c; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G38" s="5" t="n">
@@ -5031,11 +4995,11 @@
       <c r="P38" s="7" t="n"/>
       <c r="Q38" s="5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direction_c</t>
         </is>
       </c>
       <c r="R38" s="8" t="n">
-        <v>2.9131</v>
+        <v>2.9406</v>
       </c>
       <c r="S38" s="8" t="n">
         <v>2.9131</v>
@@ -5044,22 +5008,22 @@
         <v>2.7676</v>
       </c>
       <c r="U38" s="8" t="n">
-        <v>89.3151</v>
+        <v>97.78149999999999</v>
       </c>
       <c r="V38" s="8" t="n">
-        <v>93.02679999999999</v>
+        <v>97.7444</v>
       </c>
       <c r="W38" s="8" t="n">
-        <v>99.1146</v>
+        <v>99.44760000000001</v>
       </c>
       <c r="X38" s="8" t="n">
-        <v>91.1332</v>
+        <v>97.7629</v>
       </c>
       <c r="Y38" s="8" t="n">
-        <v>83.7107</v>
+        <v>95.6238</v>
       </c>
       <c r="Z38" s="8" t="n">
-        <v>90.6674</v>
+        <v>97.4479</v>
       </c>
       <c r="AA38" s="9" t="n">
         <v>0</v>
@@ -5069,24 +5033,24 @@
       </c>
       <c r="AC38" s="5" t="inlineStr">
         <is>
-          <t>3:13:21.820469</t>
+          <t>8:16:12.117763</t>
         </is>
       </c>
       <c r="AD38" s="5" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run3</t>
+          <t>outputs/RDT-CD/Run2</t>
         </is>
       </c>
       <c r="AE38" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run3/B0/LEVIR/train_log.txt</t>
+          <t>outputs/RDT-CD/Run2/D1/CDD/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>RDT-CD-Run3</t>
+          <t>RDT-CD-Run2</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -5096,22 +5060,22 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>B0</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>B0_Clean_A2Net_LWGANet_L0</t>
+          <t>D1_RDT_SCGR_Full</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>mode=none; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>mode=direction_c; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G39" s="5" t="n">
@@ -5146,11 +5110,11 @@
       <c r="P39" s="7" t="n"/>
       <c r="Q39" s="5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direction_c</t>
         </is>
       </c>
       <c r="R39" s="8" t="n">
-        <v>2.9131</v>
+        <v>2.9406</v>
       </c>
       <c r="S39" s="8" t="n">
         <v>2.9131</v>
@@ -5159,22 +5123,22 @@
         <v>2.7676</v>
       </c>
       <c r="U39" s="8" t="n">
-        <v>77.89570000000001</v>
+        <v>89.17870000000001</v>
       </c>
       <c r="V39" s="8" t="n">
-        <v>85.99719999999999</v>
+        <v>93.1447</v>
       </c>
       <c r="W39" s="8" t="n">
-        <v>91.79600000000001</v>
+        <v>99.1144</v>
       </c>
       <c r="X39" s="8" t="n">
-        <v>81.7462</v>
+        <v>91.1186</v>
       </c>
       <c r="Y39" s="8" t="n">
-        <v>69.12779999999999</v>
+        <v>83.6861</v>
       </c>
       <c r="Z39" s="8" t="n">
-        <v>76.47190000000001</v>
+        <v>90.6528</v>
       </c>
       <c r="AA39" s="9" t="n">
         <v>0</v>
@@ -5184,24 +5148,24 @@
       </c>
       <c r="AC39" s="5" t="inlineStr">
         <is>
-          <t>4:06:14.223274</t>
+          <t>5:12:10.074311</t>
         </is>
       </c>
       <c r="AD39" s="5" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run3</t>
+          <t>outputs/RDT-CD/Run2</t>
         </is>
       </c>
       <c r="AE39" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run3/B0/SYSU/train_log.txt</t>
+          <t>outputs/RDT-CD/Run2/D1/LEVIR/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>RDT-CD-Run3</t>
+          <t>RDT-CD-Run2</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -5211,22 +5175,22 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>B0</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>B0_Clean_A2Net_LWGANet_L0</t>
+          <t>D1_RDT_SCGR_Full</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>mode=none; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>mode=direction_c; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G40" s="5" t="n">
@@ -5261,11 +5225,11 @@
       <c r="P40" s="7" t="n"/>
       <c r="Q40" s="5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direction_c</t>
         </is>
       </c>
       <c r="R40" s="8" t="n">
-        <v>2.9131</v>
+        <v>2.9406</v>
       </c>
       <c r="S40" s="8" t="n">
         <v>2.9131</v>
@@ -5274,22 +5238,22 @@
         <v>2.7676</v>
       </c>
       <c r="U40" s="8" t="n">
-        <v>92.7808</v>
+        <v>78.9362</v>
       </c>
       <c r="V40" s="8" t="n">
-        <v>95.3728</v>
+        <v>86.7041</v>
       </c>
       <c r="W40" s="8" t="n">
-        <v>99.535</v>
+        <v>92.17790000000001</v>
       </c>
       <c r="X40" s="8" t="n">
-        <v>94.059</v>
+        <v>82.63800000000001</v>
       </c>
       <c r="Y40" s="8" t="n">
-        <v>88.7842</v>
+        <v>70.413</v>
       </c>
       <c r="Z40" s="8" t="n">
-        <v>93.81699999999999</v>
+        <v>77.60420000000001</v>
       </c>
       <c r="AA40" s="9" t="n">
         <v>0</v>
@@ -5299,24 +5263,24 @@
       </c>
       <c r="AC40" s="5" t="inlineStr">
         <is>
-          <t>3:15:04.521316</t>
+          <t>16:43:30.502484</t>
         </is>
       </c>
       <c r="AD40" s="5" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run3</t>
+          <t>outputs/RDT-CD/Run2</t>
         </is>
       </c>
       <c r="AE40" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run3/B0/WHU/train_log.txt</t>
+          <t>outputs/RDT-CD/Run2/D1/SYSU/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>RDT-CD-Run3</t>
+          <t>RDT-CD-Run2</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -5326,12 +5290,12 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>D1NG</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>R3_BT_SAM_RDT_Full</t>
+          <t>D1NG_RDT_SCGR_NoGradGate</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -5341,7 +5305,7 @@
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>mode=bt_sam_rdt; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>mode=direction_c; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G41" s="5" t="n">
@@ -5376,11 +5340,11 @@
       <c r="P41" s="7" t="n"/>
       <c r="Q41" s="5" t="inlineStr">
         <is>
-          <t>bt_sam_rdt</t>
+          <t>direction_c</t>
         </is>
       </c>
       <c r="R41" s="8" t="n">
-        <v>2.9269</v>
+        <v>2.9406</v>
       </c>
       <c r="S41" s="8" t="n">
         <v>2.9131</v>
@@ -5389,22 +5353,22 @@
         <v>2.7676</v>
       </c>
       <c r="U41" s="8" t="n">
-        <v>97.6738</v>
+        <v>97.87439999999999</v>
       </c>
       <c r="V41" s="8" t="n">
-        <v>97.91459999999999</v>
+        <v>97.63030000000001</v>
       </c>
       <c r="W41" s="8" t="n">
-        <v>99.45610000000001</v>
+        <v>99.4444</v>
       </c>
       <c r="X41" s="8" t="n">
-        <v>97.794</v>
+        <v>97.7522</v>
       </c>
       <c r="Y41" s="8" t="n">
-        <v>95.6833</v>
+        <v>95.6033</v>
       </c>
       <c r="Z41" s="8" t="n">
-        <v>97.4838</v>
+        <v>97.4353</v>
       </c>
       <c r="AA41" s="9" t="n">
         <v>0</v>
@@ -5414,24 +5378,24 @@
       </c>
       <c r="AC41" s="5" t="inlineStr">
         <is>
-          <t>11:08:17.035446</t>
+          <t>8:55:09.050631</t>
         </is>
       </c>
       <c r="AD41" s="5" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run3</t>
+          <t>outputs/RDT-CD/Run2</t>
         </is>
       </c>
       <c r="AE41" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run3/R3/CDD/train_log.txt</t>
+          <t>outputs/RDT-CD/Run2/D1NG/CDD/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>RDT-CD-Run3</t>
+          <t>RDT-CD-Run2</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -5441,12 +5405,12 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>D1NG</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>R3_BT_SAM_RDT_Full</t>
+          <t>D1NG_RDT_SCGR_NoGradGate</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -5456,7 +5420,7 @@
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>mode=bt_sam_rdt; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>mode=direction_c; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G42" s="5" t="n">
@@ -5491,11 +5455,11 @@
       <c r="P42" s="7" t="n"/>
       <c r="Q42" s="5" t="inlineStr">
         <is>
-          <t>bt_sam_rdt</t>
+          <t>direction_c</t>
         </is>
       </c>
       <c r="R42" s="8" t="n">
-        <v>2.9269</v>
+        <v>2.9406</v>
       </c>
       <c r="S42" s="8" t="n">
         <v>2.9131</v>
@@ -5504,22 +5468,22 @@
         <v>2.7676</v>
       </c>
       <c r="U42" s="8" t="n">
-        <v>89.21550000000001</v>
+        <v>90.3505</v>
       </c>
       <c r="V42" s="8" t="n">
-        <v>92.8203</v>
+        <v>91.75</v>
       </c>
       <c r="W42" s="8" t="n">
-        <v>99.09909999999999</v>
+        <v>99.0946</v>
       </c>
       <c r="X42" s="8" t="n">
-        <v>90.98220000000001</v>
+        <v>91.0449</v>
       </c>
       <c r="Y42" s="8" t="n">
-        <v>83.4564</v>
+        <v>83.56179999999999</v>
       </c>
       <c r="Z42" s="8" t="n">
-        <v>90.50829999999999</v>
+        <v>90.5681</v>
       </c>
       <c r="AA42" s="9" t="n">
         <v>0</v>
@@ -5529,24 +5493,24 @@
       </c>
       <c r="AC42" s="5" t="inlineStr">
         <is>
-          <t>5:19:09.846917</t>
+          <t>6:23:29.883230</t>
         </is>
       </c>
       <c r="AD42" s="5" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run3</t>
+          <t>outputs/RDT-CD/Run2</t>
         </is>
       </c>
       <c r="AE42" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run3/R3/LEVIR/train_log.txt</t>
+          <t>outputs/RDT-CD/Run2/D1NG/LEVIR/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>RDT-CD-Run3</t>
+          <t>RDT-CD-Run2</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
@@ -5556,12 +5520,12 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>D1NG</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>R3_BT_SAM_RDT_Full</t>
+          <t>D1NG_RDT_SCGR_NoGradGate</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -5571,7 +5535,7 @@
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>mode=bt_sam_rdt; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>mode=direction_c; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G43" s="5" t="n">
@@ -5606,11 +5570,11 @@
       <c r="P43" s="7" t="n"/>
       <c r="Q43" s="5" t="inlineStr">
         <is>
-          <t>bt_sam_rdt</t>
+          <t>direction_c</t>
         </is>
       </c>
       <c r="R43" s="8" t="n">
-        <v>2.9269</v>
+        <v>2.9406</v>
       </c>
       <c r="S43" s="8" t="n">
         <v>2.9131</v>
@@ -5619,22 +5583,22 @@
         <v>2.7676</v>
       </c>
       <c r="U43" s="8" t="n">
-        <v>81.1455</v>
+        <v>80.45659999999999</v>
       </c>
       <c r="V43" s="8" t="n">
-        <v>85.2085</v>
+        <v>85.00999999999999</v>
       </c>
       <c r="W43" s="8" t="n">
-        <v>92.2317</v>
+        <v>92.0454</v>
       </c>
       <c r="X43" s="8" t="n">
-        <v>83.12739999999999</v>
+        <v>82.6707</v>
       </c>
       <c r="Y43" s="8" t="n">
-        <v>71.12650000000001</v>
+        <v>70.46040000000001</v>
       </c>
       <c r="Z43" s="8" t="n">
-        <v>78.0856</v>
+        <v>77.5137</v>
       </c>
       <c r="AA43" s="9" t="n">
         <v>0</v>
@@ -5644,24 +5608,24 @@
       </c>
       <c r="AC43" s="5" t="inlineStr">
         <is>
-          <t>10:47:31.810425</t>
+          <t>8:17:02.482089</t>
         </is>
       </c>
       <c r="AD43" s="5" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run3</t>
+          <t>outputs/RDT-CD/Run2</t>
         </is>
       </c>
       <c r="AE43" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run3/R3/SYSU/train_log.txt</t>
+          <t>outputs/RDT-CD/Run2/D1NG/SYSU/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>RDT-CD-Run3</t>
+          <t>RDT-CD-Run2</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -5671,12 +5635,12 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>D1NG</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>R3_BT_SAM_RDT_Full</t>
+          <t>D1NG_RDT_SCGR_NoGradGate</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -5686,7 +5650,7 @@
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>mode=bt_sam_rdt; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>mode=direction_c; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G44" s="5" t="n">
@@ -5721,11 +5685,11 @@
       <c r="P44" s="7" t="n"/>
       <c r="Q44" s="5" t="inlineStr">
         <is>
-          <t>bt_sam_rdt</t>
+          <t>direction_c</t>
         </is>
       </c>
       <c r="R44" s="8" t="n">
-        <v>2.9269</v>
+        <v>2.9406</v>
       </c>
       <c r="S44" s="8" t="n">
         <v>2.9131</v>
@@ -5734,22 +5698,22 @@
         <v>2.7676</v>
       </c>
       <c r="U44" s="8" t="n">
-        <v>93.0294</v>
+        <v>91.36609999999999</v>
       </c>
       <c r="V44" s="8" t="n">
-        <v>94.3871</v>
+        <v>94.0733</v>
       </c>
       <c r="W44" s="8" t="n">
-        <v>99.5039</v>
+        <v>99.42910000000001</v>
       </c>
       <c r="X44" s="8" t="n">
-        <v>93.7033</v>
+        <v>92.6999</v>
       </c>
       <c r="Y44" s="8" t="n">
-        <v>88.1527</v>
+        <v>86.39320000000001</v>
       </c>
       <c r="Z44" s="8" t="n">
-        <v>93.4452</v>
+        <v>92.4029</v>
       </c>
       <c r="AA44" s="9" t="n">
         <v>0</v>
@@ -5759,17 +5723,17 @@
       </c>
       <c r="AC44" s="5" t="inlineStr">
         <is>
-          <t>4:27:10.216507</t>
+          <t>4:17:06.922035</t>
         </is>
       </c>
       <c r="AD44" s="5" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run3</t>
+          <t>outputs/RDT-CD/Run2</t>
         </is>
       </c>
       <c r="AE44" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run3/R3/WHU/train_log.txt</t>
+          <t>outputs/RDT-CD/Run2/D1NG/WHU/train_log.txt</t>
         </is>
       </c>
     </row>
@@ -5786,12 +5750,12 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>R3A</t>
+          <t>B0</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>R3A_BT_SAM_RDT_SAM_Only</t>
+          <t>B0_Clean_A2Net_LWGANet_L0</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -5801,7 +5765,7 @@
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>mode=bt_sam_rdt; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>mode=none; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G45" s="5" t="n">
@@ -5836,11 +5800,11 @@
       <c r="P45" s="7" t="n"/>
       <c r="Q45" s="5" t="inlineStr">
         <is>
-          <t>bt_sam_rdt</t>
+          <t>none</t>
         </is>
       </c>
       <c r="R45" s="8" t="n">
-        <v>2.9269</v>
+        <v>2.9131</v>
       </c>
       <c r="S45" s="8" t="n">
         <v>2.9131</v>
@@ -5849,22 +5813,22 @@
         <v>2.7676</v>
       </c>
       <c r="U45" s="8" t="n">
-        <v>97.7008</v>
+        <v>97.67400000000001</v>
       </c>
       <c r="V45" s="8" t="n">
-        <v>97.858</v>
+        <v>97.90870000000001</v>
       </c>
       <c r="W45" s="8" t="n">
-        <v>99.4522</v>
+        <v>99.45540000000001</v>
       </c>
       <c r="X45" s="8" t="n">
-        <v>97.77930000000001</v>
+        <v>97.7912</v>
       </c>
       <c r="Y45" s="8" t="n">
-        <v>95.65519999999999</v>
+        <v>95.67790000000001</v>
       </c>
       <c r="Z45" s="8" t="n">
-        <v>97.4669</v>
+        <v>97.4806</v>
       </c>
       <c r="AA45" s="9" t="n">
         <v>0</v>
@@ -5874,7 +5838,7 @@
       </c>
       <c r="AC45" s="5" t="inlineStr">
         <is>
-          <t>11:25:23.866980</t>
+          <t>3:48:35.477713</t>
         </is>
       </c>
       <c r="AD45" s="5" t="inlineStr">
@@ -5884,7 +5848,7 @@
       </c>
       <c r="AE45" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run3/R3A/CDD/train_log.txt</t>
+          <t>outputs/RDT-CD/Run3/B0/CDD/train_log.txt</t>
         </is>
       </c>
     </row>
@@ -5901,12 +5865,12 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>R3A</t>
+          <t>B0</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>R3A_BT_SAM_RDT_SAM_Only</t>
+          <t>B0_Clean_A2Net_LWGANet_L0</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -5916,7 +5880,7 @@
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>mode=bt_sam_rdt; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>mode=none; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G46" s="5" t="n">
@@ -5951,11 +5915,11 @@
       <c r="P46" s="7" t="n"/>
       <c r="Q46" s="5" t="inlineStr">
         <is>
-          <t>bt_sam_rdt</t>
+          <t>none</t>
         </is>
       </c>
       <c r="R46" s="8" t="n">
-        <v>2.9269</v>
+        <v>2.9131</v>
       </c>
       <c r="S46" s="8" t="n">
         <v>2.9131</v>
@@ -5964,22 +5928,22 @@
         <v>2.7676</v>
       </c>
       <c r="U46" s="8" t="n">
-        <v>90.7855</v>
+        <v>89.3151</v>
       </c>
       <c r="V46" s="8" t="n">
-        <v>91.2675</v>
+        <v>93.02679999999999</v>
       </c>
       <c r="W46" s="8" t="n">
-        <v>99.0881</v>
+        <v>99.1146</v>
       </c>
       <c r="X46" s="8" t="n">
-        <v>91.0258</v>
+        <v>91.1332</v>
       </c>
       <c r="Y46" s="8" t="n">
-        <v>83.52979999999999</v>
+        <v>83.7107</v>
       </c>
       <c r="Z46" s="8" t="n">
-        <v>90.5455</v>
+        <v>90.6674</v>
       </c>
       <c r="AA46" s="9" t="n">
         <v>0</v>
@@ -5989,7 +5953,7 @@
       </c>
       <c r="AC46" s="5" t="inlineStr">
         <is>
-          <t>5:37:16.217701</t>
+          <t>3:13:21.820469</t>
         </is>
       </c>
       <c r="AD46" s="5" t="inlineStr">
@@ -5999,7 +5963,7 @@
       </c>
       <c r="AE46" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run3/R3A/LEVIR/train_log.txt</t>
+          <t>outputs/RDT-CD/Run3/B0/LEVIR/train_log.txt</t>
         </is>
       </c>
     </row>
@@ -6016,12 +5980,12 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>R3A</t>
+          <t>B0</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>R3A_BT_SAM_RDT_SAM_Only</t>
+          <t>B0_Clean_A2Net_LWGANet_L0</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -6031,7 +5995,7 @@
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>mode=bt_sam_rdt; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>mode=none; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G47" s="5" t="n">
@@ -6066,11 +6030,11 @@
       <c r="P47" s="7" t="n"/>
       <c r="Q47" s="5" t="inlineStr">
         <is>
-          <t>bt_sam_rdt</t>
+          <t>none</t>
         </is>
       </c>
       <c r="R47" s="8" t="n">
-        <v>2.9269</v>
+        <v>2.9131</v>
       </c>
       <c r="S47" s="8" t="n">
         <v>2.9131</v>
@@ -6079,22 +6043,22 @@
         <v>2.7676</v>
       </c>
       <c r="U47" s="8" t="n">
-        <v>77.91940000000001</v>
+        <v>77.89570000000001</v>
       </c>
       <c r="V47" s="8" t="n">
-        <v>87.1811</v>
+        <v>85.99719999999999</v>
       </c>
       <c r="W47" s="8" t="n">
-        <v>92.0909</v>
+        <v>91.79600000000001</v>
       </c>
       <c r="X47" s="8" t="n">
-        <v>82.29049999999999</v>
+        <v>81.7462</v>
       </c>
       <c r="Y47" s="8" t="n">
-        <v>69.9098</v>
+        <v>69.12779999999999</v>
       </c>
       <c r="Z47" s="8" t="n">
-        <v>77.2196</v>
+        <v>76.47190000000001</v>
       </c>
       <c r="AA47" s="9" t="n">
         <v>0</v>
@@ -6104,7 +6068,7 @@
       </c>
       <c r="AC47" s="5" t="inlineStr">
         <is>
-          <t>10:51:06.656145</t>
+          <t>4:06:14.223274</t>
         </is>
       </c>
       <c r="AD47" s="5" t="inlineStr">
@@ -6114,7 +6078,7 @@
       </c>
       <c r="AE47" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run3/R3A/SYSU/train_log.txt</t>
+          <t>outputs/RDT-CD/Run3/B0/SYSU/train_log.txt</t>
         </is>
       </c>
     </row>
@@ -6131,12 +6095,12 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>R3A</t>
+          <t>B0</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>R3A_BT_SAM_RDT_SAM_Only</t>
+          <t>B0_Clean_A2Net_LWGANet_L0</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -6146,7 +6110,7 @@
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>mode=bt_sam_rdt; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>mode=none; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G48" s="5" t="n">
@@ -6181,11 +6145,11 @@
       <c r="P48" s="7" t="n"/>
       <c r="Q48" s="5" t="inlineStr">
         <is>
-          <t>bt_sam_rdt</t>
+          <t>none</t>
         </is>
       </c>
       <c r="R48" s="8" t="n">
-        <v>2.9269</v>
+        <v>2.9131</v>
       </c>
       <c r="S48" s="8" t="n">
         <v>2.9131</v>
@@ -6194,22 +6158,22 @@
         <v>2.7676</v>
       </c>
       <c r="U48" s="8" t="n">
-        <v>93.08840000000001</v>
+        <v>92.7808</v>
       </c>
       <c r="V48" s="8" t="n">
-        <v>94.8141</v>
+        <v>95.3728</v>
       </c>
       <c r="W48" s="8" t="n">
-        <v>99.52379999999999</v>
+        <v>99.535</v>
       </c>
       <c r="X48" s="8" t="n">
-        <v>93.94329999999999</v>
+        <v>94.059</v>
       </c>
       <c r="Y48" s="8" t="n">
-        <v>88.5784</v>
+        <v>88.7842</v>
       </c>
       <c r="Z48" s="8" t="n">
-        <v>93.6955</v>
+        <v>93.81699999999999</v>
       </c>
       <c r="AA48" s="9" t="n">
         <v>0</v>
@@ -6219,7 +6183,7 @@
       </c>
       <c r="AC48" s="5" t="inlineStr">
         <is>
-          <t>4:29:12.633871</t>
+          <t>3:15:04.521316</t>
         </is>
       </c>
       <c r="AD48" s="5" t="inlineStr">
@@ -6229,7 +6193,7 @@
       </c>
       <c r="AE48" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run3/R3A/WHU/train_log.txt</t>
+          <t>outputs/RDT-CD/Run3/B0/WHU/train_log.txt</t>
         </is>
       </c>
     </row>
@@ -6246,17 +6210,17 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>R3O</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>R3O_BT_SAM_RDT_OV_Only</t>
+          <t>R3_BT_SAM_RDT_Full</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
@@ -6309,22 +6273,22 @@
         <v>2.7676</v>
       </c>
       <c r="U49" s="8" t="n">
-        <v>79.3635</v>
+        <v>97.6738</v>
       </c>
       <c r="V49" s="8" t="n">
-        <v>86.4628</v>
+        <v>97.91459999999999</v>
       </c>
       <c r="W49" s="8" t="n">
-        <v>92.203</v>
+        <v>99.45610000000001</v>
       </c>
       <c r="X49" s="8" t="n">
-        <v>82.7612</v>
+        <v>97.794</v>
       </c>
       <c r="Y49" s="8" t="n">
-        <v>70.592</v>
+        <v>95.6833</v>
       </c>
       <c r="Z49" s="8" t="n">
-        <v>77.7353</v>
+        <v>97.4838</v>
       </c>
       <c r="AA49" s="9" t="n">
         <v>0</v>
@@ -6334,7 +6298,7 @@
       </c>
       <c r="AC49" s="5" t="inlineStr">
         <is>
-          <t>7:05:18.102962</t>
+          <t>11:08:17.035446</t>
         </is>
       </c>
       <c r="AD49" s="5" t="inlineStr">
@@ -6344,7 +6308,7 @@
       </c>
       <c r="AE49" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run3/R3O/SYSU/train_log.txt</t>
+          <t>outputs/RDT-CD/Run3/R3/CDD/train_log.txt</t>
         </is>
       </c>
     </row>
@@ -6361,17 +6325,17 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>R3O</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>R3O_BT_SAM_RDT_OV_Only</t>
+          <t>R3_BT_SAM_RDT_Full</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
@@ -6424,22 +6388,22 @@
         <v>2.7676</v>
       </c>
       <c r="U50" s="8" t="n">
-        <v>91.0621</v>
+        <v>89.21550000000001</v>
       </c>
       <c r="V50" s="8" t="n">
-        <v>95.70359999999999</v>
+        <v>92.8203</v>
       </c>
       <c r="W50" s="8" t="n">
-        <v>99.48320000000001</v>
+        <v>99.09909999999999</v>
       </c>
       <c r="X50" s="8" t="n">
-        <v>93.3252</v>
+        <v>90.98220000000001</v>
       </c>
       <c r="Y50" s="8" t="n">
-        <v>87.48559999999999</v>
+        <v>83.4564</v>
       </c>
       <c r="Z50" s="8" t="n">
-        <v>93.0565</v>
+        <v>90.50829999999999</v>
       </c>
       <c r="AA50" s="9" t="n">
         <v>0</v>
@@ -6449,7 +6413,7 @@
       </c>
       <c r="AC50" s="5" t="inlineStr">
         <is>
-          <t>3:37:24.949796</t>
+          <t>5:19:09.846917</t>
         </is>
       </c>
       <c r="AD50" s="5" t="inlineStr">
@@ -6459,14 +6423,14 @@
       </c>
       <c r="AE50" s="6" t="inlineStr">
         <is>
-          <t>outputs/RDT-CD/Run3/R3O/WHU/train_log.txt</t>
+          <t>outputs/RDT-CD/Run3/R3/LEVIR/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>SCTC-Run1</t>
+          <t>RDT-CD-Run3</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
@@ -6476,22 +6440,22 @@
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>S0</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>S0_Clean_A2Net_LWGANet_L0</t>
+          <t>R3_BT_SAM_RDT_Full</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=none</t>
+          <t>mode=bt_sam_rdt; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G51" s="5" t="n">
@@ -6524,9 +6488,13 @@
       </c>
       <c r="O51" s="7" t="n"/>
       <c r="P51" s="7" t="n"/>
-      <c r="Q51" s="5" t="n"/>
+      <c r="Q51" s="5" t="inlineStr">
+        <is>
+          <t>bt_sam_rdt</t>
+        </is>
+      </c>
       <c r="R51" s="8" t="n">
-        <v>2.9131</v>
+        <v>2.9269</v>
       </c>
       <c r="S51" s="8" t="n">
         <v>2.9131</v>
@@ -6535,47 +6503,49 @@
         <v>2.7676</v>
       </c>
       <c r="U51" s="8" t="n">
-        <v>97.68770000000001</v>
+        <v>81.1455</v>
       </c>
       <c r="V51" s="8" t="n">
-        <v>97.8814</v>
+        <v>85.2085</v>
       </c>
       <c r="W51" s="8" t="n">
-        <v>99.45359999999999</v>
+        <v>92.2317</v>
       </c>
       <c r="X51" s="8" t="n">
-        <v>97.78449999999999</v>
+        <v>83.12739999999999</v>
       </c>
       <c r="Y51" s="8" t="n">
-        <v>95.66500000000001</v>
+        <v>71.12650000000001</v>
       </c>
       <c r="Z51" s="8" t="n">
-        <v>97.47280000000001</v>
-      </c>
-      <c r="AA51" s="9" t="n"/>
+        <v>78.0856</v>
+      </c>
+      <c r="AA51" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="AB51" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AC51" s="5" t="inlineStr">
         <is>
-          <t>3:42:46.634404</t>
+          <t>10:47:31.810425</t>
         </is>
       </c>
       <c r="AD51" s="5" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1</t>
+          <t>outputs/RDT-CD/Run3</t>
         </is>
       </c>
       <c r="AE51" s="6" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1/S0/CDD/train_log.txt</t>
+          <t>outputs/RDT-CD/Run3/R3/SYSU/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>SCTC-Run1</t>
+          <t>RDT-CD-Run3</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -6585,22 +6555,22 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>S0</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>S0_Clean_A2Net_LWGANet_L0</t>
+          <t>R3_BT_SAM_RDT_Full</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=none</t>
+          <t>mode=bt_sam_rdt; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G52" s="5" t="n">
@@ -6633,9 +6603,13 @@
       </c>
       <c r="O52" s="7" t="n"/>
       <c r="P52" s="7" t="n"/>
-      <c r="Q52" s="5" t="n"/>
+      <c r="Q52" s="5" t="inlineStr">
+        <is>
+          <t>bt_sam_rdt</t>
+        </is>
+      </c>
       <c r="R52" s="8" t="n">
-        <v>2.9131</v>
+        <v>2.9269</v>
       </c>
       <c r="S52" s="8" t="n">
         <v>2.9131</v>
@@ -6644,47 +6618,49 @@
         <v>2.7676</v>
       </c>
       <c r="U52" s="8" t="n">
-        <v>89.4019</v>
+        <v>93.0294</v>
       </c>
       <c r="V52" s="8" t="n">
-        <v>92.447</v>
+        <v>94.3871</v>
       </c>
       <c r="W52" s="8" t="n">
-        <v>99.08799999999999</v>
+        <v>99.5039</v>
       </c>
       <c r="X52" s="8" t="n">
-        <v>90.8989</v>
+        <v>93.7033</v>
       </c>
       <c r="Y52" s="8" t="n">
-        <v>83.3163</v>
+        <v>88.1527</v>
       </c>
       <c r="Z52" s="8" t="n">
-        <v>90.41900000000001</v>
-      </c>
-      <c r="AA52" s="9" t="n"/>
+        <v>93.4452</v>
+      </c>
+      <c r="AA52" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="AB52" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AC52" s="5" t="inlineStr">
         <is>
-          <t>2:47:14.389924</t>
+          <t>4:27:10.216507</t>
         </is>
       </c>
       <c r="AD52" s="5" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1</t>
+          <t>outputs/RDT-CD/Run3</t>
         </is>
       </c>
       <c r="AE52" s="6" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1/S0/LEVIR/train_log.txt</t>
+          <t>outputs/RDT-CD/Run3/R3/WHU/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>SCTC-Run1</t>
+          <t>RDT-CD-Run3</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
@@ -6694,22 +6670,22 @@
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>S0</t>
+          <t>R3A</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>S0_Clean_A2Net_LWGANet_L0</t>
+          <t>R3A_BT_SAM_RDT_SAM_Only</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=none</t>
+          <t>mode=bt_sam_rdt; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G53" s="5" t="n">
@@ -6742,9 +6718,13 @@
       </c>
       <c r="O53" s="7" t="n"/>
       <c r="P53" s="7" t="n"/>
-      <c r="Q53" s="5" t="n"/>
+      <c r="Q53" s="5" t="inlineStr">
+        <is>
+          <t>bt_sam_rdt</t>
+        </is>
+      </c>
       <c r="R53" s="8" t="n">
-        <v>2.9131</v>
+        <v>2.9269</v>
       </c>
       <c r="S53" s="8" t="n">
         <v>2.9131</v>
@@ -6753,47 +6733,49 @@
         <v>2.7676</v>
       </c>
       <c r="U53" s="8" t="n">
-        <v>81.14139999999999</v>
+        <v>97.7008</v>
       </c>
       <c r="V53" s="8" t="n">
-        <v>84.9704</v>
+        <v>97.858</v>
       </c>
       <c r="W53" s="8" t="n">
-        <v>92.1679</v>
+        <v>99.4522</v>
       </c>
       <c r="X53" s="8" t="n">
-        <v>83.01180000000001</v>
+        <v>97.77930000000001</v>
       </c>
       <c r="Y53" s="8" t="n">
-        <v>70.9573</v>
+        <v>95.65519999999999</v>
       </c>
       <c r="Z53" s="8" t="n">
-        <v>77.92609999999999</v>
-      </c>
-      <c r="AA53" s="9" t="n"/>
+        <v>97.4669</v>
+      </c>
+      <c r="AA53" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="AB53" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AC53" s="5" t="inlineStr">
         <is>
-          <t>2:20:47.929272</t>
+          <t>11:25:23.866980</t>
         </is>
       </c>
       <c r="AD53" s="5" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1</t>
+          <t>outputs/RDT-CD/Run3</t>
         </is>
       </c>
       <c r="AE53" s="6" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1/S0/SYSU/train_log.txt</t>
+          <t>outputs/RDT-CD/Run3/R3A/CDD/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>SCTC-Run1</t>
+          <t>RDT-CD-Run3</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
@@ -6803,22 +6785,22 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>S0</t>
+          <t>R3A</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>S0_Clean_A2Net_LWGANet_L0</t>
+          <t>R3A_BT_SAM_RDT_SAM_Only</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=none</t>
+          <t>mode=bt_sam_rdt; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G54" s="5" t="n">
@@ -6851,9 +6833,13 @@
       </c>
       <c r="O54" s="7" t="n"/>
       <c r="P54" s="7" t="n"/>
-      <c r="Q54" s="5" t="n"/>
+      <c r="Q54" s="5" t="inlineStr">
+        <is>
+          <t>bt_sam_rdt</t>
+        </is>
+      </c>
       <c r="R54" s="8" t="n">
-        <v>2.9131</v>
+        <v>2.9269</v>
       </c>
       <c r="S54" s="8" t="n">
         <v>2.9131</v>
@@ -6862,47 +6848,49 @@
         <v>2.7676</v>
       </c>
       <c r="U54" s="8" t="n">
-        <v>91.9434</v>
+        <v>90.7855</v>
       </c>
       <c r="V54" s="8" t="n">
-        <v>95.20650000000001</v>
+        <v>91.2675</v>
       </c>
       <c r="W54" s="8" t="n">
-        <v>99.4967</v>
+        <v>99.0881</v>
       </c>
       <c r="X54" s="8" t="n">
-        <v>93.54649999999999</v>
+        <v>91.0258</v>
       </c>
       <c r="Y54" s="8" t="n">
-        <v>87.87549999999999</v>
+        <v>83.52979999999999</v>
       </c>
       <c r="Z54" s="8" t="n">
-        <v>93.2847</v>
-      </c>
-      <c r="AA54" s="9" t="n"/>
+        <v>90.5455</v>
+      </c>
+      <c r="AA54" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="AB54" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AC54" s="5" t="inlineStr">
         <is>
-          <t>2:43:01.630317</t>
+          <t>5:37:16.217701</t>
         </is>
       </c>
       <c r="AD54" s="5" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1</t>
+          <t>outputs/RDT-CD/Run3</t>
         </is>
       </c>
       <c r="AE54" s="6" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1/S0/WHU/train_log.txt</t>
+          <t>outputs/RDT-CD/Run3/R3A/LEVIR/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>SCTC-Run1</t>
+          <t>RDT-CD-Run3</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
@@ -6912,22 +6900,22 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>R3A</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>S1_FullPixel_Symmetric_Calibration</t>
+          <t>R3A_BT_SAM_RDT_SAM_Only</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=symmetric</t>
+          <t>mode=bt_sam_rdt; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G55" s="5" t="n">
@@ -6960,9 +6948,13 @@
       </c>
       <c r="O55" s="7" t="n"/>
       <c r="P55" s="7" t="n"/>
-      <c r="Q55" s="5" t="n"/>
+      <c r="Q55" s="5" t="inlineStr">
+        <is>
+          <t>bt_sam_rdt</t>
+        </is>
+      </c>
       <c r="R55" s="8" t="n">
-        <v>2.9131</v>
+        <v>2.9269</v>
       </c>
       <c r="S55" s="8" t="n">
         <v>2.9131</v>
@@ -6971,47 +6963,49 @@
         <v>2.7676</v>
       </c>
       <c r="U55" s="8" t="n">
-        <v>97.39619999999999</v>
+        <v>77.91940000000001</v>
       </c>
       <c r="V55" s="8" t="n">
-        <v>97.7011</v>
+        <v>87.1811</v>
       </c>
       <c r="W55" s="8" t="n">
-        <v>99.39570000000001</v>
+        <v>92.0909</v>
       </c>
       <c r="X55" s="8" t="n">
-        <v>97.5484</v>
+        <v>82.29049999999999</v>
       </c>
       <c r="Y55" s="8" t="n">
-        <v>95.21420000000001</v>
+        <v>69.9098</v>
       </c>
       <c r="Z55" s="8" t="n">
-        <v>97.2038</v>
-      </c>
-      <c r="AA55" s="9" t="n"/>
+        <v>77.2196</v>
+      </c>
+      <c r="AA55" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="AB55" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AC55" s="5" t="inlineStr">
         <is>
-          <t>3:19:01.505607</t>
+          <t>10:51:06.656145</t>
         </is>
       </c>
       <c r="AD55" s="5" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1</t>
+          <t>outputs/RDT-CD/Run3</t>
         </is>
       </c>
       <c r="AE55" s="6" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1/S1/CDD/train_log.txt</t>
+          <t>outputs/RDT-CD/Run3/R3A/SYSU/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>SCTC-Run1</t>
+          <t>RDT-CD-Run3</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
@@ -7021,22 +7015,22 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>R3A</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>S1_FullPixel_Symmetric_Calibration</t>
+          <t>R3A_BT_SAM_RDT_SAM_Only</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=symmetric</t>
+          <t>mode=bt_sam_rdt; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G56" s="5" t="n">
@@ -7069,9 +7063,13 @@
       </c>
       <c r="O56" s="7" t="n"/>
       <c r="P56" s="7" t="n"/>
-      <c r="Q56" s="5" t="n"/>
+      <c r="Q56" s="5" t="inlineStr">
+        <is>
+          <t>bt_sam_rdt</t>
+        </is>
+      </c>
       <c r="R56" s="8" t="n">
-        <v>2.9131</v>
+        <v>2.9269</v>
       </c>
       <c r="S56" s="8" t="n">
         <v>2.9131</v>
@@ -7080,47 +7078,49 @@
         <v>2.7676</v>
       </c>
       <c r="U56" s="8" t="n">
-        <v>89.7944</v>
+        <v>93.08840000000001</v>
       </c>
       <c r="V56" s="8" t="n">
-        <v>92.1617</v>
+        <v>94.8141</v>
       </c>
       <c r="W56" s="8" t="n">
-        <v>99.0911</v>
+        <v>99.52379999999999</v>
       </c>
       <c r="X56" s="8" t="n">
-        <v>90.96260000000001</v>
+        <v>93.94329999999999</v>
       </c>
       <c r="Y56" s="8" t="n">
-        <v>83.4233</v>
+        <v>88.5784</v>
       </c>
       <c r="Z56" s="8" t="n">
-        <v>90.4842</v>
-      </c>
-      <c r="AA56" s="9" t="n"/>
+        <v>93.6955</v>
+      </c>
+      <c r="AA56" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="AB56" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AC56" s="5" t="inlineStr">
         <is>
-          <t>0:33:15.349976</t>
+          <t>4:29:12.633871</t>
         </is>
       </c>
       <c r="AD56" s="5" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1</t>
+          <t>outputs/RDT-CD/Run3</t>
         </is>
       </c>
       <c r="AE56" s="6" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1/S1/LEVIR/train_log.txt</t>
+          <t>outputs/RDT-CD/Run3/R3A/WHU/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>SCTC-Run1</t>
+          <t>RDT-CD-Run3</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
@@ -7130,12 +7130,12 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>R3O</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>S1_FullPixel_Symmetric_Calibration</t>
+          <t>R3O_BT_SAM_RDT_OV_Only</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=symmetric</t>
+          <t>mode=bt_sam_rdt; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G57" s="5" t="n">
@@ -7178,9 +7178,13 @@
       </c>
       <c r="O57" s="7" t="n"/>
       <c r="P57" s="7" t="n"/>
-      <c r="Q57" s="5" t="n"/>
+      <c r="Q57" s="5" t="inlineStr">
+        <is>
+          <t>bt_sam_rdt</t>
+        </is>
+      </c>
       <c r="R57" s="8" t="n">
-        <v>2.9131</v>
+        <v>2.9269</v>
       </c>
       <c r="S57" s="8" t="n">
         <v>2.9131</v>
@@ -7189,47 +7193,49 @@
         <v>2.7676</v>
       </c>
       <c r="U57" s="8" t="n">
-        <v>80.42610000000001</v>
+        <v>79.3635</v>
       </c>
       <c r="V57" s="8" t="n">
-        <v>85.6097</v>
+        <v>86.4628</v>
       </c>
       <c r="W57" s="8" t="n">
-        <v>92.19580000000001</v>
+        <v>92.203</v>
       </c>
       <c r="X57" s="8" t="n">
-        <v>82.93700000000001</v>
+        <v>82.7612</v>
       </c>
       <c r="Y57" s="8" t="n">
-        <v>70.8481</v>
+        <v>70.592</v>
       </c>
       <c r="Z57" s="8" t="n">
-        <v>77.8843</v>
-      </c>
-      <c r="AA57" s="9" t="n"/>
+        <v>77.7353</v>
+      </c>
+      <c r="AA57" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="AB57" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AC57" s="5" t="inlineStr">
         <is>
-          <t>3:32:56.072083</t>
+          <t>7:05:18.102962</t>
         </is>
       </c>
       <c r="AD57" s="5" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1</t>
+          <t>outputs/RDT-CD/Run3</t>
         </is>
       </c>
       <c r="AE57" s="6" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1/S1/SYSU/train_log.txt</t>
+          <t>outputs/RDT-CD/Run3/R3O/SYSU/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>SCTC-Run1</t>
+          <t>RDT-CD-Run3</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
@@ -7239,12 +7245,12 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>R3O</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>S1_FullPixel_Symmetric_Calibration</t>
+          <t>R3O_BT_SAM_RDT_OV_Only</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -7254,7 +7260,7 @@
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=symmetric</t>
+          <t>mode=bt_sam_rdt; batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G58" s="5" t="n">
@@ -7287,9 +7293,13 @@
       </c>
       <c r="O58" s="7" t="n"/>
       <c r="P58" s="7" t="n"/>
-      <c r="Q58" s="5" t="n"/>
+      <c r="Q58" s="5" t="inlineStr">
+        <is>
+          <t>bt_sam_rdt</t>
+        </is>
+      </c>
       <c r="R58" s="8" t="n">
-        <v>2.9131</v>
+        <v>2.9269</v>
       </c>
       <c r="S58" s="8" t="n">
         <v>2.9131</v>
@@ -7298,40 +7308,42 @@
         <v>2.7676</v>
       </c>
       <c r="U58" s="8" t="n">
-        <v>92.1589</v>
+        <v>91.0621</v>
       </c>
       <c r="V58" s="8" t="n">
-        <v>95.1091</v>
+        <v>95.70359999999999</v>
       </c>
       <c r="W58" s="8" t="n">
-        <v>99.5009</v>
+        <v>99.48320000000001</v>
       </c>
       <c r="X58" s="8" t="n">
-        <v>93.61070000000001</v>
+        <v>93.3252</v>
       </c>
       <c r="Y58" s="8" t="n">
-        <v>87.9889</v>
+        <v>87.48559999999999</v>
       </c>
       <c r="Z58" s="8" t="n">
-        <v>93.3511</v>
-      </c>
-      <c r="AA58" s="9" t="n"/>
+        <v>93.0565</v>
+      </c>
+      <c r="AA58" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="AB58" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AC58" s="5" t="inlineStr">
         <is>
-          <t>2:40:44.864364</t>
+          <t>3:37:24.949796</t>
         </is>
       </c>
       <c r="AD58" s="5" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1</t>
+          <t>outputs/RDT-CD/Run3</t>
         </is>
       </c>
       <c r="AE58" s="6" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1/S1/WHU/train_log.txt</t>
+          <t>outputs/RDT-CD/Run3/R3O/WHU/train_log.txt</t>
         </is>
       </c>
     </row>
@@ -7348,12 +7360,12 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S0</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>S2_SCTC_UnchangedAware_Symmetric_CrossTemporal_Calibration</t>
+          <t>S0_Clean_A2Net_LWGANet_L0</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -7363,7 +7375,7 @@
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=sctc</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=none</t>
         </is>
       </c>
       <c r="G59" s="5" t="n">
@@ -7407,22 +7419,22 @@
         <v>2.7676</v>
       </c>
       <c r="U59" s="8" t="n">
-        <v>97.4438</v>
+        <v>97.68770000000001</v>
       </c>
       <c r="V59" s="8" t="n">
-        <v>97.71940000000001</v>
+        <v>97.8814</v>
       </c>
       <c r="W59" s="8" t="n">
-        <v>99.4038</v>
+        <v>99.45359999999999</v>
       </c>
       <c r="X59" s="8" t="n">
-        <v>97.5814</v>
+        <v>97.78449999999999</v>
       </c>
       <c r="Y59" s="8" t="n">
-        <v>95.277</v>
+        <v>95.66500000000001</v>
       </c>
       <c r="Z59" s="8" t="n">
-        <v>97.2414</v>
+        <v>97.47280000000001</v>
       </c>
       <c r="AA59" s="9" t="n"/>
       <c r="AB59" s="9" t="n">
@@ -7430,7 +7442,7 @@
       </c>
       <c r="AC59" s="5" t="inlineStr">
         <is>
-          <t>2:52:30.285254</t>
+          <t>3:42:46.634404</t>
         </is>
       </c>
       <c r="AD59" s="5" t="inlineStr">
@@ -7440,7 +7452,7 @@
       </c>
       <c r="AE59" s="6" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1/S2/CDD/train_log.txt</t>
+          <t>outputs/SCTC/Run1/S0/CDD/train_log.txt</t>
         </is>
       </c>
     </row>
@@ -7457,12 +7469,12 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S0</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>S2_SCTC_UnchangedAware_Symmetric_CrossTemporal_Calibration</t>
+          <t>S0_Clean_A2Net_LWGANet_L0</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -7472,7 +7484,7 @@
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=sctc</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=none</t>
         </is>
       </c>
       <c r="G60" s="5" t="n">
@@ -7516,22 +7528,22 @@
         <v>2.7676</v>
       </c>
       <c r="U60" s="8" t="n">
-        <v>90.1421</v>
+        <v>89.4019</v>
       </c>
       <c r="V60" s="8" t="n">
-        <v>91.4601</v>
+        <v>92.447</v>
       </c>
       <c r="W60" s="8" t="n">
-        <v>99.069</v>
+        <v>99.08799999999999</v>
       </c>
       <c r="X60" s="8" t="n">
-        <v>90.7963</v>
+        <v>90.8989</v>
       </c>
       <c r="Y60" s="8" t="n">
-        <v>83.14399999999999</v>
+        <v>83.3163</v>
       </c>
       <c r="Z60" s="8" t="n">
-        <v>90.3061</v>
+        <v>90.41900000000001</v>
       </c>
       <c r="AA60" s="9" t="n"/>
       <c r="AB60" s="9" t="n">
@@ -7539,7 +7551,7 @@
       </c>
       <c r="AC60" s="5" t="inlineStr">
         <is>
-          <t>3:18:11.767618</t>
+          <t>2:47:14.389924</t>
         </is>
       </c>
       <c r="AD60" s="5" t="inlineStr">
@@ -7549,7 +7561,7 @@
       </c>
       <c r="AE60" s="6" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1/S2/LEVIR/train_log.txt</t>
+          <t>outputs/SCTC/Run1/S0/LEVIR/train_log.txt</t>
         </is>
       </c>
     </row>
@@ -7566,12 +7578,12 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S0</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>S2_SCTC_UnchangedAware_Symmetric_CrossTemporal_Calibration</t>
+          <t>S0_Clean_A2Net_LWGANet_L0</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -7581,7 +7593,7 @@
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=sctc</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=none</t>
         </is>
       </c>
       <c r="G61" s="5" t="n">
@@ -7625,22 +7637,22 @@
         <v>2.7676</v>
       </c>
       <c r="U61" s="8" t="n">
-        <v>81.00070000000001</v>
+        <v>81.14139999999999</v>
       </c>
       <c r="V61" s="8" t="n">
-        <v>84.595</v>
+        <v>84.9704</v>
       </c>
       <c r="W61" s="8" t="n">
-        <v>92.04090000000001</v>
+        <v>92.1679</v>
       </c>
       <c r="X61" s="8" t="n">
-        <v>82.75879999999999</v>
+        <v>83.01180000000001</v>
       </c>
       <c r="Y61" s="8" t="n">
-        <v>70.5885</v>
+        <v>70.9573</v>
       </c>
       <c r="Z61" s="8" t="n">
-        <v>77.5882</v>
+        <v>77.92609999999999</v>
       </c>
       <c r="AA61" s="9" t="n"/>
       <c r="AB61" s="9" t="n">
@@ -7648,7 +7660,7 @@
       </c>
       <c r="AC61" s="5" t="inlineStr">
         <is>
-          <t>4:06:34.060509</t>
+          <t>2:20:47.929272</t>
         </is>
       </c>
       <c r="AD61" s="5" t="inlineStr">
@@ -7658,7 +7670,7 @@
       </c>
       <c r="AE61" s="6" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1/S2/SYSU/train_log.txt</t>
+          <t>outputs/SCTC/Run1/S0/SYSU/train_log.txt</t>
         </is>
       </c>
     </row>
@@ -7675,12 +7687,12 @@
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S0</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>S2_SCTC_UnchangedAware_Symmetric_CrossTemporal_Calibration</t>
+          <t>S0_Clean_A2Net_LWGANet_L0</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -7690,7 +7702,7 @@
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=sctc</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=none</t>
         </is>
       </c>
       <c r="G62" s="5" t="n">
@@ -7734,22 +7746,22 @@
         <v>2.7676</v>
       </c>
       <c r="U62" s="8" t="n">
-        <v>92.7942</v>
+        <v>91.9434</v>
       </c>
       <c r="V62" s="8" t="n">
-        <v>95.1825</v>
+        <v>95.20650000000001</v>
       </c>
       <c r="W62" s="8" t="n">
-        <v>99.5278</v>
+        <v>99.4967</v>
       </c>
       <c r="X62" s="8" t="n">
-        <v>93.9731</v>
+        <v>93.54649999999999</v>
       </c>
       <c r="Y62" s="8" t="n">
-        <v>88.6315</v>
+        <v>87.87549999999999</v>
       </c>
       <c r="Z62" s="8" t="n">
-        <v>93.7274</v>
+        <v>93.2847</v>
       </c>
       <c r="AA62" s="9" t="n"/>
       <c r="AB62" s="9" t="n">
@@ -7757,22 +7769,894 @@
       </c>
       <c r="AC62" s="5" t="inlineStr">
         <is>
+          <t>2:43:01.630317</t>
+        </is>
+      </c>
+      <c r="AD62" s="5" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="AE62" s="6" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S0/WHU/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>SCTC-Run1</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>S1_FullPixel_Symmetric_Calibration</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=symmetric</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H63" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I63" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J63" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L63" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M63" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N63" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O63" s="7" t="n"/>
+      <c r="P63" s="7" t="n"/>
+      <c r="Q63" s="5" t="n"/>
+      <c r="R63" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S63" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v>97.39619999999999</v>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v>97.7011</v>
+      </c>
+      <c r="W63" s="8" t="n">
+        <v>99.39570000000001</v>
+      </c>
+      <c r="X63" s="8" t="n">
+        <v>97.5484</v>
+      </c>
+      <c r="Y63" s="8" t="n">
+        <v>95.21420000000001</v>
+      </c>
+      <c r="Z63" s="8" t="n">
+        <v>97.2038</v>
+      </c>
+      <c r="AA63" s="9" t="n"/>
+      <c r="AB63" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="5" t="inlineStr">
+        <is>
+          <t>3:19:01.505607</t>
+        </is>
+      </c>
+      <c r="AD63" s="5" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="AE63" s="6" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S1/CDD/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>SCTC-Run1</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>S1_FullPixel_Symmetric_Calibration</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=symmetric</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H64" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J64" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L64" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M64" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N64" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O64" s="7" t="n"/>
+      <c r="P64" s="7" t="n"/>
+      <c r="Q64" s="5" t="n"/>
+      <c r="R64" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S64" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T64" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U64" s="8" t="n">
+        <v>89.7944</v>
+      </c>
+      <c r="V64" s="8" t="n">
+        <v>92.1617</v>
+      </c>
+      <c r="W64" s="8" t="n">
+        <v>99.0911</v>
+      </c>
+      <c r="X64" s="8" t="n">
+        <v>90.96260000000001</v>
+      </c>
+      <c r="Y64" s="8" t="n">
+        <v>83.4233</v>
+      </c>
+      <c r="Z64" s="8" t="n">
+        <v>90.4842</v>
+      </c>
+      <c r="AA64" s="9" t="n"/>
+      <c r="AB64" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="5" t="inlineStr">
+        <is>
+          <t>0:33:15.349976</t>
+        </is>
+      </c>
+      <c r="AD64" s="5" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="AE64" s="6" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S1/LEVIR/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>SCTC-Run1</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>S1_FullPixel_Symmetric_Calibration</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=symmetric</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J65" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L65" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M65" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N65" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O65" s="7" t="n"/>
+      <c r="P65" s="7" t="n"/>
+      <c r="Q65" s="5" t="n"/>
+      <c r="R65" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S65" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T65" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U65" s="8" t="n">
+        <v>80.42610000000001</v>
+      </c>
+      <c r="V65" s="8" t="n">
+        <v>85.6097</v>
+      </c>
+      <c r="W65" s="8" t="n">
+        <v>92.19580000000001</v>
+      </c>
+      <c r="X65" s="8" t="n">
+        <v>82.93700000000001</v>
+      </c>
+      <c r="Y65" s="8" t="n">
+        <v>70.8481</v>
+      </c>
+      <c r="Z65" s="8" t="n">
+        <v>77.8843</v>
+      </c>
+      <c r="AA65" s="9" t="n"/>
+      <c r="AB65" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="5" t="inlineStr">
+        <is>
+          <t>3:32:56.072083</t>
+        </is>
+      </c>
+      <c r="AD65" s="5" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="AE65" s="6" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S1/SYSU/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="30" customHeight="1">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>SCTC-Run1</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>S1_FullPixel_Symmetric_Calibration</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=symmetric</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J66" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K66" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L66" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M66" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N66" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O66" s="7" t="n"/>
+      <c r="P66" s="7" t="n"/>
+      <c r="Q66" s="5" t="n"/>
+      <c r="R66" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S66" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T66" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U66" s="8" t="n">
+        <v>92.1589</v>
+      </c>
+      <c r="V66" s="8" t="n">
+        <v>95.1091</v>
+      </c>
+      <c r="W66" s="8" t="n">
+        <v>99.5009</v>
+      </c>
+      <c r="X66" s="8" t="n">
+        <v>93.61070000000001</v>
+      </c>
+      <c r="Y66" s="8" t="n">
+        <v>87.9889</v>
+      </c>
+      <c r="Z66" s="8" t="n">
+        <v>93.3511</v>
+      </c>
+      <c r="AA66" s="9" t="n"/>
+      <c r="AB66" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC66" s="5" t="inlineStr">
+        <is>
+          <t>2:40:44.864364</t>
+        </is>
+      </c>
+      <c r="AD66" s="5" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="AE66" s="6" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S1/WHU/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="30" customHeight="1">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>SCTC-Run1</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>S2_SCTC_UnchangedAware_Symmetric_CrossTemporal_Calibration</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=sctc</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I67" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J67" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L67" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M67" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N67" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O67" s="7" t="n"/>
+      <c r="P67" s="7" t="n"/>
+      <c r="Q67" s="5" t="n"/>
+      <c r="R67" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S67" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T67" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U67" s="8" t="n">
+        <v>97.4438</v>
+      </c>
+      <c r="V67" s="8" t="n">
+        <v>97.71940000000001</v>
+      </c>
+      <c r="W67" s="8" t="n">
+        <v>99.4038</v>
+      </c>
+      <c r="X67" s="8" t="n">
+        <v>97.5814</v>
+      </c>
+      <c r="Y67" s="8" t="n">
+        <v>95.277</v>
+      </c>
+      <c r="Z67" s="8" t="n">
+        <v>97.2414</v>
+      </c>
+      <c r="AA67" s="9" t="n"/>
+      <c r="AB67" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC67" s="5" t="inlineStr">
+        <is>
+          <t>2:52:30.285254</t>
+        </is>
+      </c>
+      <c r="AD67" s="5" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="AE67" s="6" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S2/CDD/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>SCTC-Run1</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>S2_SCTC_UnchangedAware_Symmetric_CrossTemporal_Calibration</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=sctc</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H68" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I68" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J68" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L68" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M68" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N68" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O68" s="7" t="n"/>
+      <c r="P68" s="7" t="n"/>
+      <c r="Q68" s="5" t="n"/>
+      <c r="R68" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S68" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T68" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U68" s="8" t="n">
+        <v>90.1421</v>
+      </c>
+      <c r="V68" s="8" t="n">
+        <v>91.4601</v>
+      </c>
+      <c r="W68" s="8" t="n">
+        <v>99.069</v>
+      </c>
+      <c r="X68" s="8" t="n">
+        <v>90.7963</v>
+      </c>
+      <c r="Y68" s="8" t="n">
+        <v>83.14399999999999</v>
+      </c>
+      <c r="Z68" s="8" t="n">
+        <v>90.3061</v>
+      </c>
+      <c r="AA68" s="9" t="n"/>
+      <c r="AB68" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="5" t="inlineStr">
+        <is>
+          <t>3:18:11.767618</t>
+        </is>
+      </c>
+      <c r="AD68" s="5" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="AE68" s="6" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S2/LEVIR/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>SCTC-Run1</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>S2_SCTC_UnchangedAware_Symmetric_CrossTemporal_Calibration</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=sctc</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J69" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L69" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M69" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N69" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O69" s="7" t="n"/>
+      <c r="P69" s="7" t="n"/>
+      <c r="Q69" s="5" t="n"/>
+      <c r="R69" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S69" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T69" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U69" s="8" t="n">
+        <v>81.00070000000001</v>
+      </c>
+      <c r="V69" s="8" t="n">
+        <v>84.595</v>
+      </c>
+      <c r="W69" s="8" t="n">
+        <v>92.04090000000001</v>
+      </c>
+      <c r="X69" s="8" t="n">
+        <v>82.75879999999999</v>
+      </c>
+      <c r="Y69" s="8" t="n">
+        <v>70.5885</v>
+      </c>
+      <c r="Z69" s="8" t="n">
+        <v>77.5882</v>
+      </c>
+      <c r="AA69" s="9" t="n"/>
+      <c r="AB69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC69" s="5" t="inlineStr">
+        <is>
+          <t>4:06:34.060509</t>
+        </is>
+      </c>
+      <c r="AD69" s="5" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="AE69" s="6" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S2/SYSU/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>SCTC-Run1</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>S2_SCTC_UnchangedAware_Symmetric_CrossTemporal_Calibration</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=sctc</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H70" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I70" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J70" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K70" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L70" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M70" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N70" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O70" s="7" t="n"/>
+      <c r="P70" s="7" t="n"/>
+      <c r="Q70" s="5" t="n"/>
+      <c r="R70" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S70" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T70" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U70" s="8" t="n">
+        <v>92.7942</v>
+      </c>
+      <c r="V70" s="8" t="n">
+        <v>95.1825</v>
+      </c>
+      <c r="W70" s="8" t="n">
+        <v>99.5278</v>
+      </c>
+      <c r="X70" s="8" t="n">
+        <v>93.9731</v>
+      </c>
+      <c r="Y70" s="8" t="n">
+        <v>88.6315</v>
+      </c>
+      <c r="Z70" s="8" t="n">
+        <v>93.7274</v>
+      </c>
+      <c r="AA70" s="9" t="n"/>
+      <c r="AB70" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="5" t="inlineStr">
+        <is>
           <t>2:08:54.218613</t>
         </is>
       </c>
-      <c r="AD62" s="5" t="inlineStr">
+      <c r="AD70" s="5" t="inlineStr">
         <is>
           <t>outputs/SCTC/Run1</t>
         </is>
       </c>
-      <c r="AE62" s="6" t="inlineStr">
+      <c r="AE70" s="6" t="inlineStr">
         <is>
           <t>outputs/SCTC/Run1/S2/WHU/train_log.txt</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="X2:X62">
+  <conditionalFormatting sqref="X2:X70">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -7797,7 +8681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C62"/>
+  <dimension ref="A1:C70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -8859,6 +9743,142 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t>outputs/FA-SCRD/Run1</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="inlineStr">
+        <is>
+          <t>outputs/FA-SCRD/Run1/A1/CDD/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C63" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t>outputs/FA-SCRD/Run1</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t>outputs/FA-SCRD/Run1/A1/SYSU/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C64" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>outputs/FA-SCRD/Run1</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t>outputs/FA-SCRD/Run1/C0/CDD/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C65" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t>outputs/FA-SCRD/Run1</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="inlineStr">
+        <is>
+          <t>outputs/FA-SCRD/Run1/C0/SYSU/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C66" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t>outputs/FA-SCRD/Run1</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="inlineStr">
+        <is>
+          <t>outputs/FA-SCRD/Run1/C1/CDD/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C67" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="11" t="inlineStr">
+        <is>
+          <t>outputs/FA-SCRD/Run1</t>
+        </is>
+      </c>
+      <c r="B68" s="11" t="inlineStr">
+        <is>
+          <t>outputs/FA-SCRD/Run1/C1/SYSU/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C68" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="11" t="inlineStr">
+        <is>
+          <t>outputs/FA-SCRD/Run1</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t>outputs/FA-SCRD/Run1/M1/CDD/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C69" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="11" t="inlineStr">
+        <is>
+          <t>outputs/FA-SCRD/Run1</t>
+        </is>
+      </c>
+      <c r="B70" s="11" t="inlineStr">
+        <is>
+          <t>outputs/FA-SCRD/Run1/M1/SYSU/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C70" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -188,8 +188,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ExperimentResultsTable" displayName="ExperimentResultsTable" ref="A1:AE70" headerRowCount="1">
-  <autoFilter ref="A1:AE70"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ExperimentResultsTable" displayName="ExperimentResultsTable" ref="A1:AE76" headerRowCount="1">
+  <autoFilter ref="A1:AE76"/>
   <tableColumns count="31">
     <tableColumn id="1" name="Run"/>
     <tableColumn id="2" name="Stage"/>
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>LS-Rep_BCD_RSML_3 — Experiment Metrics (DART-R / RDT-CD / SCTC / FA-SCRD)</t>
+          <t>LS-Rep_BCD_RSML_3 — Experiment Metrics (DART-R / RDT-CD / SCTC / FA-SCRD / SAGE-CD)</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 10:05:46 +0800</t>
+          <t>2026-09-23 08:49:08 +0800</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8">
@@ -596,7 +596,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>DART-R=8, DART-R-TS=4, FA-SCRD-Run1=8, RDT-CD-Run1=12, RDT-CD-Run2=11, RDT-CD-Run3=14, SCTC-Run1=12</t>
+          <t>DART-R=8, DART-R-TS=4, FA-SCRD-Run1=8, RDT-CD-Run1=12, RDT-CD-Run2=11, RDT-CD-Run3=14, SAGE-CD-Run1=6, SCTC-Run1=12</t>
         </is>
       </c>
     </row>
@@ -633,6 +633,18 @@
       <c r="B11" s="3" t="inlineStr">
         <is>
           <t>FA-SCRD-Run1: C0=clean, C1=joint temporal BN, A1=fixed DINOv3 teacher relation KD, M1=+failure-aware weighting. A1-C1 = SYSU -0.33 / CDD -0.33 → teacher transfer negative (not a trick, a straight loss). WHU/LEVIR stopped early (C0 only). 40k, seed 2333 only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>SAGE-CD scope</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>SAGE-CD-Run1 (Safe-DINO gate): G0=clean, G1=joint temporal BN, G2=full-res DINO semantic target + aux head + logit standardization + gradient budget. G2-G1 = WHU +0.46 / SYSU -0.25 → gate FAIL (SYSU), WHU-only again; but KD mechanism fixed (kd 12-15→0.6, grad budget ~25%). 40k, seed 2333 only.</t>
         </is>
       </c>
     </row>
@@ -647,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE70"/>
+  <dimension ref="A1:AE76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -7350,7 +7362,7 @@
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>SCTC-Run1</t>
+          <t>SAGE-CD-Run1</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
@@ -7360,22 +7372,22 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>S0</t>
+          <t>G0</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>S0_Clean_A2Net_LWGANet_L0</t>
+          <t>G0_Clean</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=none</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G59" s="5" t="n">
@@ -7419,22 +7431,22 @@
         <v>2.7676</v>
       </c>
       <c r="U59" s="8" t="n">
-        <v>97.68770000000001</v>
+        <v>79.4944</v>
       </c>
       <c r="V59" s="8" t="n">
-        <v>97.8814</v>
+        <v>85.69109999999999</v>
       </c>
       <c r="W59" s="8" t="n">
-        <v>99.45359999999999</v>
+        <v>92.0338</v>
       </c>
       <c r="X59" s="8" t="n">
-        <v>97.78449999999999</v>
+        <v>82.4765</v>
       </c>
       <c r="Y59" s="8" t="n">
-        <v>95.66500000000001</v>
+        <v>70.1788</v>
       </c>
       <c r="Z59" s="8" t="n">
-        <v>97.47280000000001</v>
+        <v>77.33109999999999</v>
       </c>
       <c r="AA59" s="9" t="n"/>
       <c r="AB59" s="9" t="n">
@@ -7442,24 +7454,24 @@
       </c>
       <c r="AC59" s="5" t="inlineStr">
         <is>
-          <t>3:42:46.634404</t>
+          <t>2:41:15.108891</t>
         </is>
       </c>
       <c r="AD59" s="5" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1</t>
+          <t>outputs/SAGE-CD/Run1</t>
         </is>
       </c>
       <c r="AE59" s="6" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1/S0/CDD/train_log.txt</t>
+          <t>outputs/SAGE-CD/Run1/G0/SYSU/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>SCTC-Run1</t>
+          <t>SAGE-CD-Run1</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
@@ -7469,22 +7481,22 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>S0</t>
+          <t>G0</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>S0_Clean_A2Net_LWGANet_L0</t>
+          <t>G0_Clean</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=none</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G60" s="5" t="n">
@@ -7528,22 +7540,22 @@
         <v>2.7676</v>
       </c>
       <c r="U60" s="8" t="n">
-        <v>89.4019</v>
+        <v>90.9233</v>
       </c>
       <c r="V60" s="8" t="n">
-        <v>92.447</v>
+        <v>94.7227</v>
       </c>
       <c r="W60" s="8" t="n">
-        <v>99.08799999999999</v>
+        <v>99.43889999999999</v>
       </c>
       <c r="X60" s="8" t="n">
-        <v>90.8989</v>
+        <v>92.78410000000001</v>
       </c>
       <c r="Y60" s="8" t="n">
-        <v>83.3163</v>
+        <v>86.5395</v>
       </c>
       <c r="Z60" s="8" t="n">
-        <v>90.41900000000001</v>
+        <v>92.4923</v>
       </c>
       <c r="AA60" s="9" t="n"/>
       <c r="AB60" s="9" t="n">
@@ -7551,24 +7563,24 @@
       </c>
       <c r="AC60" s="5" t="inlineStr">
         <is>
-          <t>2:47:14.389924</t>
+          <t>2:52:00.611810</t>
         </is>
       </c>
       <c r="AD60" s="5" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1</t>
+          <t>outputs/SAGE-CD/Run1</t>
         </is>
       </c>
       <c r="AE60" s="6" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1/S0/LEVIR/train_log.txt</t>
+          <t>outputs/SAGE-CD/Run1/G0/WHU/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>SCTC-Run1</t>
+          <t>SAGE-CD-Run1</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
@@ -7578,12 +7590,12 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>S0</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>S0_Clean_A2Net_LWGANet_L0</t>
+          <t>G1_JointBN</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -7593,7 +7605,7 @@
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=none</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G61" s="5" t="n">
@@ -7637,22 +7649,22 @@
         <v>2.7676</v>
       </c>
       <c r="U61" s="8" t="n">
-        <v>81.14139999999999</v>
+        <v>81.35080000000001</v>
       </c>
       <c r="V61" s="8" t="n">
-        <v>84.9704</v>
+        <v>84.13030000000001</v>
       </c>
       <c r="W61" s="8" t="n">
-        <v>92.1679</v>
+        <v>91.98309999999999</v>
       </c>
       <c r="X61" s="8" t="n">
-        <v>83.01180000000001</v>
+        <v>82.71720000000001</v>
       </c>
       <c r="Y61" s="8" t="n">
-        <v>70.9573</v>
+        <v>70.52800000000001</v>
       </c>
       <c r="Z61" s="8" t="n">
-        <v>77.92609999999999</v>
+        <v>77.5003</v>
       </c>
       <c r="AA61" s="9" t="n"/>
       <c r="AB61" s="9" t="n">
@@ -7660,24 +7672,24 @@
       </c>
       <c r="AC61" s="5" t="inlineStr">
         <is>
-          <t>2:20:47.929272</t>
+          <t>2:50:23.439626</t>
         </is>
       </c>
       <c r="AD61" s="5" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1</t>
+          <t>outputs/SAGE-CD/Run1</t>
         </is>
       </c>
       <c r="AE61" s="6" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1/S0/SYSU/train_log.txt</t>
+          <t>outputs/SAGE-CD/Run1/G1/SYSU/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>SCTC-Run1</t>
+          <t>SAGE-CD-Run1</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
@@ -7687,12 +7699,12 @@
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>S0</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>S0_Clean_A2Net_LWGANet_L0</t>
+          <t>G1_JointBN</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -7702,7 +7714,7 @@
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=none</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G62" s="5" t="n">
@@ -7746,22 +7758,22 @@
         <v>2.7676</v>
       </c>
       <c r="U62" s="8" t="n">
-        <v>91.9434</v>
+        <v>91.2881</v>
       </c>
       <c r="V62" s="8" t="n">
-        <v>95.20650000000001</v>
+        <v>96.3824</v>
       </c>
       <c r="W62" s="8" t="n">
-        <v>99.4967</v>
+        <v>99.5184</v>
       </c>
       <c r="X62" s="8" t="n">
-        <v>93.54649999999999</v>
+        <v>93.76609999999999</v>
       </c>
       <c r="Y62" s="8" t="n">
-        <v>87.87549999999999</v>
+        <v>88.2638</v>
       </c>
       <c r="Z62" s="8" t="n">
-        <v>93.2847</v>
+        <v>93.5158</v>
       </c>
       <c r="AA62" s="9" t="n"/>
       <c r="AB62" s="9" t="n">
@@ -7769,24 +7781,24 @@
       </c>
       <c r="AC62" s="5" t="inlineStr">
         <is>
-          <t>2:43:01.630317</t>
+          <t>2:27:48.958907</t>
         </is>
       </c>
       <c r="AD62" s="5" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1</t>
+          <t>outputs/SAGE-CD/Run1</t>
         </is>
       </c>
       <c r="AE62" s="6" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1/S0/WHU/train_log.txt</t>
+          <t>outputs/SAGE-CD/Run1/G1/WHU/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>SCTC-Run1</t>
+          <t>SAGE-CD-Run1</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
@@ -7796,22 +7808,22 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>G2</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>S1_FullPixel_Symmetric_Calibration</t>
+          <t>G2_SafeDINO</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=symmetric</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G63" s="5" t="n">
@@ -7855,22 +7867,22 @@
         <v>2.7676</v>
       </c>
       <c r="U63" s="8" t="n">
-        <v>97.39619999999999</v>
+        <v>80.4331</v>
       </c>
       <c r="V63" s="8" t="n">
-        <v>97.7011</v>
+        <v>84.6131</v>
       </c>
       <c r="W63" s="8" t="n">
-        <v>99.39570000000001</v>
+        <v>91.9362</v>
       </c>
       <c r="X63" s="8" t="n">
-        <v>97.5484</v>
+        <v>82.47020000000001</v>
       </c>
       <c r="Y63" s="8" t="n">
-        <v>95.21420000000001</v>
+        <v>70.1696</v>
       </c>
       <c r="Z63" s="8" t="n">
-        <v>97.2038</v>
+        <v>77.23830000000001</v>
       </c>
       <c r="AA63" s="9" t="n"/>
       <c r="AB63" s="9" t="n">
@@ -7878,24 +7890,24 @@
       </c>
       <c r="AC63" s="5" t="inlineStr">
         <is>
-          <t>3:19:01.505607</t>
+          <t>3:03:55.831687</t>
         </is>
       </c>
       <c r="AD63" s="5" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1</t>
+          <t>outputs/SAGE-CD/Run1</t>
         </is>
       </c>
       <c r="AE63" s="6" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1/S1/CDD/train_log.txt</t>
+          <t>outputs/SAGE-CD/Run1/G2/SYSU/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>SCTC-Run1</t>
+          <t>SAGE-CD-Run1</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
@@ -7905,22 +7917,22 @@
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>G2</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>S1_FullPixel_Symmetric_Calibration</t>
+          <t>G2_SafeDINO</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=symmetric</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
         </is>
       </c>
       <c r="G64" s="5" t="n">
@@ -7964,22 +7976,22 @@
         <v>2.7676</v>
       </c>
       <c r="U64" s="8" t="n">
-        <v>89.7944</v>
+        <v>92.12320000000001</v>
       </c>
       <c r="V64" s="8" t="n">
-        <v>92.1617</v>
+        <v>96.41670000000001</v>
       </c>
       <c r="W64" s="8" t="n">
-        <v>99.0911</v>
+        <v>99.55159999999999</v>
       </c>
       <c r="X64" s="8" t="n">
-        <v>90.96260000000001</v>
+        <v>94.22110000000001</v>
       </c>
       <c r="Y64" s="8" t="n">
-        <v>83.4233</v>
+        <v>89.0736</v>
       </c>
       <c r="Z64" s="8" t="n">
-        <v>90.4842</v>
+        <v>93.988</v>
       </c>
       <c r="AA64" s="9" t="n"/>
       <c r="AB64" s="9" t="n">
@@ -7987,17 +7999,17 @@
       </c>
       <c r="AC64" s="5" t="inlineStr">
         <is>
-          <t>0:33:15.349976</t>
+          <t>2:45:52.645791</t>
         </is>
       </c>
       <c r="AD64" s="5" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1</t>
+          <t>outputs/SAGE-CD/Run1</t>
         </is>
       </c>
       <c r="AE64" s="6" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1/S1/LEVIR/train_log.txt</t>
+          <t>outputs/SAGE-CD/Run1/G2/WHU/train_log.txt</t>
         </is>
       </c>
     </row>
@@ -8014,22 +8026,22 @@
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S0</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>S1_FullPixel_Symmetric_Calibration</t>
+          <t>S0_Clean_A2Net_LWGANet_L0</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=symmetric</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=none</t>
         </is>
       </c>
       <c r="G65" s="5" t="n">
@@ -8073,22 +8085,22 @@
         <v>2.7676</v>
       </c>
       <c r="U65" s="8" t="n">
-        <v>80.42610000000001</v>
+        <v>97.68770000000001</v>
       </c>
       <c r="V65" s="8" t="n">
-        <v>85.6097</v>
+        <v>97.8814</v>
       </c>
       <c r="W65" s="8" t="n">
-        <v>92.19580000000001</v>
+        <v>99.45359999999999</v>
       </c>
       <c r="X65" s="8" t="n">
-        <v>82.93700000000001</v>
+        <v>97.78449999999999</v>
       </c>
       <c r="Y65" s="8" t="n">
-        <v>70.8481</v>
+        <v>95.66500000000001</v>
       </c>
       <c r="Z65" s="8" t="n">
-        <v>77.8843</v>
+        <v>97.47280000000001</v>
       </c>
       <c r="AA65" s="9" t="n"/>
       <c r="AB65" s="9" t="n">
@@ -8096,7 +8108,7 @@
       </c>
       <c r="AC65" s="5" t="inlineStr">
         <is>
-          <t>3:32:56.072083</t>
+          <t>3:42:46.634404</t>
         </is>
       </c>
       <c r="AD65" s="5" t="inlineStr">
@@ -8106,7 +8118,7 @@
       </c>
       <c r="AE65" s="6" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1/S1/SYSU/train_log.txt</t>
+          <t>outputs/SCTC/Run1/S0/CDD/train_log.txt</t>
         </is>
       </c>
     </row>
@@ -8123,22 +8135,22 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S0</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>S1_FullPixel_Symmetric_Calibration</t>
+          <t>S0_Clean_A2Net_LWGANet_L0</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=symmetric</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=none</t>
         </is>
       </c>
       <c r="G66" s="5" t="n">
@@ -8182,22 +8194,22 @@
         <v>2.7676</v>
       </c>
       <c r="U66" s="8" t="n">
-        <v>92.1589</v>
+        <v>89.4019</v>
       </c>
       <c r="V66" s="8" t="n">
-        <v>95.1091</v>
+        <v>92.447</v>
       </c>
       <c r="W66" s="8" t="n">
-        <v>99.5009</v>
+        <v>99.08799999999999</v>
       </c>
       <c r="X66" s="8" t="n">
-        <v>93.61070000000001</v>
+        <v>90.8989</v>
       </c>
       <c r="Y66" s="8" t="n">
-        <v>87.9889</v>
+        <v>83.3163</v>
       </c>
       <c r="Z66" s="8" t="n">
-        <v>93.3511</v>
+        <v>90.41900000000001</v>
       </c>
       <c r="AA66" s="9" t="n"/>
       <c r="AB66" s="9" t="n">
@@ -8205,7 +8217,7 @@
       </c>
       <c r="AC66" s="5" t="inlineStr">
         <is>
-          <t>2:40:44.864364</t>
+          <t>2:47:14.389924</t>
         </is>
       </c>
       <c r="AD66" s="5" t="inlineStr">
@@ -8215,7 +8227,7 @@
       </c>
       <c r="AE66" s="6" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1/S1/WHU/train_log.txt</t>
+          <t>outputs/SCTC/Run1/S0/LEVIR/train_log.txt</t>
         </is>
       </c>
     </row>
@@ -8232,22 +8244,22 @@
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S0</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>S2_SCTC_UnchangedAware_Symmetric_CrossTemporal_Calibration</t>
+          <t>S0_Clean_A2Net_LWGANet_L0</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=sctc</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=none</t>
         </is>
       </c>
       <c r="G67" s="5" t="n">
@@ -8291,22 +8303,22 @@
         <v>2.7676</v>
       </c>
       <c r="U67" s="8" t="n">
-        <v>97.4438</v>
+        <v>81.14139999999999</v>
       </c>
       <c r="V67" s="8" t="n">
-        <v>97.71940000000001</v>
+        <v>84.9704</v>
       </c>
       <c r="W67" s="8" t="n">
-        <v>99.4038</v>
+        <v>92.1679</v>
       </c>
       <c r="X67" s="8" t="n">
-        <v>97.5814</v>
+        <v>83.01180000000001</v>
       </c>
       <c r="Y67" s="8" t="n">
-        <v>95.277</v>
+        <v>70.9573</v>
       </c>
       <c r="Z67" s="8" t="n">
-        <v>97.2414</v>
+        <v>77.92609999999999</v>
       </c>
       <c r="AA67" s="9" t="n"/>
       <c r="AB67" s="9" t="n">
@@ -8314,7 +8326,7 @@
       </c>
       <c r="AC67" s="5" t="inlineStr">
         <is>
-          <t>2:52:30.285254</t>
+          <t>2:20:47.929272</t>
         </is>
       </c>
       <c r="AD67" s="5" t="inlineStr">
@@ -8324,7 +8336,7 @@
       </c>
       <c r="AE67" s="6" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1/S2/CDD/train_log.txt</t>
+          <t>outputs/SCTC/Run1/S0/SYSU/train_log.txt</t>
         </is>
       </c>
     </row>
@@ -8341,22 +8353,22 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S0</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>S2_SCTC_UnchangedAware_Symmetric_CrossTemporal_Calibration</t>
+          <t>S0_Clean_A2Net_LWGANet_L0</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=sctc</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=none</t>
         </is>
       </c>
       <c r="G68" s="5" t="n">
@@ -8400,22 +8412,22 @@
         <v>2.7676</v>
       </c>
       <c r="U68" s="8" t="n">
-        <v>90.1421</v>
+        <v>91.9434</v>
       </c>
       <c r="V68" s="8" t="n">
-        <v>91.4601</v>
+        <v>95.20650000000001</v>
       </c>
       <c r="W68" s="8" t="n">
-        <v>99.069</v>
+        <v>99.4967</v>
       </c>
       <c r="X68" s="8" t="n">
-        <v>90.7963</v>
+        <v>93.54649999999999</v>
       </c>
       <c r="Y68" s="8" t="n">
-        <v>83.14399999999999</v>
+        <v>87.87549999999999</v>
       </c>
       <c r="Z68" s="8" t="n">
-        <v>90.3061</v>
+        <v>93.2847</v>
       </c>
       <c r="AA68" s="9" t="n"/>
       <c r="AB68" s="9" t="n">
@@ -8423,7 +8435,7 @@
       </c>
       <c r="AC68" s="5" t="inlineStr">
         <is>
-          <t>3:18:11.767618</t>
+          <t>2:43:01.630317</t>
         </is>
       </c>
       <c r="AD68" s="5" t="inlineStr">
@@ -8433,7 +8445,7 @@
       </c>
       <c r="AE68" s="6" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1/S2/LEVIR/train_log.txt</t>
+          <t>outputs/SCTC/Run1/S0/WHU/train_log.txt</t>
         </is>
       </c>
     </row>
@@ -8450,22 +8462,22 @@
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>S2_SCTC_UnchangedAware_Symmetric_CrossTemporal_Calibration</t>
+          <t>S1_FullPixel_Symmetric_Calibration</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=sctc</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=symmetric</t>
         </is>
       </c>
       <c r="G69" s="5" t="n">
@@ -8509,22 +8521,22 @@
         <v>2.7676</v>
       </c>
       <c r="U69" s="8" t="n">
-        <v>81.00070000000001</v>
+        <v>97.39619999999999</v>
       </c>
       <c r="V69" s="8" t="n">
-        <v>84.595</v>
+        <v>97.7011</v>
       </c>
       <c r="W69" s="8" t="n">
-        <v>92.04090000000001</v>
+        <v>99.39570000000001</v>
       </c>
       <c r="X69" s="8" t="n">
-        <v>82.75879999999999</v>
+        <v>97.5484</v>
       </c>
       <c r="Y69" s="8" t="n">
-        <v>70.5885</v>
+        <v>95.21420000000001</v>
       </c>
       <c r="Z69" s="8" t="n">
-        <v>77.5882</v>
+        <v>97.2038</v>
       </c>
       <c r="AA69" s="9" t="n"/>
       <c r="AB69" s="9" t="n">
@@ -8532,7 +8544,7 @@
       </c>
       <c r="AC69" s="5" t="inlineStr">
         <is>
-          <t>4:06:34.060509</t>
+          <t>3:19:01.505607</t>
         </is>
       </c>
       <c r="AD69" s="5" t="inlineStr">
@@ -8542,7 +8554,7 @@
       </c>
       <c r="AE69" s="6" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1/S2/SYSU/train_log.txt</t>
+          <t>outputs/SCTC/Run1/S1/CDD/train_log.txt</t>
         </is>
       </c>
     </row>
@@ -8559,22 +8571,22 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>S2_SCTC_UnchangedAware_Symmetric_CrossTemporal_Calibration</t>
+          <t>S1_FullPixel_Symmetric_Calibration</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=sctc</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=symmetric</t>
         </is>
       </c>
       <c r="G70" s="5" t="n">
@@ -8618,22 +8630,22 @@
         <v>2.7676</v>
       </c>
       <c r="U70" s="8" t="n">
-        <v>92.7942</v>
+        <v>89.7944</v>
       </c>
       <c r="V70" s="8" t="n">
-        <v>95.1825</v>
+        <v>92.1617</v>
       </c>
       <c r="W70" s="8" t="n">
-        <v>99.5278</v>
+        <v>99.0911</v>
       </c>
       <c r="X70" s="8" t="n">
-        <v>93.9731</v>
+        <v>90.96260000000001</v>
       </c>
       <c r="Y70" s="8" t="n">
-        <v>88.6315</v>
+        <v>83.4233</v>
       </c>
       <c r="Z70" s="8" t="n">
-        <v>93.7274</v>
+        <v>90.4842</v>
       </c>
       <c r="AA70" s="9" t="n"/>
       <c r="AB70" s="9" t="n">
@@ -8641,22 +8653,676 @@
       </c>
       <c r="AC70" s="5" t="inlineStr">
         <is>
+          <t>0:33:15.349976</t>
+        </is>
+      </c>
+      <c r="AD70" s="5" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="AE70" s="6" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S1/LEVIR/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>SCTC-Run1</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>S1_FullPixel_Symmetric_Calibration</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=symmetric</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H71" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I71" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J71" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L71" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M71" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N71" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O71" s="7" t="n"/>
+      <c r="P71" s="7" t="n"/>
+      <c r="Q71" s="5" t="n"/>
+      <c r="R71" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S71" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T71" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U71" s="8" t="n">
+        <v>80.42610000000001</v>
+      </c>
+      <c r="V71" s="8" t="n">
+        <v>85.6097</v>
+      </c>
+      <c r="W71" s="8" t="n">
+        <v>92.19580000000001</v>
+      </c>
+      <c r="X71" s="8" t="n">
+        <v>82.93700000000001</v>
+      </c>
+      <c r="Y71" s="8" t="n">
+        <v>70.8481</v>
+      </c>
+      <c r="Z71" s="8" t="n">
+        <v>77.8843</v>
+      </c>
+      <c r="AA71" s="9" t="n"/>
+      <c r="AB71" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="5" t="inlineStr">
+        <is>
+          <t>3:32:56.072083</t>
+        </is>
+      </c>
+      <c r="AD71" s="5" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="AE71" s="6" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S1/SYSU/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>SCTC-Run1</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>S1_FullPixel_Symmetric_Calibration</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=symmetric</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H72" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I72" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J72" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K72" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L72" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M72" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N72" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O72" s="7" t="n"/>
+      <c r="P72" s="7" t="n"/>
+      <c r="Q72" s="5" t="n"/>
+      <c r="R72" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S72" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T72" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U72" s="8" t="n">
+        <v>92.1589</v>
+      </c>
+      <c r="V72" s="8" t="n">
+        <v>95.1091</v>
+      </c>
+      <c r="W72" s="8" t="n">
+        <v>99.5009</v>
+      </c>
+      <c r="X72" s="8" t="n">
+        <v>93.61070000000001</v>
+      </c>
+      <c r="Y72" s="8" t="n">
+        <v>87.9889</v>
+      </c>
+      <c r="Z72" s="8" t="n">
+        <v>93.3511</v>
+      </c>
+      <c r="AA72" s="9" t="n"/>
+      <c r="AB72" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC72" s="5" t="inlineStr">
+        <is>
+          <t>2:40:44.864364</t>
+        </is>
+      </c>
+      <c r="AD72" s="5" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="AE72" s="6" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S1/WHU/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="30" customHeight="1">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>SCTC-Run1</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>S2_SCTC_UnchangedAware_Symmetric_CrossTemporal_Calibration</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=sctc</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H73" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I73" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J73" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L73" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M73" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N73" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O73" s="7" t="n"/>
+      <c r="P73" s="7" t="n"/>
+      <c r="Q73" s="5" t="n"/>
+      <c r="R73" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S73" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T73" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U73" s="8" t="n">
+        <v>97.4438</v>
+      </c>
+      <c r="V73" s="8" t="n">
+        <v>97.71940000000001</v>
+      </c>
+      <c r="W73" s="8" t="n">
+        <v>99.4038</v>
+      </c>
+      <c r="X73" s="8" t="n">
+        <v>97.5814</v>
+      </c>
+      <c r="Y73" s="8" t="n">
+        <v>95.277</v>
+      </c>
+      <c r="Z73" s="8" t="n">
+        <v>97.2414</v>
+      </c>
+      <c r="AA73" s="9" t="n"/>
+      <c r="AB73" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC73" s="5" t="inlineStr">
+        <is>
+          <t>2:52:30.285254</t>
+        </is>
+      </c>
+      <c r="AD73" s="5" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="AE73" s="6" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S2/CDD/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>SCTC-Run1</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>S2_SCTC_UnchangedAware_Symmetric_CrossTemporal_Calibration</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=sctc</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H74" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J74" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K74" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L74" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M74" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N74" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O74" s="7" t="n"/>
+      <c r="P74" s="7" t="n"/>
+      <c r="Q74" s="5" t="n"/>
+      <c r="R74" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S74" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T74" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U74" s="8" t="n">
+        <v>90.1421</v>
+      </c>
+      <c r="V74" s="8" t="n">
+        <v>91.4601</v>
+      </c>
+      <c r="W74" s="8" t="n">
+        <v>99.069</v>
+      </c>
+      <c r="X74" s="8" t="n">
+        <v>90.7963</v>
+      </c>
+      <c r="Y74" s="8" t="n">
+        <v>83.14399999999999</v>
+      </c>
+      <c r="Z74" s="8" t="n">
+        <v>90.3061</v>
+      </c>
+      <c r="AA74" s="9" t="n"/>
+      <c r="AB74" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC74" s="5" t="inlineStr">
+        <is>
+          <t>3:18:11.767618</t>
+        </is>
+      </c>
+      <c r="AD74" s="5" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="AE74" s="6" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S2/LEVIR/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="30" customHeight="1">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>SCTC-Run1</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>S2_SCTC_UnchangedAware_Symmetric_CrossTemporal_Calibration</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=sctc</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H75" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J75" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L75" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M75" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N75" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O75" s="7" t="n"/>
+      <c r="P75" s="7" t="n"/>
+      <c r="Q75" s="5" t="n"/>
+      <c r="R75" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S75" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T75" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U75" s="8" t="n">
+        <v>81.00070000000001</v>
+      </c>
+      <c r="V75" s="8" t="n">
+        <v>84.595</v>
+      </c>
+      <c r="W75" s="8" t="n">
+        <v>92.04090000000001</v>
+      </c>
+      <c r="X75" s="8" t="n">
+        <v>82.75879999999999</v>
+      </c>
+      <c r="Y75" s="8" t="n">
+        <v>70.5885</v>
+      </c>
+      <c r="Z75" s="8" t="n">
+        <v>77.5882</v>
+      </c>
+      <c r="AA75" s="9" t="n"/>
+      <c r="AB75" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="5" t="inlineStr">
+        <is>
+          <t>4:06:34.060509</t>
+        </is>
+      </c>
+      <c r="AD75" s="5" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="AE75" s="6" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S2/SYSU/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="30" customHeight="1">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>SCTC-Run1</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>S2_SCTC_UnchangedAware_Symmetric_CrossTemporal_Calibration</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=sctc</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H76" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I76" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J76" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K76" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L76" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M76" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N76" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O76" s="7" t="n"/>
+      <c r="P76" s="7" t="n"/>
+      <c r="Q76" s="5" t="n"/>
+      <c r="R76" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S76" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T76" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U76" s="8" t="n">
+        <v>92.7942</v>
+      </c>
+      <c r="V76" s="8" t="n">
+        <v>95.1825</v>
+      </c>
+      <c r="W76" s="8" t="n">
+        <v>99.5278</v>
+      </c>
+      <c r="X76" s="8" t="n">
+        <v>93.9731</v>
+      </c>
+      <c r="Y76" s="8" t="n">
+        <v>88.6315</v>
+      </c>
+      <c r="Z76" s="8" t="n">
+        <v>93.7274</v>
+      </c>
+      <c r="AA76" s="9" t="n"/>
+      <c r="AB76" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC76" s="5" t="inlineStr">
+        <is>
           <t>2:08:54.218613</t>
         </is>
       </c>
-      <c r="AD70" s="5" t="inlineStr">
+      <c r="AD76" s="5" t="inlineStr">
         <is>
           <t>outputs/SCTC/Run1</t>
         </is>
       </c>
-      <c r="AE70" s="6" t="inlineStr">
+      <c r="AE76" s="6" t="inlineStr">
         <is>
           <t>outputs/SCTC/Run1/S2/WHU/train_log.txt</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="X2:X70">
+  <conditionalFormatting sqref="X2:X76">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -8681,7 +9347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C70"/>
+  <dimension ref="A1:C76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -9879,6 +10545,108 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SAGE-CD/Run1</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SAGE-CD/Run1/G0/SYSU/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C71" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SAGE-CD/Run1</t>
+        </is>
+      </c>
+      <c r="B72" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SAGE-CD/Run1/G0/WHU/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C72" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SAGE-CD/Run1</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SAGE-CD/Run1/G1/SYSU/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C73" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SAGE-CD/Run1</t>
+        </is>
+      </c>
+      <c r="B74" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SAGE-CD/Run1/G1/WHU/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C74" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SAGE-CD/Run1</t>
+        </is>
+      </c>
+      <c r="B75" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SAGE-CD/Run1/G2/SYSU/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C75" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SAGE-CD/Run1</t>
+        </is>
+      </c>
+      <c r="B76" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SAGE-CD/Run1/G2/WHU/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C76" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -188,8 +188,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ExperimentResultsTable" displayName="ExperimentResultsTable" ref="A1:AE76" headerRowCount="1">
-  <autoFilter ref="A1:AE76"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ExperimentResultsTable" displayName="ExperimentResultsTable" ref="A1:AE86" headerRowCount="1">
+  <autoFilter ref="A1:AE86"/>
   <tableColumns count="31">
     <tableColumn id="1" name="Run"/>
     <tableColumn id="2" name="Stage"/>
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -538,7 +538,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 08:49:08 +0800</t>
+          <t>2026-09-24 11:57:18 +0800</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>outputs/DirectionC (DART-R) + outputs/DART-R-TS + outputs/RDT-CD + outputs/SCTC; launcher logs excluded</t>
+          <t>outputs/DirectionC (DART-R) + outputs/DART-R-TS + outputs/RDT-CD + outputs/SCTC + outputs/SAGE-CD; launcher logs excluded</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8">
@@ -596,7 +596,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>DART-R=8, DART-R-TS=4, FA-SCRD-Run1=8, RDT-CD-Run1=12, RDT-CD-Run2=11, RDT-CD-Run3=14, SAGE-CD-Run1=6, SCTC-Run1=12</t>
+          <t>DART-R=8, DART-R-TS=4, FA-SCRD-Run1=8, RDT-CD-Run1=12, RDT-CD-Run2=11, RDT-CD-Run3=14, SAGE-CD-Run1=6, SAGE-CD-Run2=10, SCTC-Run1=12</t>
         </is>
       </c>
     </row>
@@ -645,6 +645,18 @@
       <c r="B12" s="3" t="inlineStr">
         <is>
           <t>SAGE-CD-Run1 (Safe-DINO gate): G0=clean, G1=joint temporal BN, G2=full-res DINO semantic target + aux head + logit standardization + gradient budget. G2-G1 = WHU +0.46 / SYSU -0.25 → gate FAIL (SYSU), WHU-only again; but KD mechanism fixed (kd 12-15→0.6, grad budget ~25%). 40k, seed 2333 only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>SAGE-CD Run2 scope</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>SAGE-CD-Run2 (failure-type routed native-scale dual-expert distillation + symmetric context fusion): R0=clean A2Net, R1=+joint temporal BN, R2=+SCF + identity-centered decoder gate, R3=+DINO semantic (1/16) + SAM boundary (1/4) uniform, R4=+failure-type reliability routing (main method). R4-R2 (main gate, needs &gt;=+0.30 on both) = SYSU -0.44 / WHU +0.18 → FAIL. R4-R3 = SYSU +0.19 / WHU +0.02. All 10 runs completed 40000 steps, swap/deploy error 0, deploy 2.9131M / 2.7676G. 40k, seed 2333 only.</t>
         </is>
       </c>
     </row>
@@ -659,7 +671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE76"/>
+  <dimension ref="A1:AE86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2260,7 +2272,7 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; joint_bn=True; teacher=True</t>
         </is>
       </c>
       <c r="G14" s="5" t="n">
@@ -2369,7 +2381,7 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; joint_bn=True; teacher=True</t>
         </is>
       </c>
       <c r="G15" s="5" t="n">
@@ -2478,7 +2490,7 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; joint_bn=False; teacher=False</t>
         </is>
       </c>
       <c r="G16" s="5" t="n">
@@ -2587,7 +2599,7 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; joint_bn=False; teacher=False</t>
         </is>
       </c>
       <c r="G17" s="5" t="n">
@@ -2696,7 +2708,7 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; joint_bn=True; teacher=False</t>
         </is>
       </c>
       <c r="G18" s="5" t="n">
@@ -2805,7 +2817,7 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; joint_bn=True; teacher=False</t>
         </is>
       </c>
       <c r="G19" s="5" t="n">
@@ -2914,7 +2926,7 @@
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; joint_bn=True; teacher=True</t>
         </is>
       </c>
       <c r="G20" s="5" t="n">
@@ -3023,7 +3035,7 @@
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; joint_bn=True; teacher=True</t>
         </is>
       </c>
       <c r="G21" s="5" t="n">
@@ -7387,7 +7399,7 @@
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; joint_bn=False; teacher=False</t>
         </is>
       </c>
       <c r="G59" s="5" t="n">
@@ -7496,7 +7508,7 @@
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; joint_bn=False; teacher=False</t>
         </is>
       </c>
       <c r="G60" s="5" t="n">
@@ -7605,7 +7617,7 @@
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; joint_bn=True; teacher=False</t>
         </is>
       </c>
       <c r="G61" s="5" t="n">
@@ -7714,7 +7726,7 @@
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; joint_bn=True; teacher=False</t>
         </is>
       </c>
       <c r="G62" s="5" t="n">
@@ -7823,7 +7835,7 @@
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; joint_bn=True; teacher=True</t>
         </is>
       </c>
       <c r="G63" s="5" t="n">
@@ -7932,7 +7944,7 @@
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; joint_bn=True; teacher=True</t>
         </is>
       </c>
       <c r="G64" s="5" t="n">
@@ -8016,7 +8028,7 @@
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>SCTC-Run1</t>
+          <t>SAGE-CD-Run2</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
@@ -8026,22 +8038,22 @@
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>S0</t>
+          <t>R0</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>S0_Clean_A2Net_LWGANet_L0</t>
+          <t>R0</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=none</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; dice=batch; joint_bn=False; scf=False; gate=False; teacher=False; routing=False</t>
         </is>
       </c>
       <c r="G65" s="5" t="n">
@@ -8064,9 +8076,7 @@
       <c r="L65" s="7" t="n">
         <v>0.0001</v>
       </c>
-      <c r="M65" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M65" s="5" t="n"/>
       <c r="N65" s="5" t="inlineStr">
         <is>
           <t>batch</t>
@@ -8085,22 +8095,22 @@
         <v>2.7676</v>
       </c>
       <c r="U65" s="8" t="n">
-        <v>97.68770000000001</v>
+        <v>80.1767</v>
       </c>
       <c r="V65" s="8" t="n">
-        <v>97.8814</v>
+        <v>86.2732</v>
       </c>
       <c r="W65" s="8" t="n">
-        <v>99.45359999999999</v>
+        <v>92.3167</v>
       </c>
       <c r="X65" s="8" t="n">
-        <v>97.78449999999999</v>
+        <v>83.1133</v>
       </c>
       <c r="Y65" s="8" t="n">
-        <v>95.66500000000001</v>
+        <v>71.10590000000001</v>
       </c>
       <c r="Z65" s="8" t="n">
-        <v>97.47280000000001</v>
+        <v>78.149</v>
       </c>
       <c r="AA65" s="9" t="n"/>
       <c r="AB65" s="9" t="n">
@@ -8108,24 +8118,24 @@
       </c>
       <c r="AC65" s="5" t="inlineStr">
         <is>
-          <t>3:42:46.634404</t>
+          <t>2:54:28.038880</t>
         </is>
       </c>
       <c r="AD65" s="5" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1</t>
+          <t>outputs/SAGE-CD/Run2</t>
         </is>
       </c>
       <c r="AE65" s="6" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1/S0/CDD/train_log.txt</t>
+          <t>outputs/SAGE-CD/Run2/R0/SYSU/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>SCTC-Run1</t>
+          <t>SAGE-CD-Run2</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -8135,22 +8145,22 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>S0</t>
+          <t>R0</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>S0_Clean_A2Net_LWGANet_L0</t>
+          <t>R0</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=none</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; dice=batch; joint_bn=False; scf=False; gate=False; teacher=False; routing=False</t>
         </is>
       </c>
       <c r="G66" s="5" t="n">
@@ -8173,9 +8183,7 @@
       <c r="L66" s="7" t="n">
         <v>0.0001</v>
       </c>
-      <c r="M66" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M66" s="5" t="n"/>
       <c r="N66" s="5" t="inlineStr">
         <is>
           <t>batch</t>
@@ -8194,22 +8202,22 @@
         <v>2.7676</v>
       </c>
       <c r="U66" s="8" t="n">
-        <v>89.4019</v>
+        <v>90.22409999999999</v>
       </c>
       <c r="V66" s="8" t="n">
-        <v>92.447</v>
+        <v>95.857</v>
       </c>
       <c r="W66" s="8" t="n">
-        <v>99.08799999999999</v>
+        <v>99.45739999999999</v>
       </c>
       <c r="X66" s="8" t="n">
-        <v>90.8989</v>
+        <v>92.95529999999999</v>
       </c>
       <c r="Y66" s="8" t="n">
-        <v>83.3163</v>
+        <v>86.8378</v>
       </c>
       <c r="Z66" s="8" t="n">
-        <v>90.41900000000001</v>
+        <v>92.6734</v>
       </c>
       <c r="AA66" s="9" t="n"/>
       <c r="AB66" s="9" t="n">
@@ -8217,24 +8225,24 @@
       </c>
       <c r="AC66" s="5" t="inlineStr">
         <is>
-          <t>2:47:14.389924</t>
+          <t>2:43:42.870592</t>
         </is>
       </c>
       <c r="AD66" s="5" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1</t>
+          <t>outputs/SAGE-CD/Run2</t>
         </is>
       </c>
       <c r="AE66" s="6" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1/S0/LEVIR/train_log.txt</t>
+          <t>outputs/SAGE-CD/Run2/R0/WHU/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>SCTC-Run1</t>
+          <t>SAGE-CD-Run2</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
@@ -8244,12 +8252,12 @@
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>S0</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>S0_Clean_A2Net_LWGANet_L0</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -8259,7 +8267,7 @@
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=none</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; dice=batch; joint_bn=True; scf=False; gate=False; teacher=False; routing=False</t>
         </is>
       </c>
       <c r="G67" s="5" t="n">
@@ -8282,9 +8290,7 @@
       <c r="L67" s="7" t="n">
         <v>0.0001</v>
       </c>
-      <c r="M67" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M67" s="5" t="n"/>
       <c r="N67" s="5" t="inlineStr">
         <is>
           <t>batch</t>
@@ -8303,22 +8309,22 @@
         <v>2.7676</v>
       </c>
       <c r="U67" s="8" t="n">
-        <v>81.14139999999999</v>
+        <v>79.2176</v>
       </c>
       <c r="V67" s="8" t="n">
-        <v>84.9704</v>
+        <v>86.1065</v>
       </c>
       <c r="W67" s="8" t="n">
-        <v>92.1679</v>
+        <v>92.08460000000001</v>
       </c>
       <c r="X67" s="8" t="n">
-        <v>83.01180000000001</v>
+        <v>82.51849999999999</v>
       </c>
       <c r="Y67" s="8" t="n">
-        <v>70.9573</v>
+        <v>70.2396</v>
       </c>
       <c r="Z67" s="8" t="n">
-        <v>77.92609999999999</v>
+        <v>77.41409999999999</v>
       </c>
       <c r="AA67" s="9" t="n"/>
       <c r="AB67" s="9" t="n">
@@ -8326,24 +8332,24 @@
       </c>
       <c r="AC67" s="5" t="inlineStr">
         <is>
-          <t>2:20:47.929272</t>
+          <t>2:42:50.776756</t>
         </is>
       </c>
       <c r="AD67" s="5" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1</t>
+          <t>outputs/SAGE-CD/Run2</t>
         </is>
       </c>
       <c r="AE67" s="6" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1/S0/SYSU/train_log.txt</t>
+          <t>outputs/SAGE-CD/Run2/R1/SYSU/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>SCTC-Run1</t>
+          <t>SAGE-CD-Run2</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -8353,12 +8359,12 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>S0</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>S0_Clean_A2Net_LWGANet_L0</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -8368,7 +8374,7 @@
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=none</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; dice=batch; joint_bn=True; scf=False; gate=False; teacher=False; routing=False</t>
         </is>
       </c>
       <c r="G68" s="5" t="n">
@@ -8391,9 +8397,7 @@
       <c r="L68" s="7" t="n">
         <v>0.0001</v>
       </c>
-      <c r="M68" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M68" s="5" t="n"/>
       <c r="N68" s="5" t="inlineStr">
         <is>
           <t>batch</t>
@@ -8412,22 +8416,22 @@
         <v>2.7676</v>
       </c>
       <c r="U68" s="8" t="n">
-        <v>91.9434</v>
+        <v>91.3554</v>
       </c>
       <c r="V68" s="8" t="n">
-        <v>95.20650000000001</v>
+        <v>95.5201</v>
       </c>
       <c r="W68" s="8" t="n">
-        <v>99.4967</v>
+        <v>99.48700000000001</v>
       </c>
       <c r="X68" s="8" t="n">
-        <v>93.54649999999999</v>
+        <v>93.3913</v>
       </c>
       <c r="Y68" s="8" t="n">
-        <v>87.87549999999999</v>
+        <v>87.602</v>
       </c>
       <c r="Z68" s="8" t="n">
-        <v>93.2847</v>
+        <v>93.1246</v>
       </c>
       <c r="AA68" s="9" t="n"/>
       <c r="AB68" s="9" t="n">
@@ -8435,24 +8439,24 @@
       </c>
       <c r="AC68" s="5" t="inlineStr">
         <is>
-          <t>2:43:01.630317</t>
+          <t>2:35:15.092315</t>
         </is>
       </c>
       <c r="AD68" s="5" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1</t>
+          <t>outputs/SAGE-CD/Run2</t>
         </is>
       </c>
       <c r="AE68" s="6" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1/S0/WHU/train_log.txt</t>
+          <t>outputs/SAGE-CD/Run2/R1/WHU/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>SCTC-Run1</t>
+          <t>SAGE-CD-Run2</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
@@ -8462,22 +8466,22 @@
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>S1_FullPixel_Symmetric_Calibration</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=symmetric</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; dice=batch; joint_bn=True; scf=True; gate=True; teacher=False; routing=False</t>
         </is>
       </c>
       <c r="G69" s="5" t="n">
@@ -8500,9 +8504,7 @@
       <c r="L69" s="7" t="n">
         <v>0.0001</v>
       </c>
-      <c r="M69" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M69" s="5" t="n"/>
       <c r="N69" s="5" t="inlineStr">
         <is>
           <t>batch</t>
@@ -8521,22 +8523,22 @@
         <v>2.7676</v>
       </c>
       <c r="U69" s="8" t="n">
-        <v>97.39619999999999</v>
+        <v>79.08370000000001</v>
       </c>
       <c r="V69" s="8" t="n">
-        <v>97.7011</v>
+        <v>85.9074</v>
       </c>
       <c r="W69" s="8" t="n">
-        <v>99.39570000000001</v>
+        <v>92.00789999999999</v>
       </c>
       <c r="X69" s="8" t="n">
-        <v>97.5484</v>
+        <v>82.3544</v>
       </c>
       <c r="Y69" s="8" t="n">
-        <v>95.21420000000001</v>
+        <v>70.0022</v>
       </c>
       <c r="Z69" s="8" t="n">
-        <v>97.2038</v>
+        <v>77.1999</v>
       </c>
       <c r="AA69" s="9" t="n"/>
       <c r="AB69" s="9" t="n">
@@ -8544,24 +8546,24 @@
       </c>
       <c r="AC69" s="5" t="inlineStr">
         <is>
-          <t>3:19:01.505607</t>
+          <t>3:14:23.037150</t>
         </is>
       </c>
       <c r="AD69" s="5" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1</t>
+          <t>outputs/SAGE-CD/Run2</t>
         </is>
       </c>
       <c r="AE69" s="6" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1/S1/CDD/train_log.txt</t>
+          <t>outputs/SAGE-CD/Run2/R2/SYSU/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>SCTC-Run1</t>
+          <t>SAGE-CD-Run2</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
@@ -8571,22 +8573,22 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>S1_FullPixel_Symmetric_Calibration</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=symmetric</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; dice=batch; joint_bn=True; scf=True; gate=True; teacher=False; routing=False</t>
         </is>
       </c>
       <c r="G70" s="5" t="n">
@@ -8609,9 +8611,7 @@
       <c r="L70" s="7" t="n">
         <v>0.0001</v>
       </c>
-      <c r="M70" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M70" s="5" t="n"/>
       <c r="N70" s="5" t="inlineStr">
         <is>
           <t>batch</t>
@@ -8630,22 +8630,22 @@
         <v>2.7676</v>
       </c>
       <c r="U70" s="8" t="n">
-        <v>89.7944</v>
+        <v>92.0291</v>
       </c>
       <c r="V70" s="8" t="n">
-        <v>92.1617</v>
+        <v>95.3805</v>
       </c>
       <c r="W70" s="8" t="n">
-        <v>99.0911</v>
+        <v>99.5069</v>
       </c>
       <c r="X70" s="8" t="n">
-        <v>90.96260000000001</v>
+        <v>93.6748</v>
       </c>
       <c r="Y70" s="8" t="n">
-        <v>83.4233</v>
+        <v>88.1022</v>
       </c>
       <c r="Z70" s="8" t="n">
-        <v>90.4842</v>
+        <v>93.41840000000001</v>
       </c>
       <c r="AA70" s="9" t="n"/>
       <c r="AB70" s="9" t="n">
@@ -8653,24 +8653,24 @@
       </c>
       <c r="AC70" s="5" t="inlineStr">
         <is>
-          <t>0:33:15.349976</t>
+          <t>3:05:47.496618</t>
         </is>
       </c>
       <c r="AD70" s="5" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1</t>
+          <t>outputs/SAGE-CD/Run2</t>
         </is>
       </c>
       <c r="AE70" s="6" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1/S1/LEVIR/train_log.txt</t>
+          <t>outputs/SAGE-CD/Run2/R2/WHU/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>SCTC-Run1</t>
+          <t>SAGE-CD-Run2</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>S1_FullPixel_Symmetric_Calibration</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -8695,7 +8695,7 @@
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=symmetric</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; dice=batch; joint_bn=True; scf=True; gate=True; teacher=True; routing=False</t>
         </is>
       </c>
       <c r="G71" s="5" t="n">
@@ -8718,9 +8718,7 @@
       <c r="L71" s="7" t="n">
         <v>0.0001</v>
       </c>
-      <c r="M71" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M71" s="5" t="n"/>
       <c r="N71" s="5" t="inlineStr">
         <is>
           <t>batch</t>
@@ -8739,22 +8737,22 @@
         <v>2.7676</v>
       </c>
       <c r="U71" s="8" t="n">
-        <v>80.42610000000001</v>
+        <v>77.79509999999999</v>
       </c>
       <c r="V71" s="8" t="n">
-        <v>85.6097</v>
+        <v>86.0711</v>
       </c>
       <c r="W71" s="8" t="n">
-        <v>92.19580000000001</v>
+        <v>91.7945</v>
       </c>
       <c r="X71" s="8" t="n">
-        <v>82.93700000000001</v>
+        <v>81.72409999999999</v>
       </c>
       <c r="Y71" s="8" t="n">
-        <v>70.8481</v>
+        <v>69.0962</v>
       </c>
       <c r="Z71" s="8" t="n">
-        <v>77.8843</v>
+        <v>76.45110000000001</v>
       </c>
       <c r="AA71" s="9" t="n"/>
       <c r="AB71" s="9" t="n">
@@ -8762,24 +8760,24 @@
       </c>
       <c r="AC71" s="5" t="inlineStr">
         <is>
-          <t>3:32:56.072083</t>
+          <t>3:51:41.094501</t>
         </is>
       </c>
       <c r="AD71" s="5" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1</t>
+          <t>outputs/SAGE-CD/Run2</t>
         </is>
       </c>
       <c r="AE71" s="6" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1/S1/SYSU/train_log.txt</t>
+          <t>outputs/SAGE-CD/Run2/R3/SYSU/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>SCTC-Run1</t>
+          <t>SAGE-CD-Run2</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
@@ -8789,12 +8787,12 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>S1_FullPixel_Symmetric_Calibration</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -8804,7 +8802,7 @@
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=symmetric</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; dice=batch; joint_bn=True; scf=True; gate=True; teacher=True; routing=False</t>
         </is>
       </c>
       <c r="G72" s="5" t="n">
@@ -8827,9 +8825,7 @@
       <c r="L72" s="7" t="n">
         <v>0.0001</v>
       </c>
-      <c r="M72" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M72" s="5" t="n"/>
       <c r="N72" s="5" t="inlineStr">
         <is>
           <t>batch</t>
@@ -8848,22 +8844,22 @@
         <v>2.7676</v>
       </c>
       <c r="U72" s="8" t="n">
-        <v>92.1589</v>
+        <v>91.9157</v>
       </c>
       <c r="V72" s="8" t="n">
-        <v>95.1091</v>
+        <v>95.84049999999999</v>
       </c>
       <c r="W72" s="8" t="n">
-        <v>99.5009</v>
+        <v>99.521</v>
       </c>
       <c r="X72" s="8" t="n">
-        <v>93.61070000000001</v>
+        <v>93.83709999999999</v>
       </c>
       <c r="Y72" s="8" t="n">
-        <v>87.9889</v>
+        <v>88.3897</v>
       </c>
       <c r="Z72" s="8" t="n">
-        <v>93.3511</v>
+        <v>93.58800000000001</v>
       </c>
       <c r="AA72" s="9" t="n"/>
       <c r="AB72" s="9" t="n">
@@ -8871,24 +8867,24 @@
       </c>
       <c r="AC72" s="5" t="inlineStr">
         <is>
-          <t>2:40:44.864364</t>
+          <t>3:44:11.925094</t>
         </is>
       </c>
       <c r="AD72" s="5" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1</t>
+          <t>outputs/SAGE-CD/Run2</t>
         </is>
       </c>
       <c r="AE72" s="6" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1/S1/WHU/train_log.txt</t>
+          <t>outputs/SAGE-CD/Run2/R3/WHU/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>SCTC-Run1</t>
+          <t>SAGE-CD-Run2</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
@@ -8898,22 +8894,22 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>S2_SCTC_UnchangedAware_Symmetric_CrossTemporal_Calibration</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=sctc</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; dice=batch; joint_bn=True; scf=True; gate=True; teacher=True; routing=True</t>
         </is>
       </c>
       <c r="G73" s="5" t="n">
@@ -8936,9 +8932,7 @@
       <c r="L73" s="7" t="n">
         <v>0.0001</v>
       </c>
-      <c r="M73" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M73" s="5" t="n"/>
       <c r="N73" s="5" t="inlineStr">
         <is>
           <t>batch</t>
@@ -8957,22 +8951,22 @@
         <v>2.7676</v>
       </c>
       <c r="U73" s="8" t="n">
-        <v>97.4438</v>
+        <v>77.655</v>
       </c>
       <c r="V73" s="8" t="n">
-        <v>97.71940000000001</v>
+        <v>86.6653</v>
       </c>
       <c r="W73" s="8" t="n">
-        <v>99.4038</v>
+        <v>91.9127</v>
       </c>
       <c r="X73" s="8" t="n">
-        <v>97.5814</v>
+        <v>81.9131</v>
       </c>
       <c r="Y73" s="8" t="n">
-        <v>95.277</v>
+        <v>69.3668</v>
       </c>
       <c r="Z73" s="8" t="n">
-        <v>97.2414</v>
+        <v>76.7252</v>
       </c>
       <c r="AA73" s="9" t="n"/>
       <c r="AB73" s="9" t="n">
@@ -8980,24 +8974,24 @@
       </c>
       <c r="AC73" s="5" t="inlineStr">
         <is>
-          <t>2:52:30.285254</t>
+          <t>3:36:32.815452</t>
         </is>
       </c>
       <c r="AD73" s="5" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1</t>
+          <t>outputs/SAGE-CD/Run2</t>
         </is>
       </c>
       <c r="AE73" s="6" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1/S2/CDD/train_log.txt</t>
+          <t>outputs/SAGE-CD/Run2/R4/SYSU/train_log.txt</t>
         </is>
       </c>
     </row>
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>SCTC-Run1</t>
+          <t>SAGE-CD-Run2</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
@@ -9007,22 +9001,22 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>S2_SCTC_UnchangedAware_Symmetric_CrossTemporal_Calibration</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=sctc</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; dice=batch; joint_bn=True; scf=True; gate=True; teacher=True; routing=True</t>
         </is>
       </c>
       <c r="G74" s="5" t="n">
@@ -9045,9 +9039,7 @@
       <c r="L74" s="7" t="n">
         <v>0.0001</v>
       </c>
-      <c r="M74" s="5" t="n">
-        <v>1</v>
-      </c>
+      <c r="M74" s="5" t="n"/>
       <c r="N74" s="5" t="inlineStr">
         <is>
           <t>batch</t>
@@ -9066,22 +9058,22 @@
         <v>2.7676</v>
       </c>
       <c r="U74" s="8" t="n">
-        <v>90.1421</v>
+        <v>91.9663</v>
       </c>
       <c r="V74" s="8" t="n">
-        <v>91.4601</v>
+        <v>95.8237</v>
       </c>
       <c r="W74" s="8" t="n">
-        <v>99.069</v>
+        <v>99.5222</v>
       </c>
       <c r="X74" s="8" t="n">
-        <v>90.7963</v>
+        <v>93.8554</v>
       </c>
       <c r="Y74" s="8" t="n">
-        <v>83.14399999999999</v>
+        <v>88.42219999999999</v>
       </c>
       <c r="Z74" s="8" t="n">
-        <v>90.3061</v>
+        <v>93.60690000000001</v>
       </c>
       <c r="AA74" s="9" t="n"/>
       <c r="AB74" s="9" t="n">
@@ -9089,17 +9081,17 @@
       </c>
       <c r="AC74" s="5" t="inlineStr">
         <is>
-          <t>3:18:11.767618</t>
+          <t>3:45:05.674031</t>
         </is>
       </c>
       <c r="AD74" s="5" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1</t>
+          <t>outputs/SAGE-CD/Run2</t>
         </is>
       </c>
       <c r="AE74" s="6" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1/S2/LEVIR/train_log.txt</t>
+          <t>outputs/SAGE-CD/Run2/R4/WHU/train_log.txt</t>
         </is>
       </c>
     </row>
@@ -9116,22 +9108,22 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S0</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>S2_SCTC_UnchangedAware_Symmetric_CrossTemporal_Calibration</t>
+          <t>S0_Clean_A2Net_LWGANet_L0</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=sctc</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=none</t>
         </is>
       </c>
       <c r="G75" s="5" t="n">
@@ -9175,22 +9167,22 @@
         <v>2.7676</v>
       </c>
       <c r="U75" s="8" t="n">
-        <v>81.00070000000001</v>
+        <v>97.68770000000001</v>
       </c>
       <c r="V75" s="8" t="n">
-        <v>84.595</v>
+        <v>97.8814</v>
       </c>
       <c r="W75" s="8" t="n">
-        <v>92.04090000000001</v>
+        <v>99.45359999999999</v>
       </c>
       <c r="X75" s="8" t="n">
-        <v>82.75879999999999</v>
+        <v>97.78449999999999</v>
       </c>
       <c r="Y75" s="8" t="n">
-        <v>70.5885</v>
+        <v>95.66500000000001</v>
       </c>
       <c r="Z75" s="8" t="n">
-        <v>77.5882</v>
+        <v>97.47280000000001</v>
       </c>
       <c r="AA75" s="9" t="n"/>
       <c r="AB75" s="9" t="n">
@@ -9198,7 +9190,7 @@
       </c>
       <c r="AC75" s="5" t="inlineStr">
         <is>
-          <t>4:06:34.060509</t>
+          <t>3:42:46.634404</t>
         </is>
       </c>
       <c r="AD75" s="5" t="inlineStr">
@@ -9208,7 +9200,7 @@
       </c>
       <c r="AE75" s="6" t="inlineStr">
         <is>
-          <t>outputs/SCTC/Run1/S2/SYSU/train_log.txt</t>
+          <t>outputs/SCTC/Run1/S0/CDD/train_log.txt</t>
         </is>
       </c>
     </row>
@@ -9225,22 +9217,22 @@
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S0</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>S2_SCTC_UnchangedAware_Symmetric_CrossTemporal_Calibration</t>
+          <t>S0_Clean_A2Net_LWGANet_L0</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
         <is>
-          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=sctc</t>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=none</t>
         </is>
       </c>
       <c r="G76" s="5" t="n">
@@ -9284,22 +9276,22 @@
         <v>2.7676</v>
       </c>
       <c r="U76" s="8" t="n">
-        <v>92.7942</v>
+        <v>89.4019</v>
       </c>
       <c r="V76" s="8" t="n">
-        <v>95.1825</v>
+        <v>92.447</v>
       </c>
       <c r="W76" s="8" t="n">
-        <v>99.5278</v>
+        <v>99.08799999999999</v>
       </c>
       <c r="X76" s="8" t="n">
-        <v>93.9731</v>
+        <v>90.8989</v>
       </c>
       <c r="Y76" s="8" t="n">
-        <v>88.6315</v>
+        <v>83.3163</v>
       </c>
       <c r="Z76" s="8" t="n">
-        <v>93.7274</v>
+        <v>90.41900000000001</v>
       </c>
       <c r="AA76" s="9" t="n"/>
       <c r="AB76" s="9" t="n">
@@ -9307,22 +9299,1112 @@
       </c>
       <c r="AC76" s="5" t="inlineStr">
         <is>
+          <t>2:47:14.389924</t>
+        </is>
+      </c>
+      <c r="AD76" s="5" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="AE76" s="6" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S0/LEVIR/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="30" customHeight="1">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>SCTC-Run1</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>S0</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>S0_Clean_A2Net_LWGANet_L0</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=none</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J77" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K77" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L77" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M77" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N77" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O77" s="7" t="n"/>
+      <c r="P77" s="7" t="n"/>
+      <c r="Q77" s="5" t="n"/>
+      <c r="R77" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S77" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T77" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U77" s="8" t="n">
+        <v>81.14139999999999</v>
+      </c>
+      <c r="V77" s="8" t="n">
+        <v>84.9704</v>
+      </c>
+      <c r="W77" s="8" t="n">
+        <v>92.1679</v>
+      </c>
+      <c r="X77" s="8" t="n">
+        <v>83.01180000000001</v>
+      </c>
+      <c r="Y77" s="8" t="n">
+        <v>70.9573</v>
+      </c>
+      <c r="Z77" s="8" t="n">
+        <v>77.92609999999999</v>
+      </c>
+      <c r="AA77" s="9" t="n"/>
+      <c r="AB77" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="5" t="inlineStr">
+        <is>
+          <t>2:20:47.929272</t>
+        </is>
+      </c>
+      <c r="AD77" s="5" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="AE77" s="6" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S0/SYSU/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="30" customHeight="1">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>SCTC-Run1</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>S0</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>S0_Clean_A2Net_LWGANet_L0</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=none</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H78" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I78" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J78" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K78" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L78" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M78" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N78" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O78" s="7" t="n"/>
+      <c r="P78" s="7" t="n"/>
+      <c r="Q78" s="5" t="n"/>
+      <c r="R78" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S78" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T78" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U78" s="8" t="n">
+        <v>91.9434</v>
+      </c>
+      <c r="V78" s="8" t="n">
+        <v>95.20650000000001</v>
+      </c>
+      <c r="W78" s="8" t="n">
+        <v>99.4967</v>
+      </c>
+      <c r="X78" s="8" t="n">
+        <v>93.54649999999999</v>
+      </c>
+      <c r="Y78" s="8" t="n">
+        <v>87.87549999999999</v>
+      </c>
+      <c r="Z78" s="8" t="n">
+        <v>93.2847</v>
+      </c>
+      <c r="AA78" s="9" t="n"/>
+      <c r="AB78" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC78" s="5" t="inlineStr">
+        <is>
+          <t>2:43:01.630317</t>
+        </is>
+      </c>
+      <c r="AD78" s="5" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="AE78" s="6" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S0/WHU/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="30" customHeight="1">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>SCTC-Run1</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>S1_FullPixel_Symmetric_Calibration</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=symmetric</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H79" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J79" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K79" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L79" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M79" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N79" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O79" s="7" t="n"/>
+      <c r="P79" s="7" t="n"/>
+      <c r="Q79" s="5" t="n"/>
+      <c r="R79" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S79" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T79" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U79" s="8" t="n">
+        <v>97.39619999999999</v>
+      </c>
+      <c r="V79" s="8" t="n">
+        <v>97.7011</v>
+      </c>
+      <c r="W79" s="8" t="n">
+        <v>99.39570000000001</v>
+      </c>
+      <c r="X79" s="8" t="n">
+        <v>97.5484</v>
+      </c>
+      <c r="Y79" s="8" t="n">
+        <v>95.21420000000001</v>
+      </c>
+      <c r="Z79" s="8" t="n">
+        <v>97.2038</v>
+      </c>
+      <c r="AA79" s="9" t="n"/>
+      <c r="AB79" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC79" s="5" t="inlineStr">
+        <is>
+          <t>3:19:01.505607</t>
+        </is>
+      </c>
+      <c r="AD79" s="5" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="AE79" s="6" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S1/CDD/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="30" customHeight="1">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>SCTC-Run1</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>S1_FullPixel_Symmetric_Calibration</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=symmetric</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J80" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K80" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L80" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M80" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N80" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O80" s="7" t="n"/>
+      <c r="P80" s="7" t="n"/>
+      <c r="Q80" s="5" t="n"/>
+      <c r="R80" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S80" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T80" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U80" s="8" t="n">
+        <v>89.7944</v>
+      </c>
+      <c r="V80" s="8" t="n">
+        <v>92.1617</v>
+      </c>
+      <c r="W80" s="8" t="n">
+        <v>99.0911</v>
+      </c>
+      <c r="X80" s="8" t="n">
+        <v>90.96260000000001</v>
+      </c>
+      <c r="Y80" s="8" t="n">
+        <v>83.4233</v>
+      </c>
+      <c r="Z80" s="8" t="n">
+        <v>90.4842</v>
+      </c>
+      <c r="AA80" s="9" t="n"/>
+      <c r="AB80" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC80" s="5" t="inlineStr">
+        <is>
+          <t>0:33:15.349976</t>
+        </is>
+      </c>
+      <c r="AD80" s="5" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="AE80" s="6" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S1/LEVIR/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="30" customHeight="1">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>SCTC-Run1</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>S1_FullPixel_Symmetric_Calibration</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=symmetric</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H81" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J81" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K81" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L81" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M81" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N81" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O81" s="7" t="n"/>
+      <c r="P81" s="7" t="n"/>
+      <c r="Q81" s="5" t="n"/>
+      <c r="R81" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S81" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T81" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U81" s="8" t="n">
+        <v>80.42610000000001</v>
+      </c>
+      <c r="V81" s="8" t="n">
+        <v>85.6097</v>
+      </c>
+      <c r="W81" s="8" t="n">
+        <v>92.19580000000001</v>
+      </c>
+      <c r="X81" s="8" t="n">
+        <v>82.93700000000001</v>
+      </c>
+      <c r="Y81" s="8" t="n">
+        <v>70.8481</v>
+      </c>
+      <c r="Z81" s="8" t="n">
+        <v>77.8843</v>
+      </c>
+      <c r="AA81" s="9" t="n"/>
+      <c r="AB81" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC81" s="5" t="inlineStr">
+        <is>
+          <t>3:32:56.072083</t>
+        </is>
+      </c>
+      <c r="AD81" s="5" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="AE81" s="6" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S1/SYSU/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="30" customHeight="1">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>SCTC-Run1</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>S1_FullPixel_Symmetric_Calibration</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=symmetric</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J82" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K82" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L82" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M82" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N82" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O82" s="7" t="n"/>
+      <c r="P82" s="7" t="n"/>
+      <c r="Q82" s="5" t="n"/>
+      <c r="R82" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S82" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T82" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U82" s="8" t="n">
+        <v>92.1589</v>
+      </c>
+      <c r="V82" s="8" t="n">
+        <v>95.1091</v>
+      </c>
+      <c r="W82" s="8" t="n">
+        <v>99.5009</v>
+      </c>
+      <c r="X82" s="8" t="n">
+        <v>93.61070000000001</v>
+      </c>
+      <c r="Y82" s="8" t="n">
+        <v>87.9889</v>
+      </c>
+      <c r="Z82" s="8" t="n">
+        <v>93.3511</v>
+      </c>
+      <c r="AA82" s="9" t="n"/>
+      <c r="AB82" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC82" s="5" t="inlineStr">
+        <is>
+          <t>2:40:44.864364</t>
+        </is>
+      </c>
+      <c r="AD82" s="5" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="AE82" s="6" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S1/WHU/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="30" customHeight="1">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>SCTC-Run1</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>S2_SCTC_UnchangedAware_Symmetric_CrossTemporal_Calibration</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=sctc</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H83" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J83" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K83" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L83" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M83" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N83" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O83" s="7" t="n"/>
+      <c r="P83" s="7" t="n"/>
+      <c r="Q83" s="5" t="n"/>
+      <c r="R83" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S83" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T83" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U83" s="8" t="n">
+        <v>97.4438</v>
+      </c>
+      <c r="V83" s="8" t="n">
+        <v>97.71940000000001</v>
+      </c>
+      <c r="W83" s="8" t="n">
+        <v>99.4038</v>
+      </c>
+      <c r="X83" s="8" t="n">
+        <v>97.5814</v>
+      </c>
+      <c r="Y83" s="8" t="n">
+        <v>95.277</v>
+      </c>
+      <c r="Z83" s="8" t="n">
+        <v>97.2414</v>
+      </c>
+      <c r="AA83" s="9" t="n"/>
+      <c r="AB83" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="5" t="inlineStr">
+        <is>
+          <t>2:52:30.285254</t>
+        </is>
+      </c>
+      <c r="AD83" s="5" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="AE83" s="6" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S2/CDD/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="30" customHeight="1">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>SCTC-Run1</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>S2_SCTC_UnchangedAware_Symmetric_CrossTemporal_Calibration</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=sctc</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H84" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J84" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K84" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L84" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M84" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N84" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O84" s="7" t="n"/>
+      <c r="P84" s="7" t="n"/>
+      <c r="Q84" s="5" t="n"/>
+      <c r="R84" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S84" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T84" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U84" s="8" t="n">
+        <v>90.1421</v>
+      </c>
+      <c r="V84" s="8" t="n">
+        <v>91.4601</v>
+      </c>
+      <c r="W84" s="8" t="n">
+        <v>99.069</v>
+      </c>
+      <c r="X84" s="8" t="n">
+        <v>90.7963</v>
+      </c>
+      <c r="Y84" s="8" t="n">
+        <v>83.14399999999999</v>
+      </c>
+      <c r="Z84" s="8" t="n">
+        <v>90.3061</v>
+      </c>
+      <c r="AA84" s="9" t="n"/>
+      <c r="AB84" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="5" t="inlineStr">
+        <is>
+          <t>3:18:11.767618</t>
+        </is>
+      </c>
+      <c r="AD84" s="5" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="AE84" s="6" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S2/LEVIR/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="30" customHeight="1">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>SCTC-Run1</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>S2_SCTC_UnchangedAware_Symmetric_CrossTemporal_Calibration</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=sctc</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H85" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J85" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K85" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L85" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M85" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N85" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O85" s="7" t="n"/>
+      <c r="P85" s="7" t="n"/>
+      <c r="Q85" s="5" t="n"/>
+      <c r="R85" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S85" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T85" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U85" s="8" t="n">
+        <v>81.00070000000001</v>
+      </c>
+      <c r="V85" s="8" t="n">
+        <v>84.595</v>
+      </c>
+      <c r="W85" s="8" t="n">
+        <v>92.04090000000001</v>
+      </c>
+      <c r="X85" s="8" t="n">
+        <v>82.75879999999999</v>
+      </c>
+      <c r="Y85" s="8" t="n">
+        <v>70.5885</v>
+      </c>
+      <c r="Z85" s="8" t="n">
+        <v>77.5882</v>
+      </c>
+      <c r="AA85" s="9" t="n"/>
+      <c r="AB85" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="5" t="inlineStr">
+        <is>
+          <t>4:06:34.060509</t>
+        </is>
+      </c>
+      <c r="AD85" s="5" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1</t>
+        </is>
+      </c>
+      <c r="AE85" s="6" t="inlineStr">
+        <is>
+          <t>outputs/SCTC/Run1/S2/SYSU/train_log.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="30" customHeight="1">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>SCTC-Run1</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>S2_SCTC_UnchangedAware_Symmetric_CrossTemporal_Calibration</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>batch=64; steps=40000; seed=2333; lr=0.0005; lr_mode=poly; wd=0.0001; backbone_lr=1.0; dice=batch; temporal=sctc</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="H86" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I86" s="5" t="n">
+        <v>2333</v>
+      </c>
+      <c r="J86" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K86" s="5" t="inlineStr">
+        <is>
+          <t>poly</t>
+        </is>
+      </c>
+      <c r="L86" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M86" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N86" s="5" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="O86" s="7" t="n"/>
+      <c r="P86" s="7" t="n"/>
+      <c r="Q86" s="5" t="n"/>
+      <c r="R86" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="S86" s="8" t="n">
+        <v>2.9131</v>
+      </c>
+      <c r="T86" s="8" t="n">
+        <v>2.7676</v>
+      </c>
+      <c r="U86" s="8" t="n">
+        <v>92.7942</v>
+      </c>
+      <c r="V86" s="8" t="n">
+        <v>95.1825</v>
+      </c>
+      <c r="W86" s="8" t="n">
+        <v>99.5278</v>
+      </c>
+      <c r="X86" s="8" t="n">
+        <v>93.9731</v>
+      </c>
+      <c r="Y86" s="8" t="n">
+        <v>88.6315</v>
+      </c>
+      <c r="Z86" s="8" t="n">
+        <v>93.7274</v>
+      </c>
+      <c r="AA86" s="9" t="n"/>
+      <c r="AB86" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC86" s="5" t="inlineStr">
+        <is>
           <t>2:08:54.218613</t>
         </is>
       </c>
-      <c r="AD76" s="5" t="inlineStr">
+      <c r="AD86" s="5" t="inlineStr">
         <is>
           <t>outputs/SCTC/Run1</t>
         </is>
       </c>
-      <c r="AE76" s="6" t="inlineStr">
+      <c r="AE86" s="6" t="inlineStr">
         <is>
           <t>outputs/SCTC/Run1/S2/WHU/train_log.txt</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="X2:X76">
+  <conditionalFormatting sqref="X2:X86">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -9347,7 +10429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C76"/>
+  <dimension ref="A1:C86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -10647,6 +11729,176 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SAGE-CD/Run2</t>
+        </is>
+      </c>
+      <c r="B77" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SAGE-CD/Run2/R0/SYSU/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C77" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SAGE-CD/Run2</t>
+        </is>
+      </c>
+      <c r="B78" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SAGE-CD/Run2/R0/WHU/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C78" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SAGE-CD/Run2</t>
+        </is>
+      </c>
+      <c r="B79" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SAGE-CD/Run2/R1/SYSU/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C79" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SAGE-CD/Run2</t>
+        </is>
+      </c>
+      <c r="B80" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SAGE-CD/Run2/R1/WHU/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C80" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SAGE-CD/Run2</t>
+        </is>
+      </c>
+      <c r="B81" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SAGE-CD/Run2/R2/SYSU/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C81" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SAGE-CD/Run2</t>
+        </is>
+      </c>
+      <c r="B82" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SAGE-CD/Run2/R2/WHU/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C82" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SAGE-CD/Run2</t>
+        </is>
+      </c>
+      <c r="B83" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SAGE-CD/Run2/R3/SYSU/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C83" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SAGE-CD/Run2</t>
+        </is>
+      </c>
+      <c r="B84" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SAGE-CD/Run2/R3/WHU/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C84" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SAGE-CD/Run2</t>
+        </is>
+      </c>
+      <c r="B85" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SAGE-CD/Run2/R4/SYSU/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C85" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SAGE-CD/Run2</t>
+        </is>
+      </c>
+      <c r="B86" s="11" t="inlineStr">
+        <is>
+          <t>outputs/SAGE-CD/Run2/R4/WHU/train_log.txt</t>
+        </is>
+      </c>
+      <c r="C86" s="11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
